--- a/docs/toetsmodel/Hypotheek_Toetsmodel_2026.xlsx
+++ b/docs/toetsmodel/Hypotheek_Toetsmodel_2026.xlsx
@@ -2540,7 +2540,7 @@
       </c>
       <c r="C10" s="11" t="n">
         <f aca="false">INDEX(Berekening!$C$83:$M$83,$C$4)</f>
-        <v>1114368.70942306</v>
+        <v>1056874.46685809</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="C11" s="11" t="n">
         <f aca="false">-MIN(INDEX(Berekening!$C$18:$M$18,$C$4)*INDEX(Berekening!$C$11:$M$11,$C$4),INDEX(Berekening!$C$83:$M$83,$C$4))</f>
-        <v>-40458.6134455491</v>
+        <v>-37286.0696256435</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="C12" s="11" t="n">
         <f aca="false">-MIN(INDEX(Berekening!$C$75:$M$75,$C$4),INDEX(Berekening!$C$84:$M$84,$C$4))</f>
-        <v>-35692.1953733948</v>
+        <v>-80110.1194056814</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="C17" s="12" t="n">
         <f aca="false">INDEX(Berekening!$C$101:$M$101,$C$4)</f>
-        <v>1048217.90060412</v>
+        <v>949478.277826761</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="C18" s="11" t="n">
         <f aca="false">-IF(INDEX(Berekening!$C$47:$M$47,$C$4)=1,INDEX(Berekening!$C$44:$M$44,$C$4)*INDEX(Berekening!$C$11:$M$11,$C$4),0)</f>
-        <v>-603282.429596972</v>
+        <v>-555976.311549913</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="C19" s="11" t="n">
         <f aca="false">C20-(C17+C18)</f>
-        <v>-38636.8713121134</v>
+        <v>-65149.7959022105</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="C20" s="12" t="n">
         <f aca="false">INDEX(Berekening!$C$105:$M$105,$C$4)</f>
-        <v>406298.599695031</v>
+        <v>328352.170374638</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="C21" s="11" t="n">
         <f aca="false">C22-C20</f>
-        <v>-30048.509695031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C22" s="12" t="n">
         <f aca="false">INDEX(Berekening!$C$118:$M$118,$C$4)</f>
-        <v>376250.09</v>
+        <v>328352.170374638</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="C24" s="12" t="n">
         <f aca="false">INDEX(Berekening!$C$117:$M$117,$C$4)</f>
-        <v>1000000</v>
+        <v>952102.080374638</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="C27" s="12" t="n">
         <f aca="false">INDEX(Berekening!$C$120:$M$120,$C$4)</f>
-        <v>52270.09</v>
+        <v>4372.1703746377</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="C30" s="11" t="n">
         <f aca="false">INDEX(Berekening!$C$9:$M$9,$C$4)</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="C31" s="14" t="n">
         <f aca="false">INDEX(Berekening!$C$10:$M$10,$C$4)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="C32" s="15" t="n">
         <f aca="false">INDEX(Berekening!$C$81:$M$81,$C$4)</f>
-        <v>0.274</v>
+        <v>0.292</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="C33" s="14" t="n">
         <f aca="false">INDEX(Berekening!$C$107:$M$107,$C$4)</f>
-        <v>0.0344533312677632</v>
+        <v>0.036487603997058</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="C34" s="16" t="n">
         <f aca="false">INDEX(Berekening!$C$71:$M$71,$C$4)</f>
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="C36" s="11" t="n">
         <f aca="false">INDEX(Berekening!$C$123:$M$123,$C$4)</f>
-        <v>52270.0899999999</v>
+        <v>4372.1703746377</v>
       </c>
     </row>
   </sheetData>
@@ -3067,16 +3067,16 @@
         <v>83</v>
       </c>
       <c r="C11" s="22" t="n">
-        <v>115000</v>
+        <v>107000</v>
       </c>
       <c r="D11" s="22" t="n">
-        <v>115000</v>
+        <v>107000</v>
       </c>
       <c r="E11" s="22" t="n">
-        <v>115000</v>
+        <v>107000</v>
       </c>
       <c r="F11" s="22" t="n">
-        <v>115000</v>
+        <v>107000</v>
       </c>
       <c r="G11" s="22" t="n">
         <v>0</v>
@@ -3085,19 +3085,19 @@
         <v>70000</v>
       </c>
       <c r="I11" s="22" t="n">
-        <v>115000</v>
+        <v>107000</v>
       </c>
       <c r="J11" s="22" t="n">
-        <v>115000</v>
+        <v>107000</v>
       </c>
       <c r="K11" s="22" t="n">
-        <v>115000</v>
+        <v>107000</v>
       </c>
       <c r="L11" s="22" t="n">
-        <v>115000</v>
+        <v>107000</v>
       </c>
       <c r="M11" s="22" t="n">
-        <v>115000</v>
+        <v>107000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3330,37 +3330,37 @@
         <v>98</v>
       </c>
       <c r="C18" s="24" t="n">
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="D18" s="24" t="n">
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="E18" s="24" t="n">
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="F18" s="24" t="n">
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="G18" s="24" t="n">
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="J18" s="24" t="n">
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="L18" s="24" t="n">
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="M18" s="24" t="n">
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3634,16 +3634,16 @@
         <v>107</v>
       </c>
       <c r="C26" s="22" t="n">
-        <v>142</v>
+        <v>332</v>
       </c>
       <c r="D26" s="22" t="n">
-        <v>142</v>
+        <v>332</v>
       </c>
       <c r="E26" s="22" t="n">
-        <v>142</v>
+        <v>332</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>142</v>
+        <v>332</v>
       </c>
       <c r="G26" s="22" t="n">
         <v>0</v>
@@ -3652,19 +3652,19 @@
         <v>120</v>
       </c>
       <c r="I26" s="22" t="n">
-        <v>142</v>
+        <v>332</v>
       </c>
       <c r="J26" s="22" t="n">
-        <v>142</v>
+        <v>332</v>
       </c>
       <c r="K26" s="22" t="n">
-        <v>142</v>
+        <v>332</v>
       </c>
       <c r="L26" s="22" t="n">
-        <v>142</v>
+        <v>332</v>
       </c>
       <c r="M26" s="22" t="n">
-        <v>142</v>
+        <v>332</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5633,19 +5633,19 @@
       </c>
       <c r="C9" s="29" t="n">
         <f aca="false">Invoer!C10+C7*Invoer!C11</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="D9" s="29" t="n">
         <f aca="false">Invoer!D10+D7*Invoer!D11</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="E9" s="29" t="n">
         <f aca="false">Invoer!E10+E7*Invoer!E11</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="F9" s="29" t="n">
         <f aca="false">Invoer!F10+F7*Invoer!F11</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="G9" s="29" t="n">
         <f aca="false">Invoer!G10+G7*Invoer!G11</f>
@@ -5657,23 +5657,23 @@
       </c>
       <c r="I9" s="29" t="n">
         <f aca="false">Invoer!I10+I7*Invoer!I11</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="J9" s="29" t="n">
         <f aca="false">Invoer!J10+J7*Invoer!J11</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="K9" s="29" t="n">
         <f aca="false">Invoer!K10+K7*Invoer!K11</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="L9" s="29" t="n">
         <f aca="false">Invoer!L10+L7*Invoer!L11</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="M9" s="29" t="n">
         <f aca="false">Invoer!M10+M7*Invoer!M11</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5685,15 +5685,15 @@
       </c>
       <c r="C10" s="30" t="n">
         <f aca="false">IF(AND(Invoer!C19&lt;10,AFM_Toetsrente&gt;Invoer!C18),AFM_Toetsrente,Invoer!C18)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="D10" s="30" t="n">
         <f aca="false">IF(AND(Invoer!D19&lt;10,AFM_Toetsrente&gt;Invoer!D18),AFM_Toetsrente,Invoer!D18)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="E10" s="30" t="n">
         <f aca="false">IF(AND(Invoer!E19&lt;10,AFM_Toetsrente&gt;Invoer!E18),AFM_Toetsrente,Invoer!E18)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="F10" s="30" t="n">
         <f aca="false">IF(AND(Invoer!F19&lt;10,AFM_Toetsrente&gt;Invoer!F18),AFM_Toetsrente,Invoer!F18)</f>
@@ -5701,31 +5701,31 @@
       </c>
       <c r="G10" s="30" t="n">
         <f aca="false">IF(AND(Invoer!G19&lt;10,AFM_Toetsrente&gt;Invoer!G18),AFM_Toetsrente,Invoer!G18)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="H10" s="30" t="n">
         <f aca="false">IF(AND(Invoer!H19&lt;10,AFM_Toetsrente&gt;Invoer!H18),AFM_Toetsrente,Invoer!H18)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="I10" s="30" t="n">
         <f aca="false">IF(AND(Invoer!I19&lt;10,AFM_Toetsrente&gt;Invoer!I18),AFM_Toetsrente,Invoer!I18)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="J10" s="30" t="n">
         <f aca="false">IF(AND(Invoer!J19&lt;10,AFM_Toetsrente&gt;Invoer!J18),AFM_Toetsrente,Invoer!J18)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="K10" s="30" t="n">
         <f aca="false">IF(AND(Invoer!K19&lt;10,AFM_Toetsrente&gt;Invoer!K18),AFM_Toetsrente,Invoer!K18)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="L10" s="30" t="n">
         <f aca="false">IF(AND(Invoer!L19&lt;10,AFM_Toetsrente&gt;Invoer!L18),AFM_Toetsrente,Invoer!L18)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="M10" s="30" t="n">
         <f aca="false">IF(AND(Invoer!M19&lt;10,AFM_Toetsrente&gt;Invoer!M18),AFM_Toetsrente,Invoer!M18)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5735,15 +5735,15 @@
       <c r="B11" s="19"/>
       <c r="C11" s="31" t="n">
         <f aca="false">IF(C10=0,360,(1-(1+C10/12)^(-360))/(C10/12))</f>
-        <v>209.461240454195</v>
+        <v>193.036432302847</v>
       </c>
       <c r="D11" s="31" t="n">
         <f aca="false">IF(D10=0,360,(1-(1+D10/12)^(-360))/(D10/12))</f>
-        <v>209.461240454195</v>
+        <v>193.036432302847</v>
       </c>
       <c r="E11" s="31" t="n">
         <f aca="false">IF(E10=0,360,(1-(1+E10/12)^(-360))/(E10/12))</f>
-        <v>209.461240454195</v>
+        <v>193.036432302847</v>
       </c>
       <c r="F11" s="31" t="n">
         <f aca="false">IF(F10=0,360,(1-(1+F10/12)^(-360))/(F10/12))</f>
@@ -5751,31 +5751,31 @@
       </c>
       <c r="G11" s="31" t="n">
         <f aca="false">IF(G10=0,360,(1-(1+G10/12)^(-360))/(G10/12))</f>
-        <v>209.461240454195</v>
+        <v>193.036432302847</v>
       </c>
       <c r="H11" s="31" t="n">
         <f aca="false">IF(H10=0,360,(1-(1+H10/12)^(-360))/(H10/12))</f>
-        <v>209.461240454195</v>
+        <v>193.036432302847</v>
       </c>
       <c r="I11" s="31" t="n">
         <f aca="false">IF(I10=0,360,(1-(1+I10/12)^(-360))/(I10/12))</f>
-        <v>209.461240454195</v>
+        <v>193.036432302847</v>
       </c>
       <c r="J11" s="31" t="n">
         <f aca="false">IF(J10=0,360,(1-(1+J10/12)^(-360))/(J10/12))</f>
-        <v>209.461240454195</v>
+        <v>193.036432302847</v>
       </c>
       <c r="K11" s="31" t="n">
         <f aca="false">IF(K10=0,360,(1-(1+K10/12)^(-360))/(K10/12))</f>
-        <v>209.461240454195</v>
+        <v>193.036432302847</v>
       </c>
       <c r="L11" s="31" t="n">
         <f aca="false">IF(L10=0,360,(1-(1+L10/12)^(-360))/(L10/12))</f>
-        <v>209.461240454195</v>
+        <v>193.036432302847</v>
       </c>
       <c r="M11" s="31" t="n">
         <f aca="false">IF(M10=0,360,(1-(1+M10/12)^(-360))/(M10/12))</f>
-        <v>209.461240454195</v>
+        <v>193.036432302847</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8495,15 +8495,15 @@
       </c>
       <c r="C67" s="30" t="n">
         <f aca="false">IF(Invoer!C19&lt;10,MAX(Invoer!C18,AFM_Toetsrente),Invoer!C18)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="D67" s="30" t="n">
         <f aca="false">IF(Invoer!D19&lt;10,MAX(Invoer!D18,AFM_Toetsrente),Invoer!D18)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="E67" s="30" t="n">
         <f aca="false">IF(Invoer!E19&lt;10,MAX(Invoer!E18,AFM_Toetsrente),Invoer!E18)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="F67" s="30" t="n">
         <f aca="false">IF(Invoer!F19&lt;10,MAX(Invoer!F18,AFM_Toetsrente),Invoer!F18)</f>
@@ -8511,31 +8511,31 @@
       </c>
       <c r="G67" s="30" t="n">
         <f aca="false">IF(Invoer!G19&lt;10,MAX(Invoer!G18,AFM_Toetsrente),Invoer!G18)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="H67" s="30" t="n">
         <f aca="false">IF(Invoer!H19&lt;10,MAX(Invoer!H18,AFM_Toetsrente),Invoer!H18)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="I67" s="30" t="n">
         <f aca="false">IF(Invoer!I19&lt;10,MAX(Invoer!I18,AFM_Toetsrente),Invoer!I18)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="J67" s="30" t="n">
         <f aca="false">IF(Invoer!J19&lt;10,MAX(Invoer!J18,AFM_Toetsrente),Invoer!J18)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="K67" s="30" t="n">
         <f aca="false">IF(Invoer!K19&lt;10,MAX(Invoer!K18,AFM_Toetsrente),Invoer!K18)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="L67" s="30" t="n">
         <f aca="false">IF(Invoer!L19&lt;10,MAX(Invoer!L18,AFM_Toetsrente),Invoer!L18)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="M67" s="30" t="n">
         <f aca="false">IF(Invoer!M19&lt;10,MAX(Invoer!M18,AFM_Toetsrente),Invoer!M18)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8547,15 +8547,15 @@
       </c>
       <c r="C68" s="30" t="n">
         <f aca="false">(C64+C66*C67)/(C63+C66)</f>
-        <v>0.0348065552716385</v>
+        <v>0.0371653095711625</v>
       </c>
       <c r="D68" s="30" t="n">
         <f aca="false">(D64+D66*D67)/(D63+D66)</f>
-        <v>0.0348065552716385</v>
+        <v>0.0371653095711625</v>
       </c>
       <c r="E68" s="30" t="n">
         <f aca="false">(E64+E66*E67)/(E63+E66)</f>
-        <v>0.0465815155079362</v>
+        <v>0.0489402698074602</v>
       </c>
       <c r="F68" s="30" t="n">
         <f aca="false">(F64+F66*F67)/(F63+F66)</f>
@@ -8563,31 +8563,31 @@
       </c>
       <c r="G68" s="30" t="n">
         <f aca="false">(G64+G66*G67)/(G63+G66)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="H68" s="30" t="n">
         <f aca="false">(H64+H66*H67)/(H63+H66)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="I68" s="30" t="n">
         <f aca="false">(I64+I66*I67)/(I63+I66)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="J68" s="30" t="n">
         <f aca="false">(J64+J66*J67)/(J63+J66)</f>
-        <v>0.0348065552716385</v>
+        <v>0.0371653095711625</v>
       </c>
       <c r="K68" s="30" t="n">
         <f aca="false">(K64+K66*K67)/(K63+K66)</f>
-        <v>0.0475095576187876</v>
+        <v>0.0492279628618241</v>
       </c>
       <c r="L68" s="30" t="n">
         <f aca="false">(L64+L66*L67)/(L63+L66)</f>
-        <v>0.0348065552716385</v>
+        <v>0.0371653095711625</v>
       </c>
       <c r="M68" s="30" t="n">
         <f aca="false">(M64+M66*M67)/(M63+M66)</f>
-        <v>0.0348065552716385</v>
+        <v>0.0371653095711625</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8599,47 +8599,47 @@
       </c>
       <c r="C69" s="30" t="n">
         <f aca="false">(C65+C66*Invoer!C18)/(C63+C66)</f>
-        <v>0.024143681921994</v>
+        <v>0.026502436221518</v>
       </c>
       <c r="D69" s="30" t="n">
         <f aca="false">(D65+D66*Invoer!D18)/(D63+D66)</f>
-        <v>0.024143681921994</v>
+        <v>0.026502436221518</v>
       </c>
       <c r="E69" s="30" t="n">
         <f aca="false">(E65+E66*Invoer!E18)/(E63+E66)</f>
-        <v>0.024143681921994</v>
+        <v>0.026502436221518</v>
       </c>
       <c r="F69" s="30" t="n">
         <f aca="false">(F65+F66*Invoer!F18)/(F63+F66)</f>
-        <v>0.024143681921994</v>
+        <v>0.026502436221518</v>
       </c>
       <c r="G69" s="30" t="n">
         <f aca="false">(G65+G66*Invoer!G18)/(G63+G66)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="H69" s="30" t="n">
         <f aca="false">(H65+H66*Invoer!H18)/(H63+H66)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="I69" s="30" t="n">
         <f aca="false">(I65+I66*Invoer!I18)/(I63+I66)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="J69" s="30" t="n">
         <f aca="false">(J65+J66*Invoer!J18)/(J63+J66)</f>
-        <v>0.024143681921994</v>
+        <v>0.026502436221518</v>
       </c>
       <c r="K69" s="30" t="n">
         <f aca="false">(K65+K66*Invoer!K18)/(K63+K66)</f>
-        <v>0.0352689787001638</v>
+        <v>0.0369873839432004</v>
       </c>
       <c r="L69" s="30" t="n">
         <f aca="false">(L65+L66*Invoer!L18)/(L63+L66)</f>
-        <v>0.024143681921994</v>
+        <v>0.026502436221518</v>
       </c>
       <c r="M69" s="30" t="n">
         <f aca="false">(M65+M66*Invoer!M18)/(M63+M66)</f>
-        <v>0.024143681921994</v>
+        <v>0.026502436221518</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8651,15 +8651,15 @@
       </c>
       <c r="C70" s="30" t="n">
         <f aca="false">IF(Invoer!C27="Contractrente",C69,C68)</f>
-        <v>0.0348065552716385</v>
+        <v>0.0371653095711625</v>
       </c>
       <c r="D70" s="30" t="n">
         <f aca="false">IF(Invoer!D27="Contractrente",D69,D68)</f>
-        <v>0.0348065552716385</v>
+        <v>0.0371653095711625</v>
       </c>
       <c r="E70" s="30" t="n">
         <f aca="false">IF(Invoer!E27="Contractrente",E69,E68)</f>
-        <v>0.0465815155079362</v>
+        <v>0.0489402698074602</v>
       </c>
       <c r="F70" s="30" t="n">
         <f aca="false">IF(Invoer!F27="Contractrente",F69,F68)</f>
@@ -8667,31 +8667,31 @@
       </c>
       <c r="G70" s="30" t="n">
         <f aca="false">IF(Invoer!G27="Contractrente",G69,G68)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="H70" s="30" t="n">
         <f aca="false">IF(Invoer!H27="Contractrente",H69,H68)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="I70" s="30" t="n">
         <f aca="false">IF(Invoer!I27="Contractrente",I69,I68)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="J70" s="30" t="n">
         <f aca="false">IF(Invoer!J27="Contractrente",J69,J68)</f>
-        <v>0.0348065552716385</v>
+        <v>0.0371653095711625</v>
       </c>
       <c r="K70" s="30" t="n">
         <f aca="false">IF(Invoer!K27="Contractrente",K69,K68)</f>
-        <v>0.0352689787001638</v>
+        <v>0.0369873839432004</v>
       </c>
       <c r="L70" s="30" t="n">
         <f aca="false">IF(Invoer!L27="Contractrente",L69,L68)</f>
-        <v>0.0348065552716385</v>
+        <v>0.0371653095711625</v>
       </c>
       <c r="M70" s="30" t="n">
         <f aca="false">IF(Invoer!M27="Contractrente",M69,M68)</f>
-        <v>0.0348065552716385</v>
+        <v>0.0371653095711625</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8701,11 +8701,11 @@
       <c r="B71" s="19"/>
       <c r="C71" s="31" t="n">
         <f aca="false">INDEX(Studie_factor,SUMPRODUCT(--(Studie_upTo&lt;ROUND(C70,5)))+1)</f>
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="D71" s="31" t="n">
         <f aca="false">INDEX(Studie_factor,SUMPRODUCT(--(Studie_upTo&lt;ROUND(D70,5)))+1)</f>
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="E71" s="31" t="n">
         <f aca="false">INDEX(Studie_factor,SUMPRODUCT(--(Studie_upTo&lt;ROUND(E70,5)))+1)</f>
@@ -8717,19 +8717,19 @@
       </c>
       <c r="G71" s="31" t="n">
         <f aca="false">INDEX(Studie_factor,SUMPRODUCT(--(Studie_upTo&lt;ROUND(G70,5)))+1)</f>
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="H71" s="31" t="n">
         <f aca="false">INDEX(Studie_factor,SUMPRODUCT(--(Studie_upTo&lt;ROUND(H70,5)))+1)</f>
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="I71" s="31" t="n">
         <f aca="false">INDEX(Studie_factor,SUMPRODUCT(--(Studie_upTo&lt;ROUND(I70,5)))+1)</f>
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="J71" s="31" t="n">
         <f aca="false">INDEX(Studie_factor,SUMPRODUCT(--(Studie_upTo&lt;ROUND(J70,5)))+1)</f>
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="K71" s="31" t="n">
         <f aca="false">INDEX(Studie_factor,SUMPRODUCT(--(Studie_upTo&lt;ROUND(K70,5)))+1)</f>
@@ -8737,11 +8737,11 @@
       </c>
       <c r="L71" s="31" t="n">
         <f aca="false">INDEX(Studie_factor,SUMPRODUCT(--(Studie_upTo&lt;ROUND(L70,5)))+1)</f>
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="M71" s="31" t="n">
         <f aca="false">INDEX(Studie_factor,SUMPRODUCT(--(Studie_upTo&lt;ROUND(M70,5)))+1)</f>
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8753,15 +8753,15 @@
       </c>
       <c r="C72" s="30" t="n">
         <f aca="false">IF(Invoer!C28="Gewogen",C68,C10)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="D72" s="30" t="n">
         <f aca="false">IF(Invoer!D28="Gewogen",D68,D10)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="E72" s="30" t="n">
         <f aca="false">IF(Invoer!E28="Gewogen",E68,E10)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="F72" s="30" t="n">
         <f aca="false">IF(Invoer!F28="Gewogen",F68,F10)</f>
@@ -8769,31 +8769,31 @@
       </c>
       <c r="G72" s="30" t="n">
         <f aca="false">IF(Invoer!G28="Gewogen",G68,G10)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="H72" s="30" t="n">
         <f aca="false">IF(Invoer!H28="Gewogen",H68,H10)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="I72" s="30" t="n">
         <f aca="false">IF(Invoer!I28="Gewogen",I68,I10)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="J72" s="30" t="n">
         <f aca="false">IF(Invoer!J28="Gewogen",J68,J10)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="K72" s="30" t="n">
         <f aca="false">IF(Invoer!K28="Gewogen",K68,K10)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="L72" s="30" t="n">
         <f aca="false">IF(Invoer!L28="Gewogen",L68,L10)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="M72" s="30" t="n">
         <f aca="false">IF(Invoer!M28="Gewogen",M68,M10)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8803,15 +8803,15 @@
       <c r="B73" s="19"/>
       <c r="C73" s="37" t="n">
         <f aca="false">IF(C72=0,1/360,(C72/12)/(1-(1+C72/12)^(-360)))</f>
-        <v>0.00477415295465454</v>
+        <v>0.00518036926019821</v>
       </c>
       <c r="D73" s="37" t="n">
         <f aca="false">IF(D72=0,1/360,(D72/12)/(1-(1+D72/12)^(-360)))</f>
-        <v>0.00477415295465454</v>
+        <v>0.00518036926019821</v>
       </c>
       <c r="E73" s="37" t="n">
         <f aca="false">IF(E72=0,1/360,(E72/12)/(1-(1+E72/12)^(-360)))</f>
-        <v>0.00477415295465454</v>
+        <v>0.00518036926019821</v>
       </c>
       <c r="F73" s="37" t="n">
         <f aca="false">IF(F72=0,1/360,(F72/12)/(1-(1+F72/12)^(-360)))</f>
@@ -8819,31 +8819,31 @@
       </c>
       <c r="G73" s="37" t="n">
         <f aca="false">IF(G72=0,1/360,(G72/12)/(1-(1+G72/12)^(-360)))</f>
-        <v>0.00477415295465454</v>
+        <v>0.00518036926019821</v>
       </c>
       <c r="H73" s="37" t="n">
         <f aca="false">IF(H72=0,1/360,(H72/12)/(1-(1+H72/12)^(-360)))</f>
-        <v>0.00477415295465454</v>
+        <v>0.00518036926019821</v>
       </c>
       <c r="I73" s="37" t="n">
         <f aca="false">IF(I72=0,1/360,(I72/12)/(1-(1+I72/12)^(-360)))</f>
-        <v>0.00477415295465454</v>
+        <v>0.00518036926019821</v>
       </c>
       <c r="J73" s="37" t="n">
         <f aca="false">IF(J72=0,1/360,(J72/12)/(1-(1+J72/12)^(-360)))</f>
-        <v>0.00477415295465454</v>
+        <v>0.00518036926019821</v>
       </c>
       <c r="K73" s="37" t="n">
         <f aca="false">IF(K72=0,1/360,(K72/12)/(1-(1+K72/12)^(-360)))</f>
-        <v>0.00477415295465454</v>
+        <v>0.00518036926019821</v>
       </c>
       <c r="L73" s="37" t="n">
         <f aca="false">IF(L72=0,1/360,(L72/12)/(1-(1+L72/12)^(-360)))</f>
-        <v>0.00477415295465454</v>
+        <v>0.00518036926019821</v>
       </c>
       <c r="M73" s="37" t="n">
         <f aca="false">IF(M72=0,1/360,(M72/12)/(1-(1+M72/12)^(-360)))</f>
-        <v>0.00477415295465454</v>
+        <v>0.00518036926019821</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8855,19 +8855,19 @@
       </c>
       <c r="C74" s="32" t="n">
         <f aca="false">Invoer!C26*C71</f>
-        <v>170.4</v>
+        <v>415</v>
       </c>
       <c r="D74" s="32" t="n">
         <f aca="false">Invoer!D26*D71</f>
-        <v>170.4</v>
+        <v>415</v>
       </c>
       <c r="E74" s="32" t="n">
         <f aca="false">Invoer!E26*E71</f>
-        <v>184.6</v>
+        <v>431.6</v>
       </c>
       <c r="F74" s="32" t="n">
         <f aca="false">Invoer!F26*F71</f>
-        <v>177.5</v>
+        <v>415</v>
       </c>
       <c r="G74" s="32" t="n">
         <f aca="false">Invoer!G26*G71</f>
@@ -8875,27 +8875,27 @@
       </c>
       <c r="H74" s="32" t="n">
         <f aca="false">Invoer!H26*H71</f>
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="I74" s="32" t="n">
         <f aca="false">Invoer!I26*I71</f>
-        <v>177.5</v>
+        <v>431.6</v>
       </c>
       <c r="J74" s="32" t="n">
         <f aca="false">Invoer!J26*J71</f>
-        <v>170.4</v>
+        <v>415</v>
       </c>
       <c r="K74" s="32" t="n">
         <f aca="false">Invoer!K26*K71</f>
-        <v>177.5</v>
+        <v>415</v>
       </c>
       <c r="L74" s="32" t="n">
         <f aca="false">Invoer!L26*L71</f>
-        <v>170.4</v>
+        <v>415</v>
       </c>
       <c r="M74" s="32" t="n">
         <f aca="false">Invoer!M26*M71</f>
-        <v>170.4</v>
+        <v>415</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8907,19 +8907,19 @@
       </c>
       <c r="C75" s="35" t="n">
         <f aca="false">C74/C73</f>
-        <v>35692.1953733948</v>
+        <v>80110.1194056814</v>
       </c>
       <c r="D75" s="35" t="n">
         <f aca="false">D74/D73</f>
-        <v>35692.1953733948</v>
+        <v>80110.1194056814</v>
       </c>
       <c r="E75" s="35" t="n">
         <f aca="false">E74/E73</f>
-        <v>38666.5449878444</v>
+        <v>83314.5241819087</v>
       </c>
       <c r="F75" s="35" t="n">
         <f aca="false">F74/F73</f>
-        <v>33064.9870256784</v>
+        <v>77306.8710741212</v>
       </c>
       <c r="G75" s="35" t="n">
         <f aca="false">G74/G73</f>
@@ -8927,27 +8927,27 @@
       </c>
       <c r="H75" s="35" t="n">
         <f aca="false">H74/H73</f>
-        <v>31419.1860681293</v>
+        <v>30113.6834392441</v>
       </c>
       <c r="I75" s="35" t="n">
         <f aca="false">I74/I73</f>
-        <v>37179.3701806196</v>
+        <v>83314.5241819087</v>
       </c>
       <c r="J75" s="35" t="n">
         <f aca="false">J74/J73</f>
-        <v>35692.1953733948</v>
+        <v>80110.1194056814</v>
       </c>
       <c r="K75" s="35" t="n">
         <f aca="false">K74/K73</f>
-        <v>37179.3701806196</v>
+        <v>80110.1194056814</v>
       </c>
       <c r="L75" s="35" t="n">
         <f aca="false">L74/L73</f>
-        <v>35692.1953733948</v>
+        <v>80110.1194056814</v>
       </c>
       <c r="M75" s="35" t="n">
         <f aca="false">M74/M73</f>
-        <v>35692.1953733948</v>
+        <v>80110.1194056814</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8976,19 +8976,19 @@
       </c>
       <c r="C77" s="29" t="n">
         <f aca="false">INT(C9/1000)*1000</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="D77" s="29" t="n">
         <f aca="false">INT(D9/1000)*1000</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="E77" s="29" t="n">
         <f aca="false">INT(E9/1000)*1000</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="F77" s="29" t="n">
         <f aca="false">INT(F9/1000)*1000</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="G77" s="29" t="n">
         <f aca="false">INT(G9/1000)*1000</f>
@@ -9000,23 +9000,23 @@
       </c>
       <c r="I77" s="29" t="n">
         <f aca="false">INT(I9/1000)*1000</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="J77" s="29" t="n">
         <f aca="false">INT(J9/1000)*1000</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="K77" s="29" t="n">
         <f aca="false">INT(K9/1000)*1000</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="L77" s="29" t="n">
         <f aca="false">INT(L9/1000)*1000</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="M77" s="29" t="n">
         <f aca="false">INT(M9/1000)*1000</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9026,15 +9026,15 @@
       <c r="B78" s="19"/>
       <c r="C78" s="28" t="n">
         <f aca="false">MIN(10,MAX(1,ROUNDUP(ROUND(C10*100,3)/0.5-0.000000001,0)-2))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D78" s="28" t="n">
         <f aca="false">MIN(10,MAX(1,ROUNDUP(ROUND(D10*100,3)/0.5-0.000000001,0)-2))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E78" s="28" t="n">
         <f aca="false">MIN(10,MAX(1,ROUNDUP(ROUND(E10*100,3)/0.5-0.000000001,0)-2))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F78" s="28" t="n">
         <f aca="false">MIN(10,MAX(1,ROUNDUP(ROUND(F10*100,3)/0.5-0.000000001,0)-2))</f>
@@ -9042,31 +9042,31 @@
       </c>
       <c r="G78" s="28" t="n">
         <f aca="false">MIN(10,MAX(1,ROUNDUP(ROUND(G10*100,3)/0.5-0.000000001,0)-2))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H78" s="28" t="n">
         <f aca="false">MIN(10,MAX(1,ROUNDUP(ROUND(H10*100,3)/0.5-0.000000001,0)-2))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I78" s="28" t="n">
         <f aca="false">MIN(10,MAX(1,ROUNDUP(ROUND(I10*100,3)/0.5-0.000000001,0)-2))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J78" s="28" t="n">
         <f aca="false">MIN(10,MAX(1,ROUNDUP(ROUND(J10*100,3)/0.5-0.000000001,0)-2))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K78" s="28" t="n">
         <f aca="false">MIN(10,MAX(1,ROUNDUP(ROUND(K10*100,3)/0.5-0.000000001,0)-2))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L78" s="28" t="n">
         <f aca="false">MIN(10,MAX(1,ROUNDUP(ROUND(L10*100,3)/0.5-0.000000001,0)-2))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M78" s="28" t="n">
         <f aca="false">MIN(10,MAX(1,ROUNDUP(ROUND(M10*100,3)/0.5-0.000000001,0)-2))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9180,15 +9180,15 @@
       </c>
       <c r="C81" s="38" t="n">
         <f aca="false">INDEX(T1_Tabel,C80,C78)+(C79-INDEX(T1_Inkomen,C80))/(INDEX(T1_Inkomen,C80+1)-INDEX(T1_Inkomen,C80))*(INDEX(T1_Tabel,C80+1,C78)-INDEX(T1_Tabel,C80,C78))</f>
-        <v>0.274</v>
+        <v>0.292</v>
       </c>
       <c r="D81" s="38" t="n">
         <f aca="false">INDEX(T1_Tabel,D80,D78)+(D79-INDEX(T1_Inkomen,D80))/(INDEX(T1_Inkomen,D80+1)-INDEX(T1_Inkomen,D80))*(INDEX(T1_Tabel,D80+1,D78)-INDEX(T1_Tabel,D80,D78))</f>
-        <v>0.274</v>
+        <v>0.292</v>
       </c>
       <c r="E81" s="38" t="n">
         <f aca="false">INDEX(T1_Tabel,E80,E78)+(E79-INDEX(T1_Inkomen,E80))/(INDEX(T1_Inkomen,E80+1)-INDEX(T1_Inkomen,E80))*(INDEX(T1_Tabel,E80+1,E78)-INDEX(T1_Tabel,E80,E78))</f>
-        <v>0.274</v>
+        <v>0.292</v>
       </c>
       <c r="F81" s="38" t="n">
         <f aca="false">INDEX(T1_Tabel,F80,F78)+(F79-INDEX(T1_Inkomen,F80))/(INDEX(T1_Inkomen,F80+1)-INDEX(T1_Inkomen,F80))*(INDEX(T1_Tabel,F80+1,F78)-INDEX(T1_Tabel,F80,F78))</f>
@@ -9196,31 +9196,31 @@
       </c>
       <c r="G81" s="38" t="n">
         <f aca="false">INDEX(T1_Tabel,G80,G78)+(G79-INDEX(T1_Inkomen,G80))/(INDEX(T1_Inkomen,G80+1)-INDEX(T1_Inkomen,G80))*(INDEX(T1_Tabel,G80+1,G78)-INDEX(T1_Tabel,G80,G78))</f>
-        <v>0.226</v>
+        <v>0.246</v>
       </c>
       <c r="H81" s="38" t="n">
         <f aca="false">INDEX(T1_Tabel,H80,H78)+(H79-INDEX(T1_Inkomen,H80))/(INDEX(T1_Inkomen,H80+1)-INDEX(T1_Inkomen,H80))*(INDEX(T1_Tabel,H80+1,H78)-INDEX(T1_Tabel,H80,H78))</f>
-        <v>0.274</v>
+        <v>0.292</v>
       </c>
       <c r="I81" s="38" t="n">
         <f aca="false">INDEX(T1_Tabel,I80,I78)+(I79-INDEX(T1_Inkomen,I80))/(INDEX(T1_Inkomen,I80+1)-INDEX(T1_Inkomen,I80))*(INDEX(T1_Tabel,I80+1,I78)-INDEX(T1_Tabel,I80,I78))</f>
-        <v>0.274</v>
+        <v>0.292</v>
       </c>
       <c r="J81" s="38" t="n">
         <f aca="false">INDEX(T1_Tabel,J80,J78)+(J79-INDEX(T1_Inkomen,J80))/(INDEX(T1_Inkomen,J80+1)-INDEX(T1_Inkomen,J80))*(INDEX(T1_Tabel,J80+1,J78)-INDEX(T1_Tabel,J80,J78))</f>
-        <v>0.274</v>
+        <v>0.292</v>
       </c>
       <c r="K81" s="38" t="n">
         <f aca="false">INDEX(T1_Tabel,K80,K78)+(K79-INDEX(T1_Inkomen,K80))/(INDEX(T1_Inkomen,K80+1)-INDEX(T1_Inkomen,K80))*(INDEX(T1_Tabel,K80+1,K78)-INDEX(T1_Tabel,K80,K78))</f>
-        <v>0.274</v>
+        <v>0.292</v>
       </c>
       <c r="L81" s="38" t="n">
         <f aca="false">INDEX(T1_Tabel,L80,L78)+(L79-INDEX(T1_Inkomen,L80))/(INDEX(T1_Inkomen,L80+1)-INDEX(T1_Inkomen,L80))*(INDEX(T1_Tabel,L80+1,L78)-INDEX(T1_Tabel,L80,L78))</f>
-        <v>0.274</v>
+        <v>0.292</v>
       </c>
       <c r="M81" s="38" t="n">
         <f aca="false">INDEX(T1_Tabel,M80,M78)+(M79-INDEX(T1_Inkomen,M80))/(INDEX(T1_Inkomen,M80+1)-INDEX(T1_Inkomen,M80))*(INDEX(T1_Tabel,M80+1,M78)-INDEX(T1_Tabel,M80,M78))</f>
-        <v>0.274</v>
+        <v>0.292</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9232,47 +9232,47 @@
       </c>
       <c r="C82" s="32" t="n">
         <f aca="false">C81*C9/12</f>
-        <v>5320.16666666667</v>
+        <v>5475</v>
       </c>
       <c r="D82" s="32" t="n">
         <f aca="false">D81*D9/12</f>
-        <v>5320.16666666667</v>
+        <v>5475</v>
       </c>
       <c r="E82" s="32" t="n">
         <f aca="false">E81*E9/12</f>
-        <v>5320.16666666667</v>
+        <v>5475</v>
       </c>
       <c r="F82" s="32" t="n">
         <f aca="false">F81*F9/12</f>
-        <v>5669.66666666667</v>
+        <v>5475</v>
       </c>
       <c r="G82" s="32" t="n">
         <f aca="false">G81*G9/12</f>
-        <v>1130</v>
+        <v>1230</v>
       </c>
       <c r="H82" s="32" t="n">
         <f aca="false">H81*H9/12</f>
-        <v>3425</v>
+        <v>3650</v>
       </c>
       <c r="I82" s="32" t="n">
         <f aca="false">I81*I9/12</f>
-        <v>5320.16666666667</v>
+        <v>5475</v>
       </c>
       <c r="J82" s="32" t="n">
         <f aca="false">J81*J9/12</f>
-        <v>5320.16666666667</v>
+        <v>5475</v>
       </c>
       <c r="K82" s="32" t="n">
         <f aca="false">K81*K9/12</f>
-        <v>5320.16666666667</v>
+        <v>5475</v>
       </c>
       <c r="L82" s="32" t="n">
         <f aca="false">L81*L9/12</f>
-        <v>5320.16666666667</v>
+        <v>5475</v>
       </c>
       <c r="M82" s="32" t="n">
         <f aca="false">M81*M9/12</f>
-        <v>5320.16666666667</v>
+        <v>5475</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9284,47 +9284,47 @@
       </c>
       <c r="C83" s="35" t="n">
         <f aca="false">C82*C11</f>
-        <v>1114368.70942306</v>
+        <v>1056874.46685809</v>
       </c>
       <c r="D83" s="35" t="n">
         <f aca="false">D82*D11</f>
-        <v>1114368.70942306</v>
+        <v>1056874.46685809</v>
       </c>
       <c r="E83" s="35" t="n">
         <f aca="false">E82*E11</f>
-        <v>1114368.70942306</v>
+        <v>1056874.46685809</v>
       </c>
       <c r="F83" s="35" t="n">
         <f aca="false">F82*F11</f>
-        <v>1056154.6747789</v>
+        <v>1019891.85332726</v>
       </c>
       <c r="G83" s="35" t="n">
         <f aca="false">G82*G11</f>
-        <v>236691.20171324</v>
+        <v>237434.811732502</v>
       </c>
       <c r="H83" s="35" t="n">
         <f aca="false">H82*H11</f>
-        <v>717404.748555618</v>
+        <v>704582.977905391</v>
       </c>
       <c r="I83" s="35" t="n">
         <f aca="false">I82*I11</f>
-        <v>1114368.70942306</v>
+        <v>1056874.46685809</v>
       </c>
       <c r="J83" s="35" t="n">
         <f aca="false">J82*J11</f>
-        <v>1114368.70942306</v>
+        <v>1056874.46685809</v>
       </c>
       <c r="K83" s="35" t="n">
         <f aca="false">K82*K11</f>
-        <v>1114368.70942306</v>
+        <v>1056874.46685809</v>
       </c>
       <c r="L83" s="35" t="n">
         <f aca="false">L82*L11</f>
-        <v>1114368.70942306</v>
+        <v>1056874.46685809</v>
       </c>
       <c r="M83" s="35" t="n">
         <f aca="false">M82*M11</f>
-        <v>1114368.70942306</v>
+        <v>1056874.46685809</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9336,39 +9336,39 @@
       </c>
       <c r="C84" s="29" t="n">
         <f aca="false">MAX(0,C82-C18)*C11</f>
-        <v>1073910.09597751</v>
+        <v>1019588.39723244</v>
       </c>
       <c r="D84" s="29" t="n">
         <f aca="false">MAX(0,D82-D18)*D11</f>
-        <v>1073910.09597751</v>
+        <v>1019588.39723244</v>
       </c>
       <c r="E84" s="29" t="n">
         <f aca="false">MAX(0,E82-E18)*E11</f>
-        <v>1073910.09597751</v>
+        <v>1019588.39723244</v>
       </c>
       <c r="F84" s="29" t="n">
         <f aca="false">MAX(0,F82-F18)*F11</f>
-        <v>1020173.33560733</v>
+        <v>983910.514155698</v>
       </c>
       <c r="G84" s="29" t="n">
         <f aca="false">MAX(0,G82-G18)*G11</f>
-        <v>236691.20171324</v>
+        <v>237434.811732502</v>
       </c>
       <c r="H84" s="29" t="n">
         <f aca="false">MAX(0,H82-H18)*H11</f>
-        <v>717404.748555618</v>
+        <v>704582.977905391</v>
       </c>
       <c r="I84" s="29" t="n">
         <f aca="false">MAX(0,I82-I18)*I11</f>
-        <v>1073910.09597751</v>
+        <v>1019588.39723244</v>
       </c>
       <c r="J84" s="29" t="n">
         <f aca="false">MAX(0,J82-J18)*J11</f>
-        <v>1114368.70942306</v>
+        <v>1056874.46685809</v>
       </c>
       <c r="K84" s="29" t="n">
         <f aca="false">MAX(0,K82-K18)*K11</f>
-        <v>918425.033015904</v>
+        <v>876295.624949564</v>
       </c>
       <c r="L84" s="29" t="n">
         <f aca="false">MAX(0,L82-L18)*L11</f>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="M84" s="29" t="n">
         <f aca="false">MAX(0,M82-M18)*M11</f>
-        <v>1073910.09597751</v>
+        <v>1019588.39723244</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9388,39 +9388,39 @@
       </c>
       <c r="C85" s="29" t="n">
         <f aca="false">MAX(0,C84-C75)</f>
-        <v>1038217.90060412</v>
+        <v>939478.277826761</v>
       </c>
       <c r="D85" s="29" t="n">
         <f aca="false">MAX(0,D84-D75)</f>
-        <v>1038217.90060412</v>
+        <v>939478.277826761</v>
       </c>
       <c r="E85" s="29" t="n">
         <f aca="false">MAX(0,E84-E75)</f>
-        <v>1035243.55098967</v>
+        <v>936273.873050534</v>
       </c>
       <c r="F85" s="29" t="n">
         <f aca="false">MAX(0,F84-F75)</f>
-        <v>987108.348581655</v>
+        <v>906603.643081576</v>
       </c>
       <c r="G85" s="29" t="n">
         <f aca="false">MAX(0,G84-G75)</f>
-        <v>236691.20171324</v>
+        <v>237434.811732502</v>
       </c>
       <c r="H85" s="29" t="n">
         <f aca="false">MAX(0,H84-H75)</f>
-        <v>685985.562487489</v>
+        <v>674469.294466147</v>
       </c>
       <c r="I85" s="29" t="n">
         <f aca="false">MAX(0,I84-I75)</f>
-        <v>1036730.72579689</v>
+        <v>936273.873050534</v>
       </c>
       <c r="J85" s="29" t="n">
         <f aca="false">MAX(0,J84-J75)</f>
-        <v>1078676.51404967</v>
+        <v>976764.347452405</v>
       </c>
       <c r="K85" s="29" t="n">
         <f aca="false">MAX(0,K84-K75)</f>
-        <v>881245.662835284</v>
+        <v>796185.505543883</v>
       </c>
       <c r="L85" s="29" t="n">
         <f aca="false">MAX(0,L84-L75)</f>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="M85" s="29" t="n">
         <f aca="false">MAX(0,M84-M75)</f>
-        <v>1038217.90060412</v>
+        <v>939478.277826761</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9761,19 +9761,19 @@
       </c>
       <c r="C93" s="29" t="n">
         <f aca="false">IF(C89=1,Invoer!C14,Invoer!C10)+C7*IF(C90=1,Invoer!C15,Invoer!C11)</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="D93" s="29" t="n">
         <f aca="false">IF(D89=1,Invoer!D14,Invoer!D10)+D7*IF(D90=1,Invoer!D15,Invoer!D11)</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="E93" s="29" t="n">
         <f aca="false">IF(E89=1,Invoer!E14,Invoer!E10)+E7*IF(E90=1,Invoer!E15,Invoer!E11)</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="F93" s="29" t="n">
         <f aca="false">IF(F89=1,Invoer!F14,Invoer!F10)+F7*IF(F90=1,Invoer!F15,Invoer!F11)</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="G93" s="29" t="n">
         <f aca="false">IF(G89=1,Invoer!G14,Invoer!G10)+G7*IF(G90=1,Invoer!G15,Invoer!G11)</f>
@@ -9785,23 +9785,23 @@
       </c>
       <c r="I93" s="29" t="n">
         <f aca="false">IF(I89=1,Invoer!I14,Invoer!I10)+I7*IF(I90=1,Invoer!I15,Invoer!I11)</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="J93" s="29" t="n">
         <f aca="false">IF(J89=1,Invoer!J14,Invoer!J10)+J7*IF(J90=1,Invoer!J15,Invoer!J11)</f>
-        <v>155000</v>
+        <v>147000</v>
       </c>
       <c r="K93" s="29" t="n">
         <f aca="false">IF(K89=1,Invoer!K14,Invoer!K10)+K7*IF(K90=1,Invoer!K15,Invoer!K11)</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="L93" s="29" t="n">
         <f aca="false">IF(L89=1,Invoer!L14,Invoer!L10)+L7*IF(L90=1,Invoer!L15,Invoer!L11)</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="M93" s="29" t="n">
         <f aca="false">IF(M89=1,Invoer!M14,Invoer!M10)+M7*IF(M90=1,Invoer!M15,Invoer!M11)</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9915,15 +9915,15 @@
       </c>
       <c r="C96" s="38" t="n">
         <f aca="false">INDEX(T2_Tabel,C95,C78)+(C94-INDEX(T2_Inkomen,C95))/(INDEX(T2_Inkomen,C95+1)-INDEX(T2_Inkomen,C95))*(INDEX(T2_Tabel,C95+1,C78)-INDEX(T2_Tabel,C95,C78))</f>
-        <v>0.351</v>
+        <v>0.375</v>
       </c>
       <c r="D96" s="38" t="n">
         <f aca="false">INDEX(T2_Tabel,D95,D78)+(D94-INDEX(T2_Inkomen,D95))/(INDEX(T2_Inkomen,D95+1)-INDEX(T2_Inkomen,D95))*(INDEX(T2_Tabel,D95+1,D78)-INDEX(T2_Tabel,D95,D78))</f>
-        <v>0.351</v>
+        <v>0.375</v>
       </c>
       <c r="E96" s="38" t="n">
         <f aca="false">INDEX(T2_Tabel,E95,E78)+(E94-INDEX(T2_Inkomen,E95))/(INDEX(T2_Inkomen,E95+1)-INDEX(T2_Inkomen,E95))*(INDEX(T2_Tabel,E95+1,E78)-INDEX(T2_Tabel,E95,E78))</f>
-        <v>0.351</v>
+        <v>0.375</v>
       </c>
       <c r="F96" s="38" t="n">
         <f aca="false">INDEX(T2_Tabel,F95,F78)+(F94-INDEX(T2_Inkomen,F95))/(INDEX(T2_Inkomen,F95+1)-INDEX(T2_Inkomen,F95))*(INDEX(T2_Tabel,F95+1,F78)-INDEX(T2_Tabel,F95,F78))</f>
@@ -9931,31 +9931,31 @@
       </c>
       <c r="G96" s="38" t="n">
         <f aca="false">INDEX(T2_Tabel,G95,G78)+(G94-INDEX(T2_Inkomen,G95))/(INDEX(T2_Inkomen,G95+1)-INDEX(T2_Inkomen,G95))*(INDEX(T2_Tabel,G95+1,G78)-INDEX(T2_Tabel,G95,G78))</f>
-        <v>0.321</v>
+        <v>0.341</v>
       </c>
       <c r="H96" s="38" t="n">
         <f aca="false">INDEX(T2_Tabel,H95,H78)+(H94-INDEX(T2_Inkomen,H95))/(INDEX(T2_Inkomen,H95+1)-INDEX(T2_Inkomen,H95))*(INDEX(T2_Tabel,H95+1,H78)-INDEX(T2_Tabel,H95,H78))</f>
-        <v>0.351</v>
+        <v>0.375</v>
       </c>
       <c r="I96" s="38" t="n">
         <f aca="false">INDEX(T2_Tabel,I95,I78)+(I94-INDEX(T2_Inkomen,I95))/(INDEX(T2_Inkomen,I95+1)-INDEX(T2_Inkomen,I95))*(INDEX(T2_Tabel,I95+1,I78)-INDEX(T2_Tabel,I95,I78))</f>
-        <v>0.351</v>
+        <v>0.375</v>
       </c>
       <c r="J96" s="38" t="n">
         <f aca="false">INDEX(T2_Tabel,J95,J78)+(J94-INDEX(T2_Inkomen,J95))/(INDEX(T2_Inkomen,J95+1)-INDEX(T2_Inkomen,J95))*(INDEX(T2_Tabel,J95+1,J78)-INDEX(T2_Tabel,J95,J78))</f>
-        <v>0.351</v>
+        <v>0.375</v>
       </c>
       <c r="K96" s="38" t="n">
         <f aca="false">INDEX(T2_Tabel,K95,K78)+(K94-INDEX(T2_Inkomen,K95))/(INDEX(T2_Inkomen,K95+1)-INDEX(T2_Inkomen,K95))*(INDEX(T2_Tabel,K95+1,K78)-INDEX(T2_Tabel,K95,K78))</f>
-        <v>0.351</v>
+        <v>0.375</v>
       </c>
       <c r="L96" s="38" t="n">
         <f aca="false">INDEX(T2_Tabel,L95,L78)+(L94-INDEX(T2_Inkomen,L95))/(INDEX(T2_Inkomen,L95+1)-INDEX(T2_Inkomen,L95))*(INDEX(T2_Tabel,L95+1,L78)-INDEX(T2_Tabel,L95,L78))</f>
-        <v>0.351</v>
+        <v>0.375</v>
       </c>
       <c r="M96" s="38" t="n">
         <f aca="false">INDEX(T2_Tabel,M95,M78)+(M94-INDEX(T2_Inkomen,M95))/(INDEX(T2_Inkomen,M95+1)-INDEX(T2_Inkomen,M95))*(INDEX(T2_Tabel,M95+1,M78)-INDEX(T2_Tabel,M95,M78))</f>
-        <v>0.351</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9967,39 +9967,39 @@
       </c>
       <c r="C97" s="29" t="n">
         <f aca="false">MAX(0,MAX(0,C96*C93/12-C18)*C11-C75)</f>
-        <v>1351379.91018651</v>
+        <v>1239891.22559807</v>
       </c>
       <c r="D97" s="29" t="n">
         <f aca="false">MAX(0,MAX(0,D96*D93/12-D18)*D11-D75)</f>
-        <v>1351379.91018651</v>
+        <v>1239891.22559807</v>
       </c>
       <c r="E97" s="29" t="n">
         <f aca="false">MAX(0,MAX(0,E96*E93/12-E18)*E11-E75)</f>
-        <v>1348405.56057206</v>
+        <v>1236686.82082184</v>
       </c>
       <c r="F97" s="29" t="n">
         <f aca="false">MAX(0,MAX(0,F96*F93/12-F18)*F11-F75)</f>
-        <v>1287316.69791949</v>
+        <v>1196504.40960953</v>
       </c>
       <c r="G97" s="29" t="n">
         <f aca="false">MAX(0,MAX(0,G96*G93/12-G18)*G11-G75)</f>
-        <v>336185.290928983</v>
+        <v>329127.117076354</v>
       </c>
       <c r="H97" s="29" t="n">
         <f aca="false">MAX(0,MAX(0,H96*H93/12-H18)*H11-H75)</f>
-        <v>887592.006424652</v>
+        <v>874744.59298035</v>
       </c>
       <c r="I97" s="29" t="n">
         <f aca="false">MAX(0,MAX(0,I96*I93/12-I18)*I11-I75)</f>
-        <v>1349892.73537928</v>
+        <v>1236686.82082184</v>
       </c>
       <c r="J97" s="29" t="n">
         <f aca="false">MAX(0,MAX(0,J96*J93/12-J18)*J11-J75)</f>
-        <v>913952.703535812</v>
+        <v>806650.991485521</v>
       </c>
       <c r="K97" s="29" t="n">
         <f aca="false">MAX(0,MAX(0,K96*K93/12-K18)*K11-K75)</f>
-        <v>1194407.67241768</v>
+        <v>1096598.45331519</v>
       </c>
       <c r="L97" s="29" t="n">
         <f aca="false">MAX(0,MAX(0,L96*L93/12-L18)*L11-L75)</f>
@@ -10007,7 +10007,7 @@
       </c>
       <c r="M97" s="29" t="n">
         <f aca="false">MAX(0,MAX(0,M96*M93/12-M18)*M11-M75)</f>
-        <v>1351379.91018651</v>
+        <v>1239891.22559807</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10121,39 +10121,39 @@
       </c>
       <c r="C100" s="29" t="n">
         <f aca="false">IF(C99=1,C97+C98-C86,C85)</f>
-        <v>1038217.90060412</v>
+        <v>939478.277826761</v>
       </c>
       <c r="D100" s="29" t="n">
         <f aca="false">IF(D99=1,D97+D98-D86,D85)</f>
-        <v>1038217.90060412</v>
+        <v>939478.277826761</v>
       </c>
       <c r="E100" s="29" t="n">
         <f aca="false">IF(E99=1,E97+E98-E86,E85)</f>
-        <v>1035243.55098967</v>
+        <v>936273.873050534</v>
       </c>
       <c r="F100" s="29" t="n">
         <f aca="false">IF(F99=1,F97+F98-F86,F85)</f>
-        <v>987108.348581655</v>
+        <v>906603.643081576</v>
       </c>
       <c r="G100" s="29" t="n">
         <f aca="false">IF(G99=1,G97+G98-G86,G85)</f>
-        <v>236691.20171324</v>
+        <v>237434.811732502</v>
       </c>
       <c r="H100" s="29" t="n">
         <f aca="false">IF(H99=1,H97+H98-H86,H85)</f>
-        <v>685985.562487489</v>
+        <v>674469.294466147</v>
       </c>
       <c r="I100" s="29" t="n">
         <f aca="false">IF(I99=1,I97+I98-I86,I85)</f>
-        <v>1036730.72579689</v>
+        <v>936273.873050534</v>
       </c>
       <c r="J100" s="29" t="n">
         <f aca="false">IF(J99=1,J97+J98-J86,J85)</f>
-        <v>913952.703535812</v>
+        <v>806650.991485521</v>
       </c>
       <c r="K100" s="29" t="n">
         <f aca="false">IF(K99=1,K97+K98-K86,K85)</f>
-        <v>881245.662835284</v>
+        <v>796185.505543883</v>
       </c>
       <c r="L100" s="29" t="n">
         <f aca="false">IF(L99=1,L97+L98-L86,L85)</f>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="M100" s="29" t="n">
         <f aca="false">IF(M99=1,M97+M98-M86,M85)</f>
-        <v>1038217.90060412</v>
+        <v>939478.277826761</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10173,39 +10173,39 @@
       </c>
       <c r="C101" s="35" t="n">
         <f aca="false">MAX(0,C100+C87+C86)</f>
-        <v>1048217.90060412</v>
+        <v>949478.277826761</v>
       </c>
       <c r="D101" s="35" t="n">
         <f aca="false">MAX(0,D100+D87+D86)</f>
-        <v>1048217.90060412</v>
+        <v>949478.277826761</v>
       </c>
       <c r="E101" s="35" t="n">
         <f aca="false">MAX(0,E100+E87+E86)</f>
-        <v>1045243.55098967</v>
+        <v>946273.873050534</v>
       </c>
       <c r="F101" s="35" t="n">
         <f aca="false">MAX(0,F100+F87+F86)</f>
-        <v>997108.348581655</v>
+        <v>916603.643081576</v>
       </c>
       <c r="G101" s="35" t="n">
         <f aca="false">MAX(0,G100+G87+G86)</f>
-        <v>258691.20171324</v>
+        <v>259434.811732502</v>
       </c>
       <c r="H101" s="35" t="n">
         <f aca="false">MAX(0,H100+H87+H86)</f>
-        <v>695985.562487489</v>
+        <v>684469.294466147</v>
       </c>
       <c r="I101" s="35" t="n">
         <f aca="false">MAX(0,I100+I87+I86)</f>
-        <v>1046730.72579689</v>
+        <v>946273.873050534</v>
       </c>
       <c r="J101" s="35" t="n">
         <f aca="false">MAX(0,J100+J87+J86)</f>
-        <v>923952.703535812</v>
+        <v>816650.991485521</v>
       </c>
       <c r="K101" s="35" t="n">
         <f aca="false">MAX(0,K100+K87+K86)</f>
-        <v>881245.662835284</v>
+        <v>796185.505543883</v>
       </c>
       <c r="L101" s="35" t="n">
         <f aca="false">MAX(0,L100+L87+L86)</f>
@@ -10213,7 +10213,7 @@
       </c>
       <c r="M101" s="35" t="n">
         <f aca="false">MAX(0,M100+M87+M86)</f>
-        <v>1048217.90060412</v>
+        <v>949478.277826761</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10242,39 +10242,39 @@
       </c>
       <c r="C103" s="29" t="n">
         <f aca="false">Solver!C58</f>
-        <v>406298.599695031</v>
+        <v>328352.170374638</v>
       </c>
       <c r="D103" s="29" t="n">
         <f aca="false">Solver!D58</f>
-        <v>476458.919906249</v>
+        <v>357403.722328447</v>
       </c>
       <c r="E103" s="29" t="n">
         <f aca="false">Solver!E58</f>
-        <v>385561.679249296</v>
+        <v>270854.422938313</v>
       </c>
       <c r="F103" s="29" t="n">
         <f aca="false">Solver!F58</f>
-        <v>395481.578104395</v>
+        <v>317212.252008869</v>
       </c>
       <c r="G103" s="29" t="n">
         <f aca="false">Solver!G58</f>
-        <v>258691.20171324</v>
+        <v>259434.811732502</v>
       </c>
       <c r="H103" s="29" t="n">
         <f aca="false">Solver!H58</f>
-        <v>695985.562487489</v>
+        <v>684469.294466147</v>
       </c>
       <c r="I103" s="29" t="n">
         <f aca="false">Solver!I58</f>
-        <v>1046730.72579689</v>
+        <v>946273.873050534</v>
       </c>
       <c r="J103" s="29" t="n">
         <f aca="false">Solver!J58</f>
-        <v>446757.21314058</v>
+        <v>365638.240000281</v>
       </c>
       <c r="K103" s="29" t="n">
         <f aca="false">Solver!K58</f>
-        <v>289222.677894566</v>
+        <v>183119.501315332</v>
       </c>
       <c r="L103" s="29" t="n">
         <f aca="false">Solver!L58</f>
@@ -10282,7 +10282,7 @@
       </c>
       <c r="M103" s="29" t="n">
         <f aca="false">Solver!M58</f>
-        <v>406298.599695031</v>
+        <v>328352.170374638</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10294,39 +10294,39 @@
       </c>
       <c r="C104" s="29" t="n">
         <f aca="false">Solver!C112</f>
-        <v>758097.480589537</v>
+        <v>607048.519511873</v>
       </c>
       <c r="D104" s="29" t="n">
         <f aca="false">Solver!D112</f>
-        <v>789620.929488642</v>
+        <v>636100.071465681</v>
       </c>
       <c r="E104" s="29" t="n">
         <f aca="false">Solver!E112</f>
-        <v>674321.454318775</v>
+        <v>571267.370709619</v>
       </c>
       <c r="F104" s="29" t="n">
         <f aca="false">Solver!F112</f>
-        <v>717391.7358281</v>
+        <v>628069.700454507</v>
       </c>
       <c r="G104" s="29" t="n">
         <f aca="false">Solver!G112</f>
-        <v>358185.290928983</v>
+        <v>351127.117076354</v>
       </c>
       <c r="H104" s="29" t="n">
         <f aca="false">Solver!H112</f>
-        <v>897592.006424652</v>
+        <v>884744.59298035</v>
       </c>
       <c r="I104" s="29" t="n">
         <f aca="false">Solver!I112</f>
-        <v>1359892.73537928</v>
+        <v>1246686.82082184</v>
       </c>
       <c r="J104" s="29" t="n">
         <f aca="false">Solver!J112</f>
-        <v>285498.240645907</v>
+        <v>173180.916994343</v>
       </c>
       <c r="K104" s="29" t="n">
         <f aca="false">Solver!K112</f>
-        <v>577982.452964045</v>
+        <v>483532.449086637</v>
       </c>
       <c r="L104" s="29" t="n">
         <f aca="false">Solver!L112</f>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="M104" s="29" t="n">
         <f aca="false">Solver!M112</f>
-        <v>758097.480589537</v>
+        <v>607048.519511873</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10346,39 +10346,39 @@
       </c>
       <c r="C105" s="35" t="n">
         <f aca="false">IF(C47=1,MIN(C103,IF(C92=1,C104,1000000000000000)),C101)</f>
-        <v>406298.599695031</v>
+        <v>328352.170374638</v>
       </c>
       <c r="D105" s="35" t="n">
         <f aca="false">IF(D47=1,MIN(D103,IF(D92=1,D104,1000000000000000)),D101)</f>
-        <v>476458.919906249</v>
+        <v>357403.722328447</v>
       </c>
       <c r="E105" s="35" t="n">
         <f aca="false">IF(E47=1,MIN(E103,IF(E92=1,E104,1000000000000000)),E101)</f>
-        <v>385561.679249296</v>
+        <v>270854.422938313</v>
       </c>
       <c r="F105" s="35" t="n">
         <f aca="false">IF(F47=1,MIN(F103,IF(F92=1,F104,1000000000000000)),F101)</f>
-        <v>395481.578104395</v>
+        <v>317212.252008869</v>
       </c>
       <c r="G105" s="35" t="n">
         <f aca="false">IF(G47=1,MIN(G103,IF(G92=1,G104,1000000000000000)),G101)</f>
-        <v>258691.20171324</v>
+        <v>259434.811732502</v>
       </c>
       <c r="H105" s="35" t="n">
         <f aca="false">IF(H47=1,MIN(H103,IF(H92=1,H104,1000000000000000)),H101)</f>
-        <v>695985.562487489</v>
+        <v>684469.294466147</v>
       </c>
       <c r="I105" s="35" t="n">
         <f aca="false">IF(I47=1,MIN(I103,IF(I92=1,I104,1000000000000000)),I101)</f>
-        <v>1046730.72579689</v>
+        <v>946273.873050534</v>
       </c>
       <c r="J105" s="35" t="n">
         <f aca="false">IF(J47=1,MIN(J103,IF(J92=1,J104,1000000000000000)),J101)</f>
-        <v>285498.240645907</v>
+        <v>173180.916994343</v>
       </c>
       <c r="K105" s="35" t="n">
         <f aca="false">IF(K47=1,MIN(K103,IF(K92=1,K104,1000000000000000)),K101)</f>
-        <v>289222.677894566</v>
+        <v>183119.501315332</v>
       </c>
       <c r="L105" s="35" t="n">
         <f aca="false">IF(L47=1,MIN(L103,IF(L92=1,L104,1000000000000000)),L101)</f>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="M105" s="35" t="n">
         <f aca="false">IF(M47=1,MIN(M103,IF(M92=1,M104,1000000000000000)),M101)</f>
-        <v>406298.599695031</v>
+        <v>328352.170374638</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10398,39 +10398,39 @@
       </c>
       <c r="C106" s="29" t="n">
         <f aca="false">C43+C105</f>
-        <v>1030048.50969503</v>
+        <v>952102.080374638</v>
       </c>
       <c r="D106" s="29" t="n">
         <f aca="false">D43+D105</f>
-        <v>1100208.82990625</v>
+        <v>981153.632328447</v>
       </c>
       <c r="E106" s="29" t="n">
         <f aca="false">E43+E105</f>
-        <v>1009311.5892493</v>
+        <v>894604.332938314</v>
       </c>
       <c r="F106" s="29" t="n">
         <f aca="false">F43+F105</f>
-        <v>1019231.48810439</v>
+        <v>940962.162008869</v>
       </c>
       <c r="G106" s="29" t="n">
         <f aca="false">G43+G105</f>
-        <v>258691.20171324</v>
+        <v>259434.811732502</v>
       </c>
       <c r="H106" s="29" t="n">
         <f aca="false">H43+H105</f>
-        <v>695985.562487489</v>
+        <v>684469.294466147</v>
       </c>
       <c r="I106" s="29" t="n">
         <f aca="false">I43+I105</f>
-        <v>1046730.72579689</v>
+        <v>946273.873050534</v>
       </c>
       <c r="J106" s="29" t="n">
         <f aca="false">J43+J105</f>
-        <v>909248.150645907</v>
+        <v>796930.826994343</v>
       </c>
       <c r="K106" s="29" t="n">
         <f aca="false">K43+K105</f>
-        <v>839222.677894566</v>
+        <v>733119.501315332</v>
       </c>
       <c r="L106" s="29" t="n">
         <f aca="false">L43+L105</f>
@@ -10438,7 +10438,7 @@
       </c>
       <c r="M106" s="29" t="n">
         <f aca="false">M43+M105</f>
-        <v>1030048.50969503</v>
+        <v>952102.080374638</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10450,39 +10450,39 @@
       </c>
       <c r="C107" s="30" t="n">
         <f aca="false">IF(C47=1,(C45+C105*360*C10)/(C46+C105*360),C10)</f>
-        <v>0.0344533312677632</v>
+        <v>0.036487603997058</v>
       </c>
       <c r="D107" s="30" t="n">
         <f aca="false">IF(D47=1,(D45+D105*360*D10)/(D46+D105*360),D10)</f>
-        <v>0.0355263193939105</v>
+        <v>0.0374969289823598</v>
       </c>
       <c r="E107" s="30" t="n">
         <f aca="false">IF(E47=1,(E45+E105*360*E10)/(E46+E105*360),E10)</f>
-        <v>0.0459770682304463</v>
+        <v>0.0490048046834976</v>
       </c>
       <c r="F107" s="30" t="n">
         <f aca="false">IF(F47=1,(F45+F105*360*F10)/(F46+F105*360),F10)</f>
-        <v>0.0384755334064718</v>
+        <v>0.0374621051353357</v>
       </c>
       <c r="G107" s="30" t="n">
         <f aca="false">IF(G47=1,(G45+G105*360*G10)/(G46+G105*360),G10)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="H107" s="30" t="n">
         <f aca="false">IF(H47=1,(H45+H105*360*H10)/(H46+H105*360),H10)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="I107" s="30" t="n">
         <f aca="false">IF(I47=1,(I45+I105*360*I10)/(I46+I105*360),I10)</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="J107" s="30" t="n">
         <f aca="false">IF(J47=1,(J45+J105*360*J10)/(J46+J105*360),J10)</f>
-        <v>0.033672714386364</v>
+        <v>0.0343218642018328</v>
       </c>
       <c r="K107" s="30" t="n">
         <f aca="false">IF(K47=1,(K45+K105*360*K10)/(K46+K105*360),K10)</f>
-        <v>0.0462127127195326</v>
+        <v>0.0491367068438924</v>
       </c>
       <c r="L107" s="30" t="n">
         <f aca="false">IF(L47=1,(L45+L105*360*L10)/(L46+L105*360),L10)</f>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="M107" s="30" t="n">
         <f aca="false">IF(M47=1,(M45+M105*360*M10)/(M46+M105*360),M10)</f>
-        <v>0.0344533312677632</v>
+        <v>0.036487603997058</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10571,39 +10571,39 @@
       </c>
       <c r="C110" s="29" t="n">
         <f aca="false">MIN(C105,C109)</f>
-        <v>376250.09</v>
+        <v>328352.170374638</v>
       </c>
       <c r="D110" s="29" t="n">
         <f aca="false">MIN(D105,D109)</f>
-        <v>476458.919906249</v>
+        <v>357403.722328447</v>
       </c>
       <c r="E110" s="29" t="n">
         <f aca="false">MIN(E105,E109)</f>
-        <v>376250.09</v>
+        <v>270854.422938313</v>
       </c>
       <c r="F110" s="29" t="n">
         <f aca="false">MIN(F105,F109)</f>
-        <v>376250.09</v>
+        <v>317212.252008869</v>
       </c>
       <c r="G110" s="29" t="n">
         <f aca="false">MIN(G105,G109)</f>
-        <v>258691.20171324</v>
+        <v>259434.811732502</v>
       </c>
       <c r="H110" s="29" t="n">
         <f aca="false">MIN(H105,H109)</f>
-        <v>695985.562487489</v>
+        <v>684469.294466147</v>
       </c>
       <c r="I110" s="29" t="n">
         <f aca="false">MIN(I105,I109)</f>
-        <v>1000000</v>
+        <v>946273.873050534</v>
       </c>
       <c r="J110" s="29" t="n">
         <f aca="false">MIN(J105,J109)</f>
-        <v>285498.240645907</v>
+        <v>173180.916994343</v>
       </c>
       <c r="K110" s="29" t="n">
         <f aca="false">MIN(K105,K109)</f>
-        <v>289222.677894566</v>
+        <v>183119.501315332</v>
       </c>
       <c r="L110" s="29" t="n">
         <f aca="false">MIN(L105,L109)</f>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="M110" s="29" t="n">
         <f aca="false">MIN(M105,M109)</f>
-        <v>376250.09</v>
+        <v>328352.170374638</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10623,39 +10623,39 @@
       </c>
       <c r="C111" s="29" t="n">
         <f aca="false">C110-C60</f>
-        <v>52270.09</v>
+        <v>4372.1703746377</v>
       </c>
       <c r="D111" s="29" t="n">
         <f aca="false">D110-D60</f>
-        <v>152478.919906249</v>
+        <v>33423.7223284466</v>
       </c>
       <c r="E111" s="29" t="n">
         <f aca="false">E110-E60</f>
-        <v>52270.09</v>
+        <v>-53125.5770616866</v>
       </c>
       <c r="F111" s="29" t="n">
         <f aca="false">F110-F60</f>
-        <v>52270.09</v>
+        <v>-6767.74799113092</v>
       </c>
       <c r="G111" s="29" t="n">
         <f aca="false">G110-G60</f>
-        <v>258691.20171324</v>
+        <v>259434.811732502</v>
       </c>
       <c r="H111" s="29" t="n">
         <f aca="false">H110-H60</f>
-        <v>695985.562487489</v>
+        <v>684469.294466147</v>
       </c>
       <c r="I111" s="29" t="n">
         <f aca="false">I110-I60</f>
-        <v>52270.0899999999</v>
+        <v>-1456.03694946633</v>
       </c>
       <c r="J111" s="29" t="n">
         <f aca="false">J110-J60</f>
-        <v>-38481.7593540933</v>
+        <v>-150799.083005657</v>
       </c>
       <c r="K111" s="29" t="n">
         <f aca="false">K110-K60</f>
-        <v>106822.677894566</v>
+        <v>719.501315332163</v>
       </c>
       <c r="L111" s="29" t="n">
         <f aca="false">L110-L60</f>
@@ -10663,7 +10663,7 @@
       </c>
       <c r="M111" s="29" t="n">
         <f aca="false">M110-M60</f>
-        <v>52270.09</v>
+        <v>4372.1703746377</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10831,39 +10831,39 @@
       </c>
       <c r="C115" s="29" t="n">
         <f aca="false">MIN(C101,Invoer!C21)</f>
-        <v>1000000</v>
+        <v>949478.277826761</v>
       </c>
       <c r="D115" s="29" t="n">
         <f aca="false">MIN(D101,Invoer!D21)</f>
-        <v>1048217.90060412</v>
+        <v>949478.277826761</v>
       </c>
       <c r="E115" s="29" t="n">
         <f aca="false">MIN(E101,Invoer!E21)</f>
-        <v>1000000</v>
+        <v>946273.873050534</v>
       </c>
       <c r="F115" s="29" t="n">
         <f aca="false">MIN(F101,Invoer!F21)</f>
-        <v>997108.348581655</v>
+        <v>916603.643081576</v>
       </c>
       <c r="G115" s="29" t="n">
         <f aca="false">MIN(G101,Invoer!G21)</f>
-        <v>258691.20171324</v>
+        <v>259434.811732502</v>
       </c>
       <c r="H115" s="29" t="n">
         <f aca="false">MIN(H101,Invoer!H21)</f>
-        <v>695985.562487489</v>
+        <v>684469.294466147</v>
       </c>
       <c r="I115" s="29" t="n">
         <f aca="false">MIN(I101,Invoer!I21)</f>
-        <v>1000000</v>
+        <v>946273.873050534</v>
       </c>
       <c r="J115" s="29" t="n">
         <f aca="false">MIN(J101,Invoer!J21)</f>
-        <v>923952.703535812</v>
+        <v>816650.991485521</v>
       </c>
       <c r="K115" s="29" t="n">
         <f aca="false">MIN(K101,Invoer!K21)</f>
-        <v>881245.662835284</v>
+        <v>796185.505543883</v>
       </c>
       <c r="L115" s="29" t="n">
         <f aca="false">MIN(L101,Invoer!L21)</f>
@@ -10871,7 +10871,7 @@
       </c>
       <c r="M115" s="29" t="n">
         <f aca="false">MIN(M101,Invoer!M21)</f>
-        <v>1000000</v>
+        <v>949478.277826761</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10883,23 +10883,23 @@
       </c>
       <c r="C116" s="29" t="n">
         <f aca="false">MAX(0,C114-C115)+C113</f>
-        <v>212230</v>
+        <v>262751.722173239</v>
       </c>
       <c r="D116" s="29" t="n">
         <f aca="false">MAX(0,D114-D115)+D113</f>
-        <v>164012.099395884</v>
+        <v>262751.722173239</v>
       </c>
       <c r="E116" s="29" t="n">
         <f aca="false">MAX(0,E114-E115)+E113</f>
-        <v>212230</v>
+        <v>265956.126949466</v>
       </c>
       <c r="F116" s="29" t="n">
         <f aca="false">MAX(0,F114-F115)+F113</f>
-        <v>215121.651418345</v>
+        <v>295626.356918424</v>
       </c>
       <c r="G116" s="29" t="n">
         <f aca="false">MAX(0,G114-G115)+G113</f>
-        <v>114008.79828676</v>
+        <v>113265.188267498</v>
       </c>
       <c r="H116" s="29" t="n">
         <f aca="false">MAX(0,H114-H115)+H113</f>
@@ -10907,15 +10907,15 @@
       </c>
       <c r="I116" s="29" t="n">
         <f aca="false">MAX(0,I114-I115)+I113</f>
-        <v>212230</v>
+        <v>265956.126949466</v>
       </c>
       <c r="J116" s="29" t="n">
         <f aca="false">MAX(0,J114-J115)+J113</f>
-        <v>288277.296464188</v>
+        <v>395579.008514479</v>
       </c>
       <c r="K116" s="29" t="n">
         <f aca="false">MAX(0,K114-K115)+K113</f>
-        <v>156154.337164716</v>
+        <v>241214.494456117</v>
       </c>
       <c r="L116" s="29" t="n">
         <f aca="false">MAX(0,L114-L115)+L113</f>
@@ -10923,7 +10923,7 @@
       </c>
       <c r="M116" s="29" t="n">
         <f aca="false">MAX(0,M114-M115)+M113</f>
-        <v>212230</v>
+        <v>262751.722173239</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10935,39 +10935,39 @@
       </c>
       <c r="C117" s="35" t="n">
         <f aca="false">IF(C6=1,C43+C110,C115)</f>
-        <v>1000000</v>
+        <v>952102.080374638</v>
       </c>
       <c r="D117" s="35" t="n">
         <f aca="false">IF(D6=1,D43+D110,D115)</f>
-        <v>1100208.82990625</v>
+        <v>981153.632328447</v>
       </c>
       <c r="E117" s="35" t="n">
         <f aca="false">IF(E6=1,E43+E110,E115)</f>
-        <v>1000000</v>
+        <v>894604.332938314</v>
       </c>
       <c r="F117" s="35" t="n">
         <f aca="false">IF(F6=1,F43+F110,F115)</f>
-        <v>1000000</v>
+        <v>940962.162008869</v>
       </c>
       <c r="G117" s="35" t="n">
         <f aca="false">IF(G6=1,G43+G110,G115)</f>
-        <v>258691.20171324</v>
+        <v>259434.811732502</v>
       </c>
       <c r="H117" s="35" t="n">
         <f aca="false">IF(H6=1,H43+H110,H115)</f>
-        <v>695985.562487489</v>
+        <v>684469.294466147</v>
       </c>
       <c r="I117" s="35" t="n">
         <f aca="false">IF(I6=1,I43+I110,I115)</f>
-        <v>1000000</v>
+        <v>946273.873050534</v>
       </c>
       <c r="J117" s="35" t="n">
         <f aca="false">IF(J6=1,J43+J110,J115)</f>
-        <v>909248.150645907</v>
+        <v>796930.826994343</v>
       </c>
       <c r="K117" s="35" t="n">
         <f aca="false">IF(K6=1,K43+K110,K115)</f>
-        <v>839222.677894566</v>
+        <v>733119.501315332</v>
       </c>
       <c r="L117" s="35" t="n">
         <f aca="false">IF(L6=1,L43+L110,L115)</f>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="M117" s="35" t="n">
         <f aca="false">IF(M6=1,M43+M110,M115)</f>
-        <v>1000000</v>
+        <v>952102.080374638</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10987,39 +10987,39 @@
       </c>
       <c r="C118" s="35" t="n">
         <f aca="false">IF(C6=1,C110,C115)</f>
-        <v>376250.09</v>
+        <v>328352.170374638</v>
       </c>
       <c r="D118" s="35" t="n">
         <f aca="false">IF(D6=1,D110,D115)</f>
-        <v>476458.919906249</v>
+        <v>357403.722328447</v>
       </c>
       <c r="E118" s="35" t="n">
         <f aca="false">IF(E6=1,E110,E115)</f>
-        <v>376250.09</v>
+        <v>270854.422938313</v>
       </c>
       <c r="F118" s="35" t="n">
         <f aca="false">IF(F6=1,F110,F115)</f>
-        <v>376250.09</v>
+        <v>317212.252008869</v>
       </c>
       <c r="G118" s="35" t="n">
         <f aca="false">IF(G6=1,G110,G115)</f>
-        <v>258691.20171324</v>
+        <v>259434.811732502</v>
       </c>
       <c r="H118" s="35" t="n">
         <f aca="false">IF(H6=1,H110,H115)</f>
-        <v>695985.562487489</v>
+        <v>684469.294466147</v>
       </c>
       <c r="I118" s="35" t="n">
         <f aca="false">IF(I6=1,I110,I115)</f>
-        <v>1000000</v>
+        <v>946273.873050534</v>
       </c>
       <c r="J118" s="35" t="n">
         <f aca="false">IF(J6=1,J110,J115)</f>
-        <v>285498.240645907</v>
+        <v>173180.916994343</v>
       </c>
       <c r="K118" s="35" t="n">
         <f aca="false">IF(K6=1,K110,K115)</f>
-        <v>289222.677894566</v>
+        <v>183119.501315332</v>
       </c>
       <c r="L118" s="35" t="n">
         <f aca="false">IF(L6=1,L110,L115)</f>
@@ -11027,7 +11027,7 @@
       </c>
       <c r="M118" s="35" t="n">
         <f aca="false">IF(M6=1,M110,M115)</f>
-        <v>376250.09</v>
+        <v>328352.170374638</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11091,39 +11091,39 @@
       </c>
       <c r="C120" s="35" t="n">
         <f aca="false">C118-C119</f>
-        <v>52270.09</v>
+        <v>4372.1703746377</v>
       </c>
       <c r="D120" s="35" t="n">
         <f aca="false">D118-D119</f>
-        <v>152478.919906249</v>
+        <v>33423.7223284466</v>
       </c>
       <c r="E120" s="35" t="n">
         <f aca="false">E118-E119</f>
-        <v>52270.09</v>
+        <v>-53125.5770616866</v>
       </c>
       <c r="F120" s="35" t="n">
         <f aca="false">F118-F119</f>
-        <v>52270.09</v>
+        <v>-6767.74799113092</v>
       </c>
       <c r="G120" s="35" t="n">
         <f aca="false">G118-G119</f>
-        <v>-114008.79828676</v>
+        <v>-113265.188267498</v>
       </c>
       <c r="H120" s="35" t="n">
         <f aca="false">H118-H119</f>
-        <v>101035.562487489</v>
+        <v>89519.2944661467</v>
       </c>
       <c r="I120" s="35" t="n">
         <f aca="false">I118-I119</f>
-        <v>52270.0899999999</v>
+        <v>-1456.03694946633</v>
       </c>
       <c r="J120" s="35" t="n">
         <f aca="false">J118-J119</f>
-        <v>-38481.7593540933</v>
+        <v>-150799.083005657</v>
       </c>
       <c r="K120" s="35" t="n">
         <f aca="false">K118-K119</f>
-        <v>106822.677894566</v>
+        <v>719.501315332163</v>
       </c>
       <c r="L120" s="35" t="n">
         <f aca="false">L118-L119</f>
@@ -11131,7 +11131,7 @@
       </c>
       <c r="M120" s="35" t="n">
         <f aca="false">M118-M119</f>
-        <v>52270.09</v>
+        <v>4372.1703746377</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11151,15 +11151,15 @@
       </c>
       <c r="E121" s="35" t="n">
         <f aca="false">IF(E6=1,MAX(0,-E111),E116)</f>
-        <v>0</v>
+        <v>53125.5770616866</v>
       </c>
       <c r="F121" s="35" t="n">
         <f aca="false">IF(F6=1,MAX(0,-F111),F116)</f>
-        <v>0</v>
+        <v>6767.74799113092</v>
       </c>
       <c r="G121" s="35" t="n">
         <f aca="false">IF(G6=1,MAX(0,-G111),G116)</f>
-        <v>114008.79828676</v>
+        <v>113265.188267498</v>
       </c>
       <c r="H121" s="35" t="n">
         <f aca="false">IF(H6=1,MAX(0,-H111),H116)</f>
@@ -11167,11 +11167,11 @@
       </c>
       <c r="I121" s="35" t="n">
         <f aca="false">IF(I6=1,MAX(0,-I111),I116)</f>
-        <v>0</v>
+        <v>1456.03694946633</v>
       </c>
       <c r="J121" s="35" t="n">
         <f aca="false">IF(J6=1,MAX(0,-J111),J116)</f>
-        <v>38481.7593540933</v>
+        <v>150799.083005657</v>
       </c>
       <c r="K121" s="35" t="n">
         <f aca="false">IF(K6=1,MAX(0,-K111),K116)</f>
@@ -11201,11 +11201,11 @@
       </c>
       <c r="E122" s="39" t="n">
         <f aca="false">IF(E6=1,IF(E111&gt;=0,1,0),IF(E116&lt;=0,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F122" s="39" t="n">
         <f aca="false">IF(F6=1,IF(F111&gt;=0,1,0),IF(F116&lt;=0,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122" s="39" t="n">
         <f aca="false">IF(G6=1,IF(G111&gt;=0,1,0),IF(G116&lt;=0,1,0))</f>
@@ -11217,7 +11217,7 @@
       </c>
       <c r="I122" s="39" t="n">
         <f aca="false">IF(I6=1,IF(I111&gt;=0,1,0),IF(I116&lt;=0,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J122" s="39" t="n">
         <f aca="false">IF(J6=1,IF(J111&gt;=0,1,0),IF(J116&lt;=0,1,0))</f>
@@ -11245,19 +11245,19 @@
       </c>
       <c r="C123" s="29" t="n">
         <f aca="false">IF(C6=1,Invoer!C64+C50+C43+C110-C51-Invoer!C20-C57,"n.v.t.")</f>
-        <v>52270.0899999999</v>
+        <v>4372.1703746377</v>
       </c>
       <c r="D123" s="29" t="n">
         <f aca="false">IF(D6=1,Invoer!D64+D50+D43+D110-D51-Invoer!D20-D57,"n.v.t.")</f>
-        <v>152478.919906249</v>
+        <v>33423.7223284466</v>
       </c>
       <c r="E123" s="29" t="n">
         <f aca="false">IF(E6=1,Invoer!E64+E50+E43+E110-E51-Invoer!E20-E57,"n.v.t.")</f>
-        <v>52270.0899999999</v>
+        <v>-53125.5770616867</v>
       </c>
       <c r="F123" s="29" t="n">
         <f aca="false">IF(F6=1,Invoer!F64+F50+F43+F110-F51-Invoer!F20-F57,"n.v.t.")</f>
-        <v>52270.0899999999</v>
+        <v>-6767.74799113092</v>
       </c>
       <c r="G123" s="29" t="str">
         <f aca="false">IF(G6=1,Invoer!G64+G50+G43+G110-G51-Invoer!G20-G57,"n.v.t.")</f>
@@ -11269,15 +11269,15 @@
       </c>
       <c r="I123" s="29" t="n">
         <f aca="false">IF(I6=1,Invoer!I64+I50+I43+I110-I51-Invoer!I20-I57,"n.v.t.")</f>
-        <v>52270.0899999999</v>
+        <v>-1456.03694946622</v>
       </c>
       <c r="J123" s="29" t="n">
         <f aca="false">IF(J6=1,Invoer!J64+J50+J43+J110-J51-Invoer!J20-J57,"n.v.t.")</f>
-        <v>-38481.7593540933</v>
+        <v>-150799.083005657</v>
       </c>
       <c r="K123" s="29" t="n">
         <f aca="false">IF(K6=1,Invoer!K64+K50+K43+K110-K51-Invoer!K20-K57,"n.v.t.")</f>
-        <v>106822.677894566</v>
+        <v>719.501315332251</v>
       </c>
       <c r="L123" s="29" t="n">
         <f aca="false">IF(L6=1,Invoer!L64+L50+L43+L110-L51-Invoer!L20-L57,"n.v.t.")</f>
@@ -11285,7 +11285,7 @@
       </c>
       <c r="M123" s="29" t="n">
         <f aca="false">IF(M6=1,Invoer!M64+M50+M43+M110-M51-Invoer!M20-M57,"n.v.t.")</f>
-        <v>52270.0899999999</v>
+        <v>4372.1703746377</v>
       </c>
     </row>
   </sheetData>
@@ -11401,19 +11401,19 @@
       </c>
       <c r="C6" s="29" t="n">
         <f aca="false">Berekening!C9</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="D6" s="29" t="n">
         <f aca="false">Berekening!D9</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="E6" s="29" t="n">
         <f aca="false">Berekening!E9</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="F6" s="29" t="n">
         <f aca="false">Berekening!F9</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="G6" s="29" t="n">
         <f aca="false">Berekening!G9</f>
@@ -11425,23 +11425,23 @@
       </c>
       <c r="I6" s="29" t="n">
         <f aca="false">Berekening!I9</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="J6" s="29" t="n">
         <f aca="false">Berekening!J9</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="K6" s="29" t="n">
         <f aca="false">Berekening!K9</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="L6" s="29" t="n">
         <f aca="false">Berekening!L9</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="M6" s="29" t="n">
         <f aca="false">Berekening!M9</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11557,39 +11557,39 @@
       </c>
       <c r="C9" s="29" t="n">
         <f aca="false">MAX(0,(C8*C6/12-Berekening!C18-Berekening!C44)*Berekening!C11-Berekening!C75+C7)</f>
-        <v>233449.438561892</v>
+        <v>140141.648879362</v>
       </c>
       <c r="D9" s="29" t="n">
         <f aca="false">MAX(0,(D8*D6/12-Berekening!D18-Berekening!D44)*Berekening!D11-Berekening!D75+D7)</f>
-        <v>264972.887460997</v>
+        <v>169193.200833171</v>
       </c>
       <c r="E9" s="29" t="n">
         <f aca="false">MAX(0,(E8*E6/12-Berekening!E18-Berekening!E44)*Berekening!E11-Berekening!E75+E7)</f>
-        <v>100868.943265303</v>
+        <v>17494.105540827</v>
       </c>
       <c r="F9" s="29" t="n">
         <f aca="false">MAX(0,(F8*F6/12-Berekening!F18-Berekening!F44)*Berekening!F11-Berekening!F75+F7)</f>
-        <v>207399.238760208</v>
+        <v>135587.675388946</v>
       </c>
       <c r="G9" s="29" t="n">
         <f aca="false">MAX(0,(G8*G6/12-Berekening!G18-Berekening!G44)*Berekening!G11-Berekening!G75+G7)</f>
-        <v>207373.197801963</v>
+        <v>192837.242588019</v>
       </c>
       <c r="H9" s="29" t="n">
         <f aca="false">MAX(0,(H8*H6/12-Berekening!H18-Berekening!H44)*Berekening!H11-Berekening!H75+H7)</f>
-        <v>559835.756192262</v>
+        <v>515562.416201156</v>
       </c>
       <c r="I9" s="29" t="n">
         <f aca="false">MAX(0,(I8*I6/12-Berekening!I18-Berekening!I44)*Berekening!I11-Berekening!I75+I7)</f>
-        <v>835244.693351639</v>
+        <v>692913.555653047</v>
       </c>
       <c r="J9" s="29" t="n">
         <f aca="false">MAX(0,(J8*J6/12-Berekening!J18-Berekening!J44)*Berekening!J11-Berekening!J75+J7)</f>
-        <v>273908.052007441</v>
+        <v>177427.718505005</v>
       </c>
       <c r="K9" s="29" t="n">
         <f aca="false">MAX(0,(K8*K6/12-Berekening!K18-Berekening!K44)*Berekening!K11-Berekening!K75+K7)</f>
-        <v>4529.94191057242</v>
+        <v>0</v>
       </c>
       <c r="L9" s="29" t="n">
         <f aca="false">MAX(0,(L8*L6/12-Berekening!L18-Berekening!L44)*Berekening!L11-Berekening!L75+L7)</f>
@@ -11597,7 +11597,7 @@
       </c>
       <c r="M9" s="29" t="n">
         <f aca="false">MAX(0,(M8*M6/12-Berekening!M18-Berekening!M44)*Berekening!M11-Berekening!M75+M7)</f>
-        <v>233449.438561892</v>
+        <v>140141.648879362</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11661,15 +11661,15 @@
       </c>
       <c r="C11" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,1)+0.000005)&lt;Berekening!C10,(Berekening!C45-(INDEX(T1_Rente,1)+0.000005)*Berekening!C46)/(360*((INDEX(T1_Rente,1)+0.000005)-Berekening!C10)),1000000000000))</f>
-        <v>-355564.478960192</v>
+        <v>-278643.491193291</v>
       </c>
       <c r="D11" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,1)+0.000005)&lt;Berekening!D10,(Berekening!D45-(INDEX(T1_Rente,1)+0.000005)*Berekening!D46)/(360*((INDEX(T1_Rente,1)+0.000005)-Berekening!D10)),1000000000000))</f>
-        <v>-426831.210060012</v>
+        <v>-334492.744801693</v>
       </c>
       <c r="E11" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,1)+0.000005)&lt;Berekening!E10,(Berekening!E45-(INDEX(T1_Rente,1)+0.000005)*Berekening!E46)/(360*((INDEX(T1_Rente,1)+0.000005)-Berekening!E10)),1000000000000))</f>
-        <v>-802033.052874975</v>
+        <v>-628525.353710926</v>
       </c>
       <c r="F11" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,1)+0.000005)&lt;Berekening!F10,(Berekening!F45-(INDEX(T1_Rente,1)+0.000005)*Berekening!F46)/(360*((INDEX(T1_Rente,1)+0.000005)-Berekening!F10)),1000000000000))</f>
@@ -11689,19 +11689,19 @@
       </c>
       <c r="J11" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,1)+0.000005)&lt;Berekening!J10,(Berekening!J45-(INDEX(T1_Rente,1)+0.000005)*Berekening!J46)/(360*((INDEX(T1_Rente,1)+0.000005)-Berekening!J10)),1000000000000))</f>
-        <v>-355564.478960192</v>
+        <v>-278643.491193291</v>
       </c>
       <c r="K11" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,1)+0.000005)&lt;Berekening!K10,(Berekening!K45-(INDEX(T1_Rente,1)+0.000005)*Berekening!K46)/(360*((INDEX(T1_Rente,1)+0.000005)-Berekening!K10)),1000000000000))</f>
-        <v>-664260.185370407</v>
+        <v>-520557.558656007</v>
       </c>
       <c r="L11" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,1)+0.000005)&lt;Berekening!L10,(Berekening!L45-(INDEX(T1_Rente,1)+0.000005)*Berekening!L46)/(360*((INDEX(T1_Rente,1)+0.000005)-Berekening!L10)),1000000000000))</f>
-        <v>-355564.478960192</v>
+        <v>-278643.491193291</v>
       </c>
       <c r="M11" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,1)+0.000005)&lt;Berekening!M10,(Berekening!M45-(INDEX(T1_Rente,1)+0.000005)*Berekening!M46)/(360*((INDEX(T1_Rente,1)+0.000005)-Berekening!M10)),1000000000000))</f>
-        <v>-355564.478960192</v>
+        <v>-278643.491193291</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11817,39 +11817,39 @@
       </c>
       <c r="C14" s="29" t="n">
         <f aca="false">MAX(0,(C13*C6/12-Berekening!C18-Berekening!C44)*Berekening!C11-Berekening!C75+C7)</f>
-        <v>278186.868502234</v>
+        <v>179955.413041824</v>
       </c>
       <c r="D14" s="29" t="n">
         <f aca="false">MAX(0,(D13*D6/12-Berekening!D18-Berekening!D44)*Berekening!D11-Berekening!D75+D7)</f>
-        <v>309710.317401339</v>
+        <v>209006.964995633</v>
       </c>
       <c r="E14" s="29" t="n">
         <f aca="false">MAX(0,(E13*E6/12-Berekening!E18-Berekening!E44)*Berekening!E11-Berekening!E75+E7)</f>
-        <v>145606.373205645</v>
+        <v>57307.8697032892</v>
       </c>
       <c r="F14" s="29" t="n">
         <f aca="false">MAX(0,(F13*F6/12-Berekening!F18-Berekening!F44)*Berekening!F11-Berekening!F75+F7)</f>
-        <v>247185.887467632</v>
+        <v>174008.258904699</v>
       </c>
       <c r="G14" s="29" t="n">
         <f aca="false">MAX(0,(G13*G6/12-Berekening!G18-Berekening!G44)*Berekening!G11-Berekening!G75+G7)</f>
-        <v>217846.259824672</v>
+        <v>202489.064203162</v>
       </c>
       <c r="H14" s="29" t="n">
         <f aca="false">MAX(0,(H13*H6/12-Berekening!H18-Berekening!H44)*Berekening!H11-Berekening!H75+H7)</f>
-        <v>588636.676754714</v>
+        <v>542104.925642797</v>
       </c>
       <c r="I14" s="29" t="n">
         <f aca="false">MAX(0,(I13*I6/12-Berekening!I18-Berekening!I44)*Berekening!I11-Berekening!I75+I7)</f>
-        <v>879982.123291981</v>
+        <v>732727.31981551</v>
       </c>
       <c r="J14" s="29" t="n">
         <f aca="false">MAX(0,(J13*J6/12-Berekening!J18-Berekening!J44)*Berekening!J11-Berekening!J75+J7)</f>
-        <v>318645.481947783</v>
+        <v>217241.482667468</v>
       </c>
       <c r="K14" s="29" t="n">
         <f aca="false">MAX(0,(K13*K6/12-Berekening!K18-Berekening!K44)*Berekening!K11-Berekening!K75+K7)</f>
-        <v>49267.3718509142</v>
+        <v>0</v>
       </c>
       <c r="L14" s="29" t="n">
         <f aca="false">MAX(0,(L13*L6/12-Berekening!L18-Berekening!L44)*Berekening!L11-Berekening!L75+L7)</f>
@@ -11857,7 +11857,7 @@
       </c>
       <c r="M14" s="29" t="n">
         <f aca="false">MAX(0,(M13*M6/12-Berekening!M18-Berekening!M44)*Berekening!M11-Berekening!M75+M7)</f>
-        <v>278186.868502234</v>
+        <v>179955.413041824</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11921,15 +11921,15 @@
       </c>
       <c r="C16" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,2)+0.000005)&lt;Berekening!C10,(Berekening!C45-(INDEX(T1_Rente,2)+0.000005)*Berekening!C46)/(360*((INDEX(T1_Rente,2)+0.000005)-Berekening!C10)),1000000000000),IF((INDEX(T1_Rente,2)-0.005+0.000005)&gt;Berekening!C10,(Berekening!C45-(INDEX(T1_Rente,2)-0.005+0.000005)*Berekening!C46)/(360*((INDEX(T1_Rente,2)-0.005+0.000005)-Berekening!C10)),1000000000000))</f>
-        <v>-301230.012250229</v>
+        <v>-223948.469787817</v>
       </c>
       <c r="D16" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,2)+0.000005)&lt;Berekening!D10,(Berekening!D45-(INDEX(T1_Rente,2)+0.000005)*Berekening!D46)/(360*((INDEX(T1_Rente,2)+0.000005)-Berekening!D10)),1000000000000),IF((INDEX(T1_Rente,2)-0.005+0.000005)&gt;Berekening!D10,(Berekening!D45-(INDEX(T1_Rente,2)-0.005+0.000005)*Berekening!D46)/(360*((INDEX(T1_Rente,2)-0.005+0.000005)-Berekening!D10)),1000000000000))</f>
-        <v>-377589.224578645</v>
+        <v>-280717.477057074</v>
       </c>
       <c r="E16" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,2)+0.000005)&lt;Berekening!E10,(Berekening!E45-(INDEX(T1_Rente,2)+0.000005)*Berekening!E46)/(360*((INDEX(T1_Rente,2)+0.000005)-Berekening!E10)),1000000000000),IF((INDEX(T1_Rente,2)-0.005+0.000005)&gt;Berekening!E10,(Berekening!E45-(INDEX(T1_Rente,2)-0.005+0.000005)*Berekening!E46)/(360*((INDEX(T1_Rente,2)-0.005+0.000005)-Berekening!E10)),1000000000000))</f>
-        <v>-859343.640907393</v>
+        <v>-638876.226062217</v>
       </c>
       <c r="F16" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,2)+0.000005)&lt;Berekening!F10,(Berekening!F45-(INDEX(T1_Rente,2)+0.000005)*Berekening!F46)/(360*((INDEX(T1_Rente,2)+0.000005)-Berekening!F10)),1000000000000),IF((INDEX(T1_Rente,2)-0.005+0.000005)&gt;Berekening!F10,(Berekening!F45-(INDEX(T1_Rente,2)-0.005+0.000005)*Berekening!F46)/(360*((INDEX(T1_Rente,2)-0.005+0.000005)-Berekening!F10)),1000000000000))</f>
@@ -11949,19 +11949,19 @@
       </c>
       <c r="J16" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,2)+0.000005)&lt;Berekening!J10,(Berekening!J45-(INDEX(T1_Rente,2)+0.000005)*Berekening!J46)/(360*((INDEX(T1_Rente,2)+0.000005)-Berekening!J10)),1000000000000),IF((INDEX(T1_Rente,2)-0.005+0.000005)&gt;Berekening!J10,(Berekening!J45-(INDEX(T1_Rente,2)-0.005+0.000005)*Berekening!J46)/(360*((INDEX(T1_Rente,2)-0.005+0.000005)-Berekening!J10)),1000000000000))</f>
-        <v>-301230.012250229</v>
+        <v>-223948.469787817</v>
       </c>
       <c r="K16" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,2)+0.000005)&lt;Berekening!K10,(Berekening!K45-(INDEX(T1_Rente,2)+0.000005)*Berekening!K46)/(360*((INDEX(T1_Rente,2)+0.000005)-Berekening!K10)),1000000000000),IF((INDEX(T1_Rente,2)-0.005+0.000005)&gt;Berekening!K10,(Berekening!K45-(INDEX(T1_Rente,2)-0.005+0.000005)*Berekening!K46)/(360*((INDEX(T1_Rente,2)-0.005+0.000005)-Berekening!K10)),1000000000000))</f>
-        <v>-711725.987052319</v>
+        <v>-529130.362934044</v>
       </c>
       <c r="L16" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,2)+0.000005)&lt;Berekening!L10,(Berekening!L45-(INDEX(T1_Rente,2)+0.000005)*Berekening!L46)/(360*((INDEX(T1_Rente,2)+0.000005)-Berekening!L10)),1000000000000),IF((INDEX(T1_Rente,2)-0.005+0.000005)&gt;Berekening!L10,(Berekening!L45-(INDEX(T1_Rente,2)-0.005+0.000005)*Berekening!L46)/(360*((INDEX(T1_Rente,2)-0.005+0.000005)-Berekening!L10)),1000000000000))</f>
-        <v>-301230.012250229</v>
+        <v>-223948.469787817</v>
       </c>
       <c r="M16" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,2)+0.000005)&lt;Berekening!M10,(Berekening!M45-(INDEX(T1_Rente,2)+0.000005)*Berekening!M46)/(360*((INDEX(T1_Rente,2)+0.000005)-Berekening!M10)),1000000000000),IF((INDEX(T1_Rente,2)-0.005+0.000005)&gt;Berekening!M10,(Berekening!M45-(INDEX(T1_Rente,2)-0.005+0.000005)*Berekening!M46)/(360*((INDEX(T1_Rente,2)-0.005+0.000005)-Berekening!M10)),1000000000000))</f>
-        <v>-301230.012250229</v>
+        <v>-223948.469787817</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12077,39 +12077,39 @@
       </c>
       <c r="C19" s="29" t="n">
         <f aca="false">MAX(0,(C18*C6/12-Berekening!C18-Berekening!C44)*Berekening!C11-Berekening!C75+C7)</f>
-        <v>322924.298442576</v>
+        <v>219769.177204286</v>
       </c>
       <c r="D19" s="29" t="n">
         <f aca="false">MAX(0,(D18*D6/12-Berekening!D18-Berekening!D44)*Berekening!D11-Berekening!D75+D7)</f>
-        <v>354447.747341681</v>
+        <v>248820.729158095</v>
       </c>
       <c r="E19" s="29" t="n">
         <f aca="false">MAX(0,(E18*E6/12-Berekening!E18-Berekening!E44)*Berekening!E11-Berekening!E75+E7)</f>
-        <v>190343.803145987</v>
+        <v>97121.6338657513</v>
       </c>
       <c r="F19" s="29" t="n">
         <f aca="false">MAX(0,(F18*F6/12-Berekening!F18-Berekening!F44)*Berekening!F11-Berekening!F75+F7)</f>
-        <v>286972.536175056</v>
+        <v>212428.842420452</v>
       </c>
       <c r="G19" s="29" t="n">
         <f aca="false">MAX(0,(G18*G6/12-Berekening!G18-Berekening!G44)*Berekening!G11-Berekening!G75+G7)</f>
-        <v>228319.321847382</v>
+        <v>212140.885818304</v>
       </c>
       <c r="H19" s="29" t="n">
         <f aca="false">MAX(0,(H18*H6/12-Berekening!H18-Berekening!H44)*Berekening!H11-Berekening!H75+H7)</f>
-        <v>617437.597317166</v>
+        <v>568647.435084439</v>
       </c>
       <c r="I19" s="29" t="n">
         <f aca="false">MAX(0,(I18*I6/12-Berekening!I18-Berekening!I44)*Berekening!I11-Berekening!I75+I7)</f>
-        <v>924719.553232323</v>
+        <v>772541.083977972</v>
       </c>
       <c r="J19" s="29" t="n">
         <f aca="false">MAX(0,(J18*J6/12-Berekening!J18-Berekening!J44)*Berekening!J11-Berekening!J75+J7)</f>
-        <v>363382.911888125</v>
+        <v>257055.24682993</v>
       </c>
       <c r="K19" s="29" t="n">
         <f aca="false">MAX(0,(K18*K6/12-Berekening!K18-Berekening!K44)*Berekening!K11-Berekening!K75+K7)</f>
-        <v>94004.8017912562</v>
+        <v>9386.71224277015</v>
       </c>
       <c r="L19" s="29" t="n">
         <f aca="false">MAX(0,(L18*L6/12-Berekening!L18-Berekening!L44)*Berekening!L11-Berekening!L75+L7)</f>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="M19" s="29" t="n">
         <f aca="false">MAX(0,(M18*M6/12-Berekening!M18-Berekening!M44)*Berekening!M11-Berekening!M75+M7)</f>
-        <v>322924.298442576</v>
+        <v>219769.177204286</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12181,15 +12181,15 @@
       </c>
       <c r="C21" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,3)+0.000005)&lt;Berekening!C10,(Berekening!C45-(INDEX(T1_Rente,3)+0.000005)*Berekening!C46)/(360*((INDEX(T1_Rente,3)+0.000005)-Berekening!C10)),1000000000000),IF((INDEX(T1_Rente,3)-0.005+0.000005)&gt;Berekening!C10,(Berekening!C45-(INDEX(T1_Rente,3)-0.005+0.000005)*Berekening!C46)/(360*((INDEX(T1_Rente,3)-0.005+0.000005)-Berekening!C10)),1000000000000))</f>
-        <v>-210660.489381572</v>
+        <v>-144272.849430311</v>
       </c>
       <c r="D21" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,3)+0.000005)&lt;Berekening!D10,(Berekening!D45-(INDEX(T1_Rente,3)+0.000005)*Berekening!D46)/(360*((INDEX(T1_Rente,3)+0.000005)-Berekening!D10)),1000000000000),IF((INDEX(T1_Rente,3)-0.005+0.000005)&gt;Berekening!D10,(Berekening!D45-(INDEX(T1_Rente,3)-0.005+0.000005)*Berekening!D46)/(360*((INDEX(T1_Rente,3)-0.005+0.000005)-Berekening!D10)),1000000000000))</f>
-        <v>-295508.302464155</v>
+        <v>-202381.685108472</v>
       </c>
       <c r="E21" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,3)+0.000005)&lt;Berekening!E10,(Berekening!E45-(INDEX(T1_Rente,3)+0.000005)*Berekening!E46)/(360*((INDEX(T1_Rente,3)+0.000005)-Berekening!E10)),1000000000000),IF((INDEX(T1_Rente,3)-0.005+0.000005)&gt;Berekening!E10,(Berekening!E45-(INDEX(T1_Rente,3)-0.005+0.000005)*Berekening!E46)/(360*((INDEX(T1_Rente,3)-0.005+0.000005)-Berekening!E10)),1000000000000))</f>
-        <v>-954874.027560965</v>
+        <v>-653954.603483748</v>
       </c>
       <c r="F21" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,3)+0.000005)&lt;Berekening!F10,(Berekening!F45-(INDEX(T1_Rente,3)+0.000005)*Berekening!F46)/(360*((INDEX(T1_Rente,3)+0.000005)-Berekening!F10)),1000000000000),IF((INDEX(T1_Rente,3)-0.005+0.000005)&gt;Berekening!F10,(Berekening!F45-(INDEX(T1_Rente,3)-0.005+0.000005)*Berekening!F46)/(360*((INDEX(T1_Rente,3)-0.005+0.000005)-Berekening!F10)),1000000000000))</f>
@@ -12209,19 +12209,19 @@
       </c>
       <c r="J21" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,3)+0.000005)&lt;Berekening!J10,(Berekening!J45-(INDEX(T1_Rente,3)+0.000005)*Berekening!J46)/(360*((INDEX(T1_Rente,3)+0.000005)-Berekening!J10)),1000000000000),IF((INDEX(T1_Rente,3)-0.005+0.000005)&gt;Berekening!J10,(Berekening!J45-(INDEX(T1_Rente,3)-0.005+0.000005)*Berekening!J46)/(360*((INDEX(T1_Rente,3)-0.005+0.000005)-Berekening!J10)),1000000000000))</f>
-        <v>-210660.489381572</v>
+        <v>-144272.849430311</v>
       </c>
       <c r="K21" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,3)+0.000005)&lt;Berekening!K10,(Berekening!K45-(INDEX(T1_Rente,3)+0.000005)*Berekening!K46)/(360*((INDEX(T1_Rente,3)+0.000005)-Berekening!K10)),1000000000000),IF((INDEX(T1_Rente,3)-0.005+0.000005)&gt;Berekening!K10,(Berekening!K45-(INDEX(T1_Rente,3)-0.005+0.000005)*Berekening!K46)/(360*((INDEX(T1_Rente,3)-0.005+0.000005)-Berekening!K10)),1000000000000))</f>
-        <v>-790846.207995258</v>
+        <v>-541618.58364416</v>
       </c>
       <c r="L21" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,3)+0.000005)&lt;Berekening!L10,(Berekening!L45-(INDEX(T1_Rente,3)+0.000005)*Berekening!L46)/(360*((INDEX(T1_Rente,3)+0.000005)-Berekening!L10)),1000000000000),IF((INDEX(T1_Rente,3)-0.005+0.000005)&gt;Berekening!L10,(Berekening!L45-(INDEX(T1_Rente,3)-0.005+0.000005)*Berekening!L46)/(360*((INDEX(T1_Rente,3)-0.005+0.000005)-Berekening!L10)),1000000000000))</f>
-        <v>-210660.489381572</v>
+        <v>-144272.849430311</v>
       </c>
       <c r="M21" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,3)+0.000005)&lt;Berekening!M10,(Berekening!M45-(INDEX(T1_Rente,3)+0.000005)*Berekening!M46)/(360*((INDEX(T1_Rente,3)+0.000005)-Berekening!M10)),1000000000000),IF((INDEX(T1_Rente,3)-0.005+0.000005)&gt;Berekening!M10,(Berekening!M45-(INDEX(T1_Rente,3)-0.005+0.000005)*Berekening!M46)/(360*((INDEX(T1_Rente,3)-0.005+0.000005)-Berekening!M10)),1000000000000))</f>
-        <v>-210660.489381572</v>
+        <v>-144272.849430311</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12337,39 +12337,39 @@
       </c>
       <c r="C24" s="29" t="n">
         <f aca="false">MAX(0,(C23*C6/12-Berekening!C18-Berekening!C44)*Berekening!C11-Berekening!C75+C7)</f>
-        <v>367661.728382918</v>
+        <v>259582.941366748</v>
       </c>
       <c r="D24" s="29" t="n">
         <f aca="false">MAX(0,(D23*D6/12-Berekening!D18-Berekening!D44)*Berekening!D11-Berekening!D75+D7)</f>
-        <v>399185.177282023</v>
+        <v>288634.493320557</v>
       </c>
       <c r="E24" s="29" t="n">
         <f aca="false">MAX(0,(E23*E6/12-Berekening!E18-Berekening!E44)*Berekening!E11-Berekening!E75+E7)</f>
-        <v>235081.233086328</v>
+        <v>136935.398028213</v>
       </c>
       <c r="F24" s="29" t="n">
         <f aca="false">MAX(0,(F23*F6/12-Berekening!F18-Berekening!F44)*Berekening!F11-Berekening!F75+F7)</f>
-        <v>326759.18488248</v>
+        <v>250849.425936205</v>
       </c>
       <c r="G24" s="29" t="n">
         <f aca="false">MAX(0,(G23*G6/12-Berekening!G18-Berekening!G44)*Berekening!G11-Berekening!G75+G7)</f>
-        <v>238792.383870092</v>
+        <v>221792.707433446</v>
       </c>
       <c r="H24" s="29" t="n">
         <f aca="false">MAX(0,(H23*H6/12-Berekening!H18-Berekening!H44)*Berekening!H11-Berekening!H75+H7)</f>
-        <v>646238.517879618</v>
+        <v>595189.94452608</v>
       </c>
       <c r="I24" s="29" t="n">
         <f aca="false">MAX(0,(I23*I6/12-Berekening!I18-Berekening!I44)*Berekening!I11-Berekening!I75+I7)</f>
-        <v>969456.983172665</v>
+        <v>812354.848140434</v>
       </c>
       <c r="J24" s="29" t="n">
         <f aca="false">MAX(0,(J23*J6/12-Berekening!J18-Berekening!J44)*Berekening!J11-Berekening!J75+J7)</f>
-        <v>408120.341828467</v>
+        <v>296869.010992392</v>
       </c>
       <c r="K24" s="29" t="n">
         <f aca="false">MAX(0,(K23*K6/12-Berekening!K18-Berekening!K44)*Berekening!K11-Berekening!K75+K7)</f>
-        <v>138742.231731598</v>
+        <v>49200.4764052323</v>
       </c>
       <c r="L24" s="29" t="n">
         <f aca="false">MAX(0,(L23*L6/12-Berekening!L18-Berekening!L44)*Berekening!L11-Berekening!L75+L7)</f>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="M24" s="29" t="n">
         <f aca="false">MAX(0,(M23*M6/12-Berekening!M18-Berekening!M44)*Berekening!M11-Berekening!M75+M7)</f>
-        <v>367661.728382918</v>
+        <v>259582.941366748</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12441,15 +12441,15 @@
       </c>
       <c r="C26" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,4)+0.000005)&lt;Berekening!C10,(Berekening!C45-(INDEX(T1_Rente,4)+0.000005)*Berekening!C46)/(360*((INDEX(T1_Rente,4)+0.000005)-Berekening!C10)),1000000000000),IF((INDEX(T1_Rente,4)-0.005+0.000005)&gt;Berekening!C10,(Berekening!C45-(INDEX(T1_Rente,4)-0.005+0.000005)*Berekening!C46)/(360*((INDEX(T1_Rente,4)-0.005+0.000005)-Berekening!C10)),1000000000000))</f>
-        <v>-29476.1362291147</v>
+        <v>-17437.9391305121</v>
       </c>
       <c r="D26" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,4)+0.000005)&lt;Berekening!D10,(Berekening!D45-(INDEX(T1_Rente,4)+0.000005)*Berekening!D46)/(360*((INDEX(T1_Rente,4)+0.000005)-Berekening!D10)),1000000000000),IF((INDEX(T1_Rente,4)-0.005+0.000005)&gt;Berekening!D10,(Berekening!D45-(INDEX(T1_Rente,4)-0.005+0.000005)*Berekening!D46)/(360*((INDEX(T1_Rente,4)-0.005+0.000005)-Berekening!D10)),1000000000000))</f>
-        <v>-131305.397243622</v>
+        <v>-77679.6357176679</v>
       </c>
       <c r="E26" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,4)+0.000005)&lt;Berekening!E10,(Berekening!E45-(INDEX(T1_Rente,4)+0.000005)*Berekening!E46)/(360*((INDEX(T1_Rente,4)+0.000005)-Berekening!E10)),1000000000000),IF((INDEX(T1_Rente,4)-0.005+0.000005)&gt;Berekening!E10,(Berekening!E45-(INDEX(T1_Rente,4)-0.005+0.000005)*Berekening!E46)/(360*((INDEX(T1_Rente,4)-0.005+0.000005)-Berekening!E10)),1000000000000))</f>
-        <v>-1145982.58995598</v>
+        <v>-677957.738183486</v>
       </c>
       <c r="F26" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,4)+0.000005)&lt;Berekening!F10,(Berekening!F45-(INDEX(T1_Rente,4)+0.000005)*Berekening!F46)/(360*((INDEX(T1_Rente,4)+0.000005)-Berekening!F10)),1000000000000),IF((INDEX(T1_Rente,4)-0.005+0.000005)&gt;Berekening!F10,(Berekening!F45-(INDEX(T1_Rente,4)-0.005+0.000005)*Berekening!F46)/(360*((INDEX(T1_Rente,4)-0.005+0.000005)-Berekening!F10)),1000000000000))</f>
@@ -12469,19 +12469,19 @@
       </c>
       <c r="J26" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,4)+0.000005)&lt;Berekening!J10,(Berekening!J45-(INDEX(T1_Rente,4)+0.000005)*Berekening!J46)/(360*((INDEX(T1_Rente,4)+0.000005)-Berekening!J10)),1000000000000),IF((INDEX(T1_Rente,4)-0.005+0.000005)&gt;Berekening!J10,(Berekening!J45-(INDEX(T1_Rente,4)-0.005+0.000005)*Berekening!J46)/(360*((INDEX(T1_Rente,4)-0.005+0.000005)-Berekening!J10)),1000000000000))</f>
-        <v>-29476.1362291147</v>
+        <v>-17437.9391305121</v>
       </c>
       <c r="K26" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,4)+0.000005)&lt;Berekening!K10,(Berekening!K45-(INDEX(T1_Rente,4)+0.000005)*Berekening!K46)/(360*((INDEX(T1_Rente,4)+0.000005)-Berekening!K10)),1000000000000),IF((INDEX(T1_Rente,4)-0.005+0.000005)&gt;Berekening!K10,(Berekening!K45-(INDEX(T1_Rente,4)-0.005+0.000005)*Berekening!K46)/(360*((INDEX(T1_Rente,4)-0.005+0.000005)-Berekening!K10)),1000000000000))</f>
-        <v>-949126.229781557</v>
+        <v>-561498.470948012</v>
       </c>
       <c r="L26" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,4)+0.000005)&lt;Berekening!L10,(Berekening!L45-(INDEX(T1_Rente,4)+0.000005)*Berekening!L46)/(360*((INDEX(T1_Rente,4)+0.000005)-Berekening!L10)),1000000000000),IF((INDEX(T1_Rente,4)-0.005+0.000005)&gt;Berekening!L10,(Berekening!L45-(INDEX(T1_Rente,4)-0.005+0.000005)*Berekening!L46)/(360*((INDEX(T1_Rente,4)-0.005+0.000005)-Berekening!L10)),1000000000000))</f>
-        <v>-29476.1362291147</v>
+        <v>-17437.9391305121</v>
       </c>
       <c r="M26" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,4)+0.000005)&lt;Berekening!M10,(Berekening!M45-(INDEX(T1_Rente,4)+0.000005)*Berekening!M46)/(360*((INDEX(T1_Rente,4)+0.000005)-Berekening!M10)),1000000000000),IF((INDEX(T1_Rente,4)-0.005+0.000005)&gt;Berekening!M10,(Berekening!M45-(INDEX(T1_Rente,4)-0.005+0.000005)*Berekening!M46)/(360*((INDEX(T1_Rente,4)-0.005+0.000005)-Berekening!M10)),1000000000000))</f>
-        <v>-29476.1362291147</v>
+        <v>-17437.9391305121</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12597,39 +12597,39 @@
       </c>
       <c r="C29" s="29" t="n">
         <f aca="false">MAX(0,(C28*C6/12-Berekening!C18-Berekening!C44)*Berekening!C11-Berekening!C75+C7)</f>
-        <v>406298.599695031</v>
+        <v>293967.555870693</v>
       </c>
       <c r="D29" s="29" t="n">
         <f aca="false">MAX(0,(D28*D6/12-Berekening!D18-Berekening!D44)*Berekening!D11-Berekening!D75+D7)</f>
-        <v>437822.048594136</v>
+        <v>323019.107824502</v>
       </c>
       <c r="E29" s="29" t="n">
         <f aca="false">MAX(0,(E28*E6/12-Berekening!E18-Berekening!E44)*Berekening!E11-Berekening!E75+E7)</f>
-        <v>273718.104398442</v>
+        <v>171320.012532158</v>
       </c>
       <c r="F29" s="29" t="n">
         <f aca="false">MAX(0,(F28*F6/12-Berekening!F18-Berekening!F44)*Berekening!F11-Berekening!F75+F7)</f>
-        <v>361120.381493438</v>
+        <v>284030.838972537</v>
       </c>
       <c r="G29" s="29" t="n">
         <f aca="false">MAX(0,(G28*G6/12-Berekening!G18-Berekening!G44)*Berekening!G11-Berekening!G75+G7)</f>
-        <v>248741.792791666</v>
+        <v>230961.937967832</v>
       </c>
       <c r="H29" s="29" t="n">
         <f aca="false">MAX(0,(H28*H6/12-Berekening!H18-Berekening!H44)*Berekening!H11-Berekening!H75+H7)</f>
-        <v>671112.040183553</v>
+        <v>618113.020862043</v>
       </c>
       <c r="I29" s="29" t="n">
         <f aca="false">MAX(0,(I28*I6/12-Berekening!I18-Berekening!I44)*Berekening!I11-Berekening!I75+I7)</f>
-        <v>1008093.85448478</v>
+        <v>846739.462644378</v>
       </c>
       <c r="J29" s="29" t="n">
         <f aca="false">MAX(0,(J28*J6/12-Berekening!J18-Berekening!J44)*Berekening!J11-Berekening!J75+J7)</f>
-        <v>446757.21314058</v>
+        <v>331253.625496337</v>
       </c>
       <c r="K29" s="29" t="n">
         <f aca="false">MAX(0,(K28*K6/12-Berekening!K18-Berekening!K44)*Berekening!K11-Berekening!K75+K7)</f>
-        <v>177379.103043711</v>
+        <v>83585.0909091769</v>
       </c>
       <c r="L29" s="29" t="n">
         <f aca="false">MAX(0,(L28*L6/12-Berekening!L18-Berekening!L44)*Berekening!L11-Berekening!L75+L7)</f>
@@ -12637,7 +12637,7 @@
       </c>
       <c r="M29" s="29" t="n">
         <f aca="false">MAX(0,(M28*M6/12-Berekening!M18-Berekening!M44)*Berekening!M11-Berekening!M75+M7)</f>
-        <v>406298.599695031</v>
+        <v>293967.555870693</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12701,15 +12701,15 @@
       </c>
       <c r="C31" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,5)+0.000005)&lt;Berekening!C10,(Berekening!C45-(INDEX(T1_Rente,5)+0.000005)*Berekening!C46)/(360*((INDEX(T1_Rente,5)+0.000005)-Berekening!C10)),1000000000000),IF((INDEX(T1_Rente,5)-0.005+0.000005)&gt;Berekening!C10,(Berekening!C45-(INDEX(T1_Rente,5)-0.005+0.000005)*Berekening!C46)/(360*((INDEX(T1_Rente,5)-0.005+0.000005)-Berekening!C10)),1000000000000))</f>
-        <v>514439.654665999</v>
+        <v>216025.731404512</v>
       </c>
       <c r="D31" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,5)+0.000005)&lt;Berekening!D10,(Berekening!D45-(INDEX(T1_Rente,5)+0.000005)*Berekening!D46)/(360*((INDEX(T1_Rente,5)+0.000005)-Berekening!D10)),1000000000000),IF((INDEX(T1_Rente,5)-0.005+0.000005)&gt;Berekening!D10,(Berekening!D45-(INDEX(T1_Rente,5)-0.005+0.000005)*Berekening!D46)/(360*((INDEX(T1_Rente,5)-0.005+0.000005)-Berekening!D10)),1000000000000))</f>
-        <v>361632.052962963</v>
+        <v>151858.100424548</v>
       </c>
       <c r="E31" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,5)+0.000005)&lt;Berekening!E10,(Berekening!E45-(INDEX(T1_Rente,5)+0.000005)*Berekening!E46)/(360*((INDEX(T1_Rente,5)+0.000005)-Berekening!E10)),1000000000000),IF((INDEX(T1_Rente,5)-0.005+0.000005)&gt;Berekening!E10,(Berekening!E45-(INDEX(T1_Rente,5)-0.005+0.000005)*Berekening!E46)/(360*((INDEX(T1_Rente,5)-0.005+0.000005)-Berekening!E10)),1000000000000))</f>
-        <v>-1719690.87686553</v>
+        <v>-722140.052958666</v>
       </c>
       <c r="F31" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,5)+0.000005)&lt;Berekening!F10,(Berekening!F45-(INDEX(T1_Rente,5)+0.000005)*Berekening!F46)/(360*((INDEX(T1_Rente,5)+0.000005)-Berekening!F10)),1000000000000),IF((INDEX(T1_Rente,5)-0.005+0.000005)&gt;Berekening!F10,(Berekening!F45-(INDEX(T1_Rente,5)-0.005+0.000005)*Berekening!F46)/(360*((INDEX(T1_Rente,5)-0.005+0.000005)-Berekening!F10)),1000000000000))</f>
@@ -12729,19 +12729,19 @@
       </c>
       <c r="J31" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,5)+0.000005)&lt;Berekening!J10,(Berekening!J45-(INDEX(T1_Rente,5)+0.000005)*Berekening!J46)/(360*((INDEX(T1_Rente,5)+0.000005)-Berekening!J10)),1000000000000),IF((INDEX(T1_Rente,5)-0.005+0.000005)&gt;Berekening!J10,(Berekening!J45-(INDEX(T1_Rente,5)-0.005+0.000005)*Berekening!J46)/(360*((INDEX(T1_Rente,5)-0.005+0.000005)-Berekening!J10)),1000000000000))</f>
-        <v>514439.654665999</v>
+        <v>216025.731404512</v>
       </c>
       <c r="K31" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,5)+0.000005)&lt;Berekening!K10,(Berekening!K45-(INDEX(T1_Rente,5)+0.000005)*Berekening!K46)/(360*((INDEX(T1_Rente,5)+0.000005)-Berekening!K10)),1000000000000),IF((INDEX(T1_Rente,5)-0.005+0.000005)&gt;Berekening!K10,(Berekening!K45-(INDEX(T1_Rente,5)-0.005+0.000005)*Berekening!K46)/(360*((INDEX(T1_Rente,5)-0.005+0.000005)-Berekening!K10)),1000000000000))</f>
-        <v>-1424283.17206095</v>
+        <v>-598091.168091168</v>
       </c>
       <c r="L31" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,5)+0.000005)&lt;Berekening!L10,(Berekening!L45-(INDEX(T1_Rente,5)+0.000005)*Berekening!L46)/(360*((INDEX(T1_Rente,5)+0.000005)-Berekening!L10)),1000000000000),IF((INDEX(T1_Rente,5)-0.005+0.000005)&gt;Berekening!L10,(Berekening!L45-(INDEX(T1_Rente,5)-0.005+0.000005)*Berekening!L46)/(360*((INDEX(T1_Rente,5)-0.005+0.000005)-Berekening!L10)),1000000000000))</f>
-        <v>514439.654665999</v>
+        <v>216025.731404512</v>
       </c>
       <c r="M31" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,5)+0.000005)&lt;Berekening!M10,(Berekening!M45-(INDEX(T1_Rente,5)+0.000005)*Berekening!M46)/(360*((INDEX(T1_Rente,5)+0.000005)-Berekening!M10)),1000000000000),IF((INDEX(T1_Rente,5)-0.005+0.000005)&gt;Berekening!M10,(Berekening!M45-(INDEX(T1_Rente,5)-0.005+0.000005)*Berekening!M46)/(360*((INDEX(T1_Rente,5)-0.005+0.000005)-Berekening!M10)),1000000000000))</f>
-        <v>514439.654665999</v>
+        <v>216025.731404512</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12753,11 +12753,11 @@
       </c>
       <c r="C32" s="29" t="n">
         <f aca="false">IF(C30&gt;C31,-1,IF(C29&lt;C30-0.000000001,-1,IF(C29&gt;C31,MAX(C30,C31-1),C29)))</f>
-        <v>406298.599695031</v>
+        <v>216024.731404512</v>
       </c>
       <c r="D32" s="29" t="n">
         <f aca="false">IF(D30&gt;D31,-1,IF(D29&lt;D30-0.000000001,-1,IF(D29&gt;D31,MAX(D30,D31-1),D29)))</f>
-        <v>361631.052962963</v>
+        <v>151857.100424548</v>
       </c>
       <c r="E32" s="29" t="n">
         <f aca="false">IF(E30&gt;E31,-1,IF(E29&lt;E30-0.000000001,-1,IF(E29&gt;E31,MAX(E30,E31-1),E29)))</f>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="J32" s="29" t="n">
         <f aca="false">IF(J30&gt;J31,-1,IF(J29&lt;J30-0.000000001,-1,IF(J29&gt;J31,MAX(J30,J31-1),J29)))</f>
-        <v>446757.21314058</v>
+        <v>216024.731404512</v>
       </c>
       <c r="K32" s="29" t="n">
         <f aca="false">IF(K30&gt;K31,-1,IF(K29&lt;K30-0.000000001,-1,IF(K29&gt;K31,MAX(K30,K31-1),K29)))</f>
@@ -12793,7 +12793,7 @@
       </c>
       <c r="M32" s="29" t="n">
         <f aca="false">IF(M30&gt;M31,-1,IF(M29&lt;M30-0.000000001,-1,IF(M29&gt;M31,MAX(M30,M31-1),M29)))</f>
-        <v>406298.599695031</v>
+        <v>216024.731404512</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12857,39 +12857,39 @@
       </c>
       <c r="C34" s="29" t="n">
         <f aca="false">MAX(0,(C33*C6/12-Berekening!C18-Berekening!C44)*Berekening!C11-Berekening!C75+C7)</f>
-        <v>444935.471007145</v>
+        <v>328352.170374638</v>
       </c>
       <c r="D34" s="29" t="n">
         <f aca="false">MAX(0,(D33*D6/12-Berekening!D18-Berekening!D44)*Berekening!D11-Berekening!D75+D7)</f>
-        <v>476458.919906249</v>
+        <v>357403.722328447</v>
       </c>
       <c r="E34" s="29" t="n">
         <f aca="false">MAX(0,(E33*E6/12-Berekening!E18-Berekening!E44)*Berekening!E11-Berekening!E75+E7)</f>
-        <v>312354.975710555</v>
+        <v>205704.627036103</v>
       </c>
       <c r="F34" s="29" t="n">
         <f aca="false">MAX(0,(F33*F6/12-Berekening!F18-Berekening!F44)*Berekening!F11-Berekening!F75+F7)</f>
-        <v>395481.578104395</v>
+        <v>317212.252008869</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">MAX(0,(G33*G6/12-Berekening!G18-Berekening!G44)*Berekening!G11-Berekening!G75+G7)</f>
-        <v>258691.20171324</v>
+        <v>240131.168502217</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">MAX(0,(H33*H6/12-Berekening!H18-Berekening!H44)*Berekening!H11-Berekening!H75+H7)</f>
-        <v>695985.562487489</v>
+        <v>641036.097198006</v>
       </c>
       <c r="I34" s="29" t="n">
         <f aca="false">MAX(0,(I33*I6/12-Berekening!I18-Berekening!I44)*Berekening!I11-Berekening!I75+I7)</f>
-        <v>1046730.72579689</v>
+        <v>881124.077148323</v>
       </c>
       <c r="J34" s="29" t="n">
         <f aca="false">MAX(0,(J33*J6/12-Berekening!J18-Berekening!J44)*Berekening!J11-Berekening!J75+J7)</f>
-        <v>485394.084452694</v>
+        <v>365638.240000281</v>
       </c>
       <c r="K34" s="29" t="n">
         <f aca="false">MAX(0,(K33*K6/12-Berekening!K18-Berekening!K44)*Berekening!K11-Berekening!K75+K7)</f>
-        <v>216015.974355825</v>
+        <v>117969.705413122</v>
       </c>
       <c r="L34" s="29" t="n">
         <f aca="false">MAX(0,(L33*L6/12-Berekening!L18-Berekening!L44)*Berekening!L11-Berekening!L75+L7)</f>
@@ -12897,7 +12897,7 @@
       </c>
       <c r="M34" s="29" t="n">
         <f aca="false">MAX(0,(M33*M6/12-Berekening!M18-Berekening!M44)*Berekening!M11-Berekening!M75+M7)</f>
-        <v>444935.471007145</v>
+        <v>328352.170374638</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12909,15 +12909,15 @@
       </c>
       <c r="C35" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,6)+0.000005)&gt;Berekening!C10,(Berekening!C45-(INDEX(T1_Rente,6)+0.000005)*Berekening!C46)/(360*((INDEX(T1_Rente,6)+0.000005)-Berekening!C10)),IF((INDEX(T1_Rente,6)+0.000005)=Berekening!C10,IF(Berekening!C45-(INDEX(T1_Rente,6)+0.000005)*Berekening!C46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,6)-0.005+0.000005)&lt;Berekening!C10,(Berekening!C45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!C46)/(360*((INDEX(T1_Rente,6)-0.005+0.000005)-Berekening!C10)),IF((INDEX(T1_Rente,6)-0.005+0.000005)=Berekening!C10,IF(Berekening!C45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!C46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>514439.654665999</v>
+        <v>216025.731404512</v>
       </c>
       <c r="D35" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,6)+0.000005)&gt;Berekening!D10,(Berekening!D45-(INDEX(T1_Rente,6)+0.000005)*Berekening!D46)/(360*((INDEX(T1_Rente,6)+0.000005)-Berekening!D10)),IF((INDEX(T1_Rente,6)+0.000005)=Berekening!D10,IF(Berekening!D45-(INDEX(T1_Rente,6)+0.000005)*Berekening!D46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,6)-0.005+0.000005)&lt;Berekening!D10,(Berekening!D45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!D46)/(360*((INDEX(T1_Rente,6)-0.005+0.000005)-Berekening!D10)),IF((INDEX(T1_Rente,6)-0.005+0.000005)=Berekening!D10,IF(Berekening!D45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!D46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>361632.052962963</v>
+        <v>151858.100424548</v>
       </c>
       <c r="E35" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,6)+0.000005)&gt;Berekening!E10,(Berekening!E45-(INDEX(T1_Rente,6)+0.000005)*Berekening!E46)/(360*((INDEX(T1_Rente,6)+0.000005)-Berekening!E10)),IF((INDEX(T1_Rente,6)+0.000005)=Berekening!E10,IF(Berekening!E45-(INDEX(T1_Rente,6)+0.000005)*Berekening!E46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,6)-0.005+0.000005)&lt;Berekening!E10,(Berekening!E45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!E46)/(360*((INDEX(T1_Rente,6)-0.005+0.000005)-Berekening!E10)),IF((INDEX(T1_Rente,6)-0.005+0.000005)=Berekening!E10,IF(Berekening!E45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!E46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>1145123174.65578</v>
+        <v>0</v>
       </c>
       <c r="F35" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,6)+0.000005)&gt;Berekening!F10,(Berekening!F45-(INDEX(T1_Rente,6)+0.000005)*Berekening!F46)/(360*((INDEX(T1_Rente,6)+0.000005)-Berekening!F10)),IF((INDEX(T1_Rente,6)+0.000005)=Berekening!F10,IF(Berekening!F45-(INDEX(T1_Rente,6)+0.000005)*Berekening!F46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,6)-0.005+0.000005)&lt;Berekening!F10,(Berekening!F45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!F46)/(360*((INDEX(T1_Rente,6)-0.005+0.000005)-Berekening!F10)),IF((INDEX(T1_Rente,6)-0.005+0.000005)=Berekening!F10,IF(Berekening!F45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!F46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
@@ -12937,19 +12937,19 @@
       </c>
       <c r="J35" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,6)+0.000005)&gt;Berekening!J10,(Berekening!J45-(INDEX(T1_Rente,6)+0.000005)*Berekening!J46)/(360*((INDEX(T1_Rente,6)+0.000005)-Berekening!J10)),IF((INDEX(T1_Rente,6)+0.000005)=Berekening!J10,IF(Berekening!J45-(INDEX(T1_Rente,6)+0.000005)*Berekening!J46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,6)-0.005+0.000005)&lt;Berekening!J10,(Berekening!J45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!J46)/(360*((INDEX(T1_Rente,6)-0.005+0.000005)-Berekening!J10)),IF((INDEX(T1_Rente,6)-0.005+0.000005)=Berekening!J10,IF(Berekening!J45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!J46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>514439.654665999</v>
+        <v>216025.731404512</v>
       </c>
       <c r="K35" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,6)+0.000005)&gt;Berekening!K10,(Berekening!K45-(INDEX(T1_Rente,6)+0.000005)*Berekening!K46)/(360*((INDEX(T1_Rente,6)+0.000005)-Berekening!K10)),IF((INDEX(T1_Rente,6)+0.000005)=Berekening!K10,IF(Berekening!K45-(INDEX(T1_Rente,6)+0.000005)*Berekening!K46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,6)-0.005+0.000005)&lt;Berekening!K10,(Berekening!K45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!K46)/(360*((INDEX(T1_Rente,6)-0.005+0.000005)-Berekening!K10)),IF((INDEX(T1_Rente,6)-0.005+0.000005)=Berekening!K10,IF(Berekening!K45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!K46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>948414444.444812</v>
+        <v>0</v>
       </c>
       <c r="L35" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,6)+0.000005)&gt;Berekening!L10,(Berekening!L45-(INDEX(T1_Rente,6)+0.000005)*Berekening!L46)/(360*((INDEX(T1_Rente,6)+0.000005)-Berekening!L10)),IF((INDEX(T1_Rente,6)+0.000005)=Berekening!L10,IF(Berekening!L45-(INDEX(T1_Rente,6)+0.000005)*Berekening!L46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,6)-0.005+0.000005)&lt;Berekening!L10,(Berekening!L45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!L46)/(360*((INDEX(T1_Rente,6)-0.005+0.000005)-Berekening!L10)),IF((INDEX(T1_Rente,6)-0.005+0.000005)=Berekening!L10,IF(Berekening!L45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!L46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>514439.654665999</v>
+        <v>216025.731404512</v>
       </c>
       <c r="M35" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,6)+0.000005)&gt;Berekening!M10,(Berekening!M45-(INDEX(T1_Rente,6)+0.000005)*Berekening!M46)/(360*((INDEX(T1_Rente,6)+0.000005)-Berekening!M10)),IF((INDEX(T1_Rente,6)+0.000005)=Berekening!M10,IF(Berekening!M45-(INDEX(T1_Rente,6)+0.000005)*Berekening!M46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,6)-0.005+0.000005)&lt;Berekening!M10,(Berekening!M45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!M46)/(360*((INDEX(T1_Rente,6)-0.005+0.000005)-Berekening!M10)),IF((INDEX(T1_Rente,6)-0.005+0.000005)=Berekening!M10,IF(Berekening!M45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!M46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>514439.654665999</v>
+        <v>216025.731404512</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12961,15 +12961,15 @@
       </c>
       <c r="C36" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,6)+0.000005)&lt;Berekening!C10,(Berekening!C45-(INDEX(T1_Rente,6)+0.000005)*Berekening!C46)/(360*((INDEX(T1_Rente,6)+0.000005)-Berekening!C10)),1000000000000),IF((INDEX(T1_Rente,6)-0.005+0.000005)&gt;Berekening!C10,(Berekening!C45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!C46)/(360*((INDEX(T1_Rente,6)-0.005+0.000005)-Berekening!C10)),1000000000000))</f>
-        <v>1000000000000</v>
+        <v>788087.908879381</v>
       </c>
       <c r="D36" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,6)+0.000005)&lt;Berekening!D10,(Berekening!D45-(INDEX(T1_Rente,6)+0.000005)*Berekening!D46)/(360*((INDEX(T1_Rente,6)+0.000005)-Berekening!D10)),1000000000000),IF((INDEX(T1_Rente,6)-0.005+0.000005)&gt;Berekening!D10,(Berekening!D45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!D46)/(360*((INDEX(T1_Rente,6)-0.005+0.000005)-Berekening!D10)),1000000000000))</f>
-        <v>1000000000000</v>
+        <v>714300.45751269</v>
       </c>
       <c r="E36" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,6)+0.000005)&lt;Berekening!E10,(Berekening!E45-(INDEX(T1_Rente,6)+0.000005)*Berekening!E46)/(360*((INDEX(T1_Rente,6)+0.000005)-Berekening!E10)),1000000000000),IF((INDEX(T1_Rente,6)-0.005+0.000005)&gt;Berekening!E10,(Berekening!E45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!E46)/(360*((INDEX(T1_Rente,6)-0.005+0.000005)-Berekening!E10)),1000000000000))</f>
-        <v>1000000000000</v>
+        <v>-830401.14188204</v>
       </c>
       <c r="F36" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,6)+0.000005)&lt;Berekening!F10,(Berekening!F45-(INDEX(T1_Rente,6)+0.000005)*Berekening!F46)/(360*((INDEX(T1_Rente,6)+0.000005)-Berekening!F10)),1000000000000),IF((INDEX(T1_Rente,6)-0.005+0.000005)&gt;Berekening!F10,(Berekening!F45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!F46)/(360*((INDEX(T1_Rente,6)-0.005+0.000005)-Berekening!F10)),1000000000000))</f>
@@ -12977,31 +12977,31 @@
       </c>
       <c r="G36" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,6)+0.000005)&lt;Berekening!G10,(Berekening!G45-(INDEX(T1_Rente,6)+0.000005)*Berekening!G46)/(360*((INDEX(T1_Rente,6)+0.000005)-Berekening!G10)),1000000000000),IF((INDEX(T1_Rente,6)-0.005+0.000005)&gt;Berekening!G10,(Berekening!G45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!G46)/(360*((INDEX(T1_Rente,6)-0.005+0.000005)-Berekening!G10)),1000000000000))</f>
-        <v>1000000000000</v>
+        <v>-0</v>
       </c>
       <c r="H36" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,6)+0.000005)&lt;Berekening!H10,(Berekening!H45-(INDEX(T1_Rente,6)+0.000005)*Berekening!H46)/(360*((INDEX(T1_Rente,6)+0.000005)-Berekening!H10)),1000000000000),IF((INDEX(T1_Rente,6)-0.005+0.000005)&gt;Berekening!H10,(Berekening!H45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!H46)/(360*((INDEX(T1_Rente,6)-0.005+0.000005)-Berekening!H10)),1000000000000))</f>
-        <v>1000000000000</v>
+        <v>-0</v>
       </c>
       <c r="I36" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,6)+0.000005)&lt;Berekening!I10,(Berekening!I45-(INDEX(T1_Rente,6)+0.000005)*Berekening!I46)/(360*((INDEX(T1_Rente,6)+0.000005)-Berekening!I10)),1000000000000),IF((INDEX(T1_Rente,6)-0.005+0.000005)&gt;Berekening!I10,(Berekening!I45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!I46)/(360*((INDEX(T1_Rente,6)-0.005+0.000005)-Berekening!I10)),1000000000000))</f>
-        <v>1000000000000</v>
+        <v>-0</v>
       </c>
       <c r="J36" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,6)+0.000005)&lt;Berekening!J10,(Berekening!J45-(INDEX(T1_Rente,6)+0.000005)*Berekening!J46)/(360*((INDEX(T1_Rente,6)+0.000005)-Berekening!J10)),1000000000000),IF((INDEX(T1_Rente,6)-0.005+0.000005)&gt;Berekening!J10,(Berekening!J45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!J46)/(360*((INDEX(T1_Rente,6)-0.005+0.000005)-Berekening!J10)),1000000000000))</f>
-        <v>1000000000000</v>
+        <v>788087.908879381</v>
       </c>
       <c r="K36" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,6)+0.000005)&lt;Berekening!K10,(Berekening!K45-(INDEX(T1_Rente,6)+0.000005)*Berekening!K46)/(360*((INDEX(T1_Rente,6)+0.000005)-Berekening!K10)),1000000000000),IF((INDEX(T1_Rente,6)-0.005+0.000005)&gt;Berekening!K10,(Berekening!K45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!K46)/(360*((INDEX(T1_Rente,6)-0.005+0.000005)-Berekening!K10)),1000000000000))</f>
-        <v>1000000000000</v>
+        <v>-687755.21714608</v>
       </c>
       <c r="L36" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,6)+0.000005)&lt;Berekening!L10,(Berekening!L45-(INDEX(T1_Rente,6)+0.000005)*Berekening!L46)/(360*((INDEX(T1_Rente,6)+0.000005)-Berekening!L10)),1000000000000),IF((INDEX(T1_Rente,6)-0.005+0.000005)&gt;Berekening!L10,(Berekening!L45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!L46)/(360*((INDEX(T1_Rente,6)-0.005+0.000005)-Berekening!L10)),1000000000000))</f>
-        <v>1000000000000</v>
+        <v>788087.908879381</v>
       </c>
       <c r="M36" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,6)+0.000005)&lt;Berekening!M10,(Berekening!M45-(INDEX(T1_Rente,6)+0.000005)*Berekening!M46)/(360*((INDEX(T1_Rente,6)+0.000005)-Berekening!M10)),1000000000000),IF((INDEX(T1_Rente,6)-0.005+0.000005)&gt;Berekening!M10,(Berekening!M45-(INDEX(T1_Rente,6)-0.005+0.000005)*Berekening!M46)/(360*((INDEX(T1_Rente,6)-0.005+0.000005)-Berekening!M10)),1000000000000))</f>
-        <v>1000000000000</v>
+        <v>788087.908879381</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13013,11 +13013,11 @@
       </c>
       <c r="C37" s="29" t="n">
         <f aca="false">IF(C35&gt;C36,-1,IF(C34&lt;C35-0.000000001,-1,IF(C34&gt;C36,MAX(C35,C36-1),C34)))</f>
-        <v>-1</v>
+        <v>328352.170374638</v>
       </c>
       <c r="D37" s="29" t="n">
         <f aca="false">IF(D35&gt;D36,-1,IF(D34&lt;D35-0.000000001,-1,IF(D34&gt;D36,MAX(D35,D36-1),D34)))</f>
-        <v>476458.919906249</v>
+        <v>357403.722328447</v>
       </c>
       <c r="E37" s="29" t="n">
         <f aca="false">IF(E35&gt;E36,-1,IF(E34&lt;E35-0.000000001,-1,IF(E34&gt;E36,MAX(E35,E36-1),E34)))</f>
@@ -13025,23 +13025,23 @@
       </c>
       <c r="F37" s="29" t="n">
         <f aca="false">IF(F35&gt;F36,-1,IF(F34&lt;F35-0.000000001,-1,IF(F34&gt;F36,MAX(F35,F36-1),F34)))</f>
-        <v>395481.578104395</v>
+        <v>317212.252008869</v>
       </c>
       <c r="G37" s="29" t="n">
         <f aca="false">IF(G35&gt;G36,-1,IF(G34&lt;G35-0.000000001,-1,IF(G34&gt;G36,MAX(G35,G36-1),G34)))</f>
-        <v>258691.20171324</v>
+        <v>-0</v>
       </c>
       <c r="H37" s="29" t="n">
         <f aca="false">IF(H35&gt;H36,-1,IF(H34&lt;H35-0.000000001,-1,IF(H34&gt;H36,MAX(H35,H36-1),H34)))</f>
-        <v>695985.562487489</v>
+        <v>-0</v>
       </c>
       <c r="I37" s="29" t="n">
         <f aca="false">IF(I35&gt;I36,-1,IF(I34&lt;I35-0.000000001,-1,IF(I34&gt;I36,MAX(I35,I36-1),I34)))</f>
-        <v>1046730.72579689</v>
+        <v>-0</v>
       </c>
       <c r="J37" s="29" t="n">
         <f aca="false">IF(J35&gt;J36,-1,IF(J34&lt;J35-0.000000001,-1,IF(J34&gt;J36,MAX(J35,J36-1),J34)))</f>
-        <v>-1</v>
+        <v>365638.240000281</v>
       </c>
       <c r="K37" s="29" t="n">
         <f aca="false">IF(K35&gt;K36,-1,IF(K34&lt;K35-0.000000001,-1,IF(K34&gt;K36,MAX(K35,K36-1),K34)))</f>
@@ -13053,7 +13053,7 @@
       </c>
       <c r="M37" s="29" t="n">
         <f aca="false">IF(M35&gt;M36,-1,IF(M34&lt;M35-0.000000001,-1,IF(M34&gt;M36,MAX(M35,M36-1),M34)))</f>
-        <v>-1</v>
+        <v>328352.170374638</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13117,39 +13117,39 @@
       </c>
       <c r="C39" s="29" t="n">
         <f aca="false">MAX(0,(C38*C6/12-Berekening!C18-Berekening!C44)*Berekening!C11-Berekening!C75+C7)</f>
-        <v>481538.822776515</v>
+        <v>360927.068325743</v>
       </c>
       <c r="D39" s="29" t="n">
         <f aca="false">MAX(0,(D38*D6/12-Berekening!D18-Berekening!D44)*Berekening!D11-Berekening!D75+D7)</f>
-        <v>513062.27167562</v>
+        <v>389978.620279552</v>
       </c>
       <c r="E39" s="29" t="n">
         <f aca="false">MAX(0,(E38*E6/12-Berekening!E18-Berekening!E44)*Berekening!E11-Berekening!E75+E7)</f>
-        <v>348958.327479926</v>
+        <v>238279.524987208</v>
       </c>
       <c r="F39" s="29" t="n">
         <f aca="false">MAX(0,(F38*F6/12-Berekening!F18-Berekening!F44)*Berekening!F11-Berekening!F75+F7)</f>
-        <v>428034.290683197</v>
+        <v>348647.274885394</v>
       </c>
       <c r="G39" s="29" t="n">
         <f aca="false">MAX(0,(G38*G6/12-Berekening!G18-Berekening!G44)*Berekening!G11-Berekening!G75+G7)</f>
-        <v>269164.26373595</v>
+        <v>249782.990117359</v>
       </c>
       <c r="H39" s="29" t="n">
         <f aca="false">MAX(0,(H38*H6/12-Berekening!H18-Berekening!H44)*Berekening!H11-Berekening!H75+H7)</f>
-        <v>719549.952038586</v>
+        <v>662752.695832076</v>
       </c>
       <c r="I39" s="29" t="n">
         <f aca="false">MAX(0,(I38*I6/12-Berekening!I18-Berekening!I44)*Berekening!I11-Berekening!I75+I7)</f>
-        <v>1083334.07756626</v>
+        <v>913698.975099428</v>
       </c>
       <c r="J39" s="29" t="n">
         <f aca="false">MAX(0,(J38*J6/12-Berekening!J18-Berekening!J44)*Berekening!J11-Berekening!J75+J7)</f>
-        <v>521997.436222064</v>
+        <v>398213.137951386</v>
       </c>
       <c r="K39" s="29" t="n">
         <f aca="false">MAX(0,(K38*K6/12-Berekening!K18-Berekening!K44)*Berekening!K11-Berekening!K75+K7)</f>
-        <v>252619.326125195</v>
+        <v>150544.603364227</v>
       </c>
       <c r="L39" s="29" t="n">
         <f aca="false">MAX(0,(L38*L6/12-Berekening!L18-Berekening!L44)*Berekening!L11-Berekening!L75+L7)</f>
@@ -13157,7 +13157,7 @@
       </c>
       <c r="M39" s="29" t="n">
         <f aca="false">MAX(0,(M38*M6/12-Berekening!M18-Berekening!M44)*Berekening!M11-Berekening!M75+M7)</f>
-        <v>481538.822776515</v>
+        <v>360927.068325743</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13169,15 +13169,15 @@
       </c>
       <c r="C40" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,7)+0.000005)&gt;Berekening!C10,(Berekening!C45-(INDEX(T1_Rente,7)+0.000005)*Berekening!C46)/(360*((INDEX(T1_Rente,7)+0.000005)-Berekening!C10)),IF((INDEX(T1_Rente,7)+0.000005)=Berekening!C10,IF(Berekening!C45-(INDEX(T1_Rente,7)+0.000005)*Berekening!C46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,7)-0.005+0.000005)&lt;Berekening!C10,(Berekening!C45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!C46)/(360*((INDEX(T1_Rente,7)-0.005+0.000005)-Berekening!C10)),IF((INDEX(T1_Rente,7)-0.005+0.000005)=Berekening!C10,IF(Berekening!C45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!C46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>788087.908879381</v>
       </c>
       <c r="D40" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,7)+0.000005)&gt;Berekening!D10,(Berekening!D45-(INDEX(T1_Rente,7)+0.000005)*Berekening!D46)/(360*((INDEX(T1_Rente,7)+0.000005)-Berekening!D10)),IF((INDEX(T1_Rente,7)+0.000005)=Berekening!D10,IF(Berekening!D45-(INDEX(T1_Rente,7)+0.000005)*Berekening!D46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,7)-0.005+0.000005)&lt;Berekening!D10,(Berekening!D45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!D46)/(360*((INDEX(T1_Rente,7)-0.005+0.000005)-Berekening!D10)),IF((INDEX(T1_Rente,7)-0.005+0.000005)=Berekening!D10,IF(Berekening!D45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!D46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>714300.45751269</v>
       </c>
       <c r="E40" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,7)+0.000005)&gt;Berekening!E10,(Berekening!E45-(INDEX(T1_Rente,7)+0.000005)*Berekening!E46)/(360*((INDEX(T1_Rente,7)+0.000005)-Berekening!E10)),IF((INDEX(T1_Rente,7)+0.000005)=Berekening!E10,IF(Berekening!E45-(INDEX(T1_Rente,7)+0.000005)*Berekening!E46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,7)-0.005+0.000005)&lt;Berekening!E10,(Berekening!E45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!E46)/(360*((INDEX(T1_Rente,7)-0.005+0.000005)-Berekening!E10)),IF((INDEX(T1_Rente,7)-0.005+0.000005)=Berekening!E10,IF(Berekening!E45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!E46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>571703.459862139</v>
+        <v>0</v>
       </c>
       <c r="F40" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,7)+0.000005)&gt;Berekening!F10,(Berekening!F45-(INDEX(T1_Rente,7)+0.000005)*Berekening!F46)/(360*((INDEX(T1_Rente,7)+0.000005)-Berekening!F10)),IF((INDEX(T1_Rente,7)+0.000005)=Berekening!F10,IF(Berekening!F45-(INDEX(T1_Rente,7)+0.000005)*Berekening!F46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,7)-0.005+0.000005)&lt;Berekening!F10,(Berekening!F45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!F46)/(360*((INDEX(T1_Rente,7)-0.005+0.000005)-Berekening!F10)),IF((INDEX(T1_Rente,7)-0.005+0.000005)=Berekening!F10,IF(Berekening!F45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!F46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
@@ -13185,31 +13185,31 @@
       </c>
       <c r="G40" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,7)+0.000005)&gt;Berekening!G10,(Berekening!G45-(INDEX(T1_Rente,7)+0.000005)*Berekening!G46)/(360*((INDEX(T1_Rente,7)+0.000005)-Berekening!G10)),IF((INDEX(T1_Rente,7)+0.000005)=Berekening!G10,IF(Berekening!G45-(INDEX(T1_Rente,7)+0.000005)*Berekening!G46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,7)-0.005+0.000005)&lt;Berekening!G10,(Berekening!G45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!G46)/(360*((INDEX(T1_Rente,7)-0.005+0.000005)-Berekening!G10)),IF((INDEX(T1_Rente,7)-0.005+0.000005)=Berekening!G10,IF(Berekening!G45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!G46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H40" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,7)+0.000005)&gt;Berekening!H10,(Berekening!H45-(INDEX(T1_Rente,7)+0.000005)*Berekening!H46)/(360*((INDEX(T1_Rente,7)+0.000005)-Berekening!H10)),IF((INDEX(T1_Rente,7)+0.000005)=Berekening!H10,IF(Berekening!H45-(INDEX(T1_Rente,7)+0.000005)*Berekening!H46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,7)-0.005+0.000005)&lt;Berekening!H10,(Berekening!H45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!H46)/(360*((INDEX(T1_Rente,7)-0.005+0.000005)-Berekening!H10)),IF((INDEX(T1_Rente,7)-0.005+0.000005)=Berekening!H10,IF(Berekening!H45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!H46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I40" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,7)+0.000005)&gt;Berekening!I10,(Berekening!I45-(INDEX(T1_Rente,7)+0.000005)*Berekening!I46)/(360*((INDEX(T1_Rente,7)+0.000005)-Berekening!I10)),IF((INDEX(T1_Rente,7)+0.000005)=Berekening!I10,IF(Berekening!I45-(INDEX(T1_Rente,7)+0.000005)*Berekening!I46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,7)-0.005+0.000005)&lt;Berekening!I10,(Berekening!I45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!I46)/(360*((INDEX(T1_Rente,7)-0.005+0.000005)-Berekening!I10)),IF((INDEX(T1_Rente,7)-0.005+0.000005)=Berekening!I10,IF(Berekening!I45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!I46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J40" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,7)+0.000005)&gt;Berekening!J10,(Berekening!J45-(INDEX(T1_Rente,7)+0.000005)*Berekening!J46)/(360*((INDEX(T1_Rente,7)+0.000005)-Berekening!J10)),IF((INDEX(T1_Rente,7)+0.000005)=Berekening!J10,IF(Berekening!J45-(INDEX(T1_Rente,7)+0.000005)*Berekening!J46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,7)-0.005+0.000005)&lt;Berekening!J10,(Berekening!J45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!J46)/(360*((INDEX(T1_Rente,7)-0.005+0.000005)-Berekening!J10)),IF((INDEX(T1_Rente,7)-0.005+0.000005)=Berekening!J10,IF(Berekening!J45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!J46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>788087.908879381</v>
       </c>
       <c r="K40" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,7)+0.000005)&gt;Berekening!K10,(Berekening!K45-(INDEX(T1_Rente,7)+0.000005)*Berekening!K46)/(360*((INDEX(T1_Rente,7)+0.000005)-Berekening!K10)),IF((INDEX(T1_Rente,7)+0.000005)=Berekening!K10,IF(Berekening!K45-(INDEX(T1_Rente,7)+0.000005)*Berekening!K46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,7)-0.005+0.000005)&lt;Berekening!K10,(Berekening!K45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!K46)/(360*((INDEX(T1_Rente,7)-0.005+0.000005)-Berekening!K10)),IF((INDEX(T1_Rente,7)-0.005+0.000005)=Berekening!K10,IF(Berekening!K45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!K46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>473496.503496504</v>
+        <v>0</v>
       </c>
       <c r="L40" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,7)+0.000005)&gt;Berekening!L10,(Berekening!L45-(INDEX(T1_Rente,7)+0.000005)*Berekening!L46)/(360*((INDEX(T1_Rente,7)+0.000005)-Berekening!L10)),IF((INDEX(T1_Rente,7)+0.000005)=Berekening!L10,IF(Berekening!L45-(INDEX(T1_Rente,7)+0.000005)*Berekening!L46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,7)-0.005+0.000005)&lt;Berekening!L10,(Berekening!L45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!L46)/(360*((INDEX(T1_Rente,7)-0.005+0.000005)-Berekening!L10)),IF((INDEX(T1_Rente,7)-0.005+0.000005)=Berekening!L10,IF(Berekening!L45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!L46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>788087.908879381</v>
       </c>
       <c r="M40" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,7)+0.000005)&gt;Berekening!M10,(Berekening!M45-(INDEX(T1_Rente,7)+0.000005)*Berekening!M46)/(360*((INDEX(T1_Rente,7)+0.000005)-Berekening!M10)),IF((INDEX(T1_Rente,7)+0.000005)=Berekening!M10,IF(Berekening!M45-(INDEX(T1_Rente,7)+0.000005)*Berekening!M46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,7)-0.005+0.000005)&lt;Berekening!M10,(Berekening!M45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!M46)/(360*((INDEX(T1_Rente,7)-0.005+0.000005)-Berekening!M10)),IF((INDEX(T1_Rente,7)-0.005+0.000005)=Berekening!M10,IF(Berekening!M45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!M46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>788087.908879381</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13221,15 +13221,15 @@
       </c>
       <c r="C41" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,7)+0.000005)&lt;Berekening!C10,(Berekening!C45-(INDEX(T1_Rente,7)+0.000005)*Berekening!C46)/(360*((INDEX(T1_Rente,7)+0.000005)-Berekening!C10)),1000000000000),IF((INDEX(T1_Rente,7)-0.005+0.000005)&gt;Berekening!C10,(Berekening!C45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!C46)/(360*((INDEX(T1_Rente,7)-0.005+0.000005)-Berekening!C10)),1000000000000))</f>
-        <v>-1086773226.34509</v>
+        <v>4378947.85667018</v>
       </c>
       <c r="D41" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,7)+0.000005)&lt;Berekening!D10,(Berekening!D45-(INDEX(T1_Rente,7)+0.000005)*Berekening!D46)/(360*((INDEX(T1_Rente,7)+0.000005)-Berekening!D10)),1000000000000),IF((INDEX(T1_Rente,7)-0.005+0.000005)&gt;Berekening!D10,(Berekening!D45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!D46)/(360*((INDEX(T1_Rente,7)-0.005+0.000005)-Berekening!D10)),1000000000000))</f>
-        <v>-985020330.910382</v>
+        <v>4244776.3612401</v>
       </c>
       <c r="E41" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,7)+0.000005)&lt;Berekening!E10,(Berekening!E45-(INDEX(T1_Rente,7)+0.000005)*Berekening!E46)/(360*((INDEX(T1_Rente,7)+0.000005)-Berekening!E10)),1000000000000),IF((INDEX(T1_Rente,7)-0.005+0.000005)&gt;Berekening!E10,(Berekening!E45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!E46)/(360*((INDEX(T1_Rente,7)-0.005+0.000005)-Berekening!E10)),1000000000000))</f>
-        <v>1145123174.65578</v>
+        <v>-1509960.85309235</v>
       </c>
       <c r="F41" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,7)+0.000005)&lt;Berekening!F10,(Berekening!F45-(INDEX(T1_Rente,7)+0.000005)*Berekening!F46)/(360*((INDEX(T1_Rente,7)+0.000005)-Berekening!F10)),1000000000000),IF((INDEX(T1_Rente,7)-0.005+0.000005)&gt;Berekening!F10,(Berekening!F45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!F46)/(360*((INDEX(T1_Rente,7)-0.005+0.000005)-Berekening!F10)),1000000000000))</f>
@@ -13237,31 +13237,31 @@
       </c>
       <c r="G41" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,7)+0.000005)&lt;Berekening!G10,(Berekening!G45-(INDEX(T1_Rente,7)+0.000005)*Berekening!G46)/(360*((INDEX(T1_Rente,7)+0.000005)-Berekening!G10)),1000000000000),IF((INDEX(T1_Rente,7)-0.005+0.000005)&gt;Berekening!G10,(Berekening!G45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!G46)/(360*((INDEX(T1_Rente,7)-0.005+0.000005)-Berekening!G10)),1000000000000))</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H41" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,7)+0.000005)&lt;Berekening!H10,(Berekening!H45-(INDEX(T1_Rente,7)+0.000005)*Berekening!H46)/(360*((INDEX(T1_Rente,7)+0.000005)-Berekening!H10)),1000000000000),IF((INDEX(T1_Rente,7)-0.005+0.000005)&gt;Berekening!H10,(Berekening!H45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!H46)/(360*((INDEX(T1_Rente,7)-0.005+0.000005)-Berekening!H10)),1000000000000))</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I41" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,7)+0.000005)&lt;Berekening!I10,(Berekening!I45-(INDEX(T1_Rente,7)+0.000005)*Berekening!I46)/(360*((INDEX(T1_Rente,7)+0.000005)-Berekening!I10)),1000000000000),IF((INDEX(T1_Rente,7)-0.005+0.000005)&gt;Berekening!I10,(Berekening!I45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!I46)/(360*((INDEX(T1_Rente,7)-0.005+0.000005)-Berekening!I10)),1000000000000))</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J41" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,7)+0.000005)&lt;Berekening!J10,(Berekening!J45-(INDEX(T1_Rente,7)+0.000005)*Berekening!J46)/(360*((INDEX(T1_Rente,7)+0.000005)-Berekening!J10)),1000000000000),IF((INDEX(T1_Rente,7)-0.005+0.000005)&gt;Berekening!J10,(Berekening!J45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!J46)/(360*((INDEX(T1_Rente,7)-0.005+0.000005)-Berekening!J10)),1000000000000))</f>
-        <v>-1086773226.34509</v>
+        <v>4378947.85667018</v>
       </c>
       <c r="K41" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,7)+0.000005)&lt;Berekening!K10,(Berekening!K45-(INDEX(T1_Rente,7)+0.000005)*Berekening!K46)/(360*((INDEX(T1_Rente,7)+0.000005)-Berekening!K10)),1000000000000),IF((INDEX(T1_Rente,7)-0.005+0.000005)&gt;Berekening!K10,(Berekening!K45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!K46)/(360*((INDEX(T1_Rente,7)-0.005+0.000005)-Berekening!K10)),1000000000000))</f>
-        <v>948414444.444812</v>
+        <v>-1250580.47493404</v>
       </c>
       <c r="L41" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,7)+0.000005)&lt;Berekening!L10,(Berekening!L45-(INDEX(T1_Rente,7)+0.000005)*Berekening!L46)/(360*((INDEX(T1_Rente,7)+0.000005)-Berekening!L10)),1000000000000),IF((INDEX(T1_Rente,7)-0.005+0.000005)&gt;Berekening!L10,(Berekening!L45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!L46)/(360*((INDEX(T1_Rente,7)-0.005+0.000005)-Berekening!L10)),1000000000000))</f>
-        <v>-1086773226.34509</v>
+        <v>4378947.85667018</v>
       </c>
       <c r="M41" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,7)+0.000005)&lt;Berekening!M10,(Berekening!M45-(INDEX(T1_Rente,7)+0.000005)*Berekening!M46)/(360*((INDEX(T1_Rente,7)+0.000005)-Berekening!M10)),1000000000000),IF((INDEX(T1_Rente,7)-0.005+0.000005)&gt;Berekening!M10,(Berekening!M45-(INDEX(T1_Rente,7)-0.005+0.000005)*Berekening!M46)/(360*((INDEX(T1_Rente,7)-0.005+0.000005)-Berekening!M10)),1000000000000))</f>
-        <v>-1086773226.34509</v>
+        <v>4378947.85667018</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13289,15 +13289,15 @@
       </c>
       <c r="G42" s="29" t="n">
         <f aca="false">IF(G40&gt;G41,-1,IF(G39&lt;G40-0.000000001,-1,IF(G39&gt;G41,MAX(G40,G41-1),G39)))</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H42" s="29" t="n">
         <f aca="false">IF(H40&gt;H41,-1,IF(H39&lt;H40-0.000000001,-1,IF(H39&gt;H41,MAX(H40,H41-1),H39)))</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I42" s="29" t="n">
         <f aca="false">IF(I40&gt;I41,-1,IF(I39&lt;I40-0.000000001,-1,IF(I39&gt;I41,MAX(I40,I41-1),I39)))</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J42" s="29" t="n">
         <f aca="false">IF(J40&gt;J41,-1,IF(J39&lt;J40-0.000000001,-1,IF(J39&gt;J41,MAX(J40,J41-1),J39)))</f>
@@ -13377,39 +13377,39 @@
       </c>
       <c r="C44" s="29" t="n">
         <f aca="false">MAX(0,(C43*C6/12-Berekening!C18-Berekening!C44)*Berekening!C11-Berekening!C75+C7)</f>
-        <v>518142.174545886</v>
+        <v>393501.966276848</v>
       </c>
       <c r="D44" s="29" t="n">
         <f aca="false">MAX(0,(D43*D6/12-Berekening!D18-Berekening!D44)*Berekening!D11-Berekening!D75+D7)</f>
-        <v>549665.623444991</v>
+        <v>422553.518230657</v>
       </c>
       <c r="E44" s="29" t="n">
         <f aca="false">MAX(0,(E43*E6/12-Berekening!E18-Berekening!E44)*Berekening!E11-Berekening!E75+E7)</f>
-        <v>385561.679249296</v>
+        <v>270854.422938313</v>
       </c>
       <c r="F44" s="29" t="n">
         <f aca="false">MAX(0,(F43*F6/12-Berekening!F18-Berekening!F44)*Berekening!F11-Berekening!F75+F7)</f>
-        <v>460587.003261998</v>
+        <v>380082.297761919</v>
       </c>
       <c r="G44" s="29" t="n">
         <f aca="false">MAX(0,(G43*G6/12-Berekening!G18-Berekening!G44)*Berekening!G11-Berekening!G75+G7)</f>
-        <v>279637.32575866</v>
+        <v>259434.811732502</v>
       </c>
       <c r="H44" s="29" t="n">
         <f aca="false">MAX(0,(H43*H6/12-Berekening!H18-Berekening!H44)*Berekening!H11-Berekening!H75+H7)</f>
-        <v>743114.341589683</v>
+        <v>684469.294466147</v>
       </c>
       <c r="I44" s="29" t="n">
         <f aca="false">MAX(0,(I43*I6/12-Berekening!I18-Berekening!I44)*Berekening!I11-Berekening!I75+I7)</f>
-        <v>1119937.42933563</v>
+        <v>946273.873050534</v>
       </c>
       <c r="J44" s="29" t="n">
         <f aca="false">MAX(0,(J43*J6/12-Berekening!J18-Berekening!J44)*Berekening!J11-Berekening!J75+J7)</f>
-        <v>558600.787991435</v>
+        <v>430788.035902492</v>
       </c>
       <c r="K44" s="29" t="n">
         <f aca="false">MAX(0,(K43*K6/12-Berekening!K18-Berekening!K44)*Berekening!K11-Berekening!K75+K7)</f>
-        <v>289222.677894566</v>
+        <v>183119.501315332</v>
       </c>
       <c r="L44" s="29" t="n">
         <f aca="false">MAX(0,(L43*L6/12-Berekening!L18-Berekening!L44)*Berekening!L11-Berekening!L75+L7)</f>
@@ -13417,7 +13417,7 @@
       </c>
       <c r="M44" s="29" t="n">
         <f aca="false">MAX(0,(M43*M6/12-Berekening!M18-Berekening!M44)*Berekening!M11-Berekening!M75+M7)</f>
-        <v>518142.174545886</v>
+        <v>393501.966276848</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13429,11 +13429,11 @@
       </c>
       <c r="C45" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,8)+0.000005)&gt;Berekening!C10,(Berekening!C45-(INDEX(T1_Rente,8)+0.000005)*Berekening!C46)/(360*((INDEX(T1_Rente,8)+0.000005)-Berekening!C10)),IF((INDEX(T1_Rente,8)+0.000005)=Berekening!C10,IF(Berekening!C45-(INDEX(T1_Rente,8)+0.000005)*Berekening!C46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,8)-0.005+0.000005)&lt;Berekening!C10,(Berekening!C45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!C46)/(360*((INDEX(T1_Rente,8)-0.005+0.000005)-Berekening!C10)),IF((INDEX(T1_Rente,8)-0.005+0.000005)=Berekening!C10,IF(Berekening!C45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!C46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>4378947.8566702</v>
       </c>
       <c r="D45" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,8)+0.000005)&gt;Berekening!D10,(Berekening!D45-(INDEX(T1_Rente,8)+0.000005)*Berekening!D46)/(360*((INDEX(T1_Rente,8)+0.000005)-Berekening!D10)),IF((INDEX(T1_Rente,8)+0.000005)=Berekening!D10,IF(Berekening!D45-(INDEX(T1_Rente,8)+0.000005)*Berekening!D46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,8)-0.005+0.000005)&lt;Berekening!D10,(Berekening!D45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!D46)/(360*((INDEX(T1_Rente,8)-0.005+0.000005)-Berekening!D10)),IF((INDEX(T1_Rente,8)-0.005+0.000005)=Berekening!D10,IF(Berekening!D45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!D46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>4244776.36124012</v>
       </c>
       <c r="E45" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,8)+0.000005)&gt;Berekening!E10,(Berekening!E45-(INDEX(T1_Rente,8)+0.000005)*Berekening!E46)/(360*((INDEX(T1_Rente,8)+0.000005)-Berekening!E10)),IF((INDEX(T1_Rente,8)+0.000005)=Berekening!E10,IF(Berekening!E45-(INDEX(T1_Rente,8)+0.000005)*Berekening!E46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,8)-0.005+0.000005)&lt;Berekening!E10,(Berekening!E45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!E46)/(360*((INDEX(T1_Rente,8)-0.005+0.000005)-Berekening!E10)),IF((INDEX(T1_Rente,8)-0.005+0.000005)=Berekening!E10,IF(Berekening!E45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!E46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
@@ -13445,19 +13445,19 @@
       </c>
       <c r="G45" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,8)+0.000005)&gt;Berekening!G10,(Berekening!G45-(INDEX(T1_Rente,8)+0.000005)*Berekening!G46)/(360*((INDEX(T1_Rente,8)+0.000005)-Berekening!G10)),IF((INDEX(T1_Rente,8)+0.000005)=Berekening!G10,IF(Berekening!G45-(INDEX(T1_Rente,8)+0.000005)*Berekening!G46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,8)-0.005+0.000005)&lt;Berekening!G10,(Berekening!G45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!G46)/(360*((INDEX(T1_Rente,8)-0.005+0.000005)-Berekening!G10)),IF((INDEX(T1_Rente,8)-0.005+0.000005)=Berekening!G10,IF(Berekening!G45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!G46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H45" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,8)+0.000005)&gt;Berekening!H10,(Berekening!H45-(INDEX(T1_Rente,8)+0.000005)*Berekening!H46)/(360*((INDEX(T1_Rente,8)+0.000005)-Berekening!H10)),IF((INDEX(T1_Rente,8)+0.000005)=Berekening!H10,IF(Berekening!H45-(INDEX(T1_Rente,8)+0.000005)*Berekening!H46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,8)-0.005+0.000005)&lt;Berekening!H10,(Berekening!H45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!H46)/(360*((INDEX(T1_Rente,8)-0.005+0.000005)-Berekening!H10)),IF((INDEX(T1_Rente,8)-0.005+0.000005)=Berekening!H10,IF(Berekening!H45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!H46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I45" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,8)+0.000005)&gt;Berekening!I10,(Berekening!I45-(INDEX(T1_Rente,8)+0.000005)*Berekening!I46)/(360*((INDEX(T1_Rente,8)+0.000005)-Berekening!I10)),IF((INDEX(T1_Rente,8)+0.000005)=Berekening!I10,IF(Berekening!I45-(INDEX(T1_Rente,8)+0.000005)*Berekening!I46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,8)-0.005+0.000005)&lt;Berekening!I10,(Berekening!I45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!I46)/(360*((INDEX(T1_Rente,8)-0.005+0.000005)-Berekening!I10)),IF((INDEX(T1_Rente,8)-0.005+0.000005)=Berekening!I10,IF(Berekening!I45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!I46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J45" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,8)+0.000005)&gt;Berekening!J10,(Berekening!J45-(INDEX(T1_Rente,8)+0.000005)*Berekening!J46)/(360*((INDEX(T1_Rente,8)+0.000005)-Berekening!J10)),IF((INDEX(T1_Rente,8)+0.000005)=Berekening!J10,IF(Berekening!J45-(INDEX(T1_Rente,8)+0.000005)*Berekening!J46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,8)-0.005+0.000005)&lt;Berekening!J10,(Berekening!J45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!J46)/(360*((INDEX(T1_Rente,8)-0.005+0.000005)-Berekening!J10)),IF((INDEX(T1_Rente,8)-0.005+0.000005)=Berekening!J10,IF(Berekening!J45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!J46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>4378947.8566702</v>
       </c>
       <c r="K45" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,8)+0.000005)&gt;Berekening!K10,(Berekening!K45-(INDEX(T1_Rente,8)+0.000005)*Berekening!K46)/(360*((INDEX(T1_Rente,8)+0.000005)-Berekening!K10)),IF((INDEX(T1_Rente,8)+0.000005)=Berekening!K10,IF(Berekening!K45-(INDEX(T1_Rente,8)+0.000005)*Berekening!K46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,8)-0.005+0.000005)&lt;Berekening!K10,(Berekening!K45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!K46)/(360*((INDEX(T1_Rente,8)-0.005+0.000005)-Berekening!K10)),IF((INDEX(T1_Rente,8)-0.005+0.000005)=Berekening!K10,IF(Berekening!K45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!K46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
@@ -13465,11 +13465,11 @@
       </c>
       <c r="L45" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,8)+0.000005)&gt;Berekening!L10,(Berekening!L45-(INDEX(T1_Rente,8)+0.000005)*Berekening!L46)/(360*((INDEX(T1_Rente,8)+0.000005)-Berekening!L10)),IF((INDEX(T1_Rente,8)+0.000005)=Berekening!L10,IF(Berekening!L45-(INDEX(T1_Rente,8)+0.000005)*Berekening!L46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,8)-0.005+0.000005)&lt;Berekening!L10,(Berekening!L45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!L46)/(360*((INDEX(T1_Rente,8)-0.005+0.000005)-Berekening!L10)),IF((INDEX(T1_Rente,8)-0.005+0.000005)=Berekening!L10,IF(Berekening!L45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!L46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>4378947.8566702</v>
       </c>
       <c r="M45" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T1_Rente,8)+0.000005)&gt;Berekening!M10,(Berekening!M45-(INDEX(T1_Rente,8)+0.000005)*Berekening!M46)/(360*((INDEX(T1_Rente,8)+0.000005)-Berekening!M10)),IF((INDEX(T1_Rente,8)+0.000005)=Berekening!M10,IF(Berekening!M45-(INDEX(T1_Rente,8)+0.000005)*Berekening!M46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T1_Rente,8)-0.005+0.000005)&lt;Berekening!M10,(Berekening!M45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!M46)/(360*((INDEX(T1_Rente,8)-0.005+0.000005)-Berekening!M10)),IF((INDEX(T1_Rente,8)-0.005+0.000005)=Berekening!M10,IF(Berekening!M45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!M46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>4378947.8566702</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13481,15 +13481,15 @@
       </c>
       <c r="C46" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,8)+0.000005)&lt;Berekening!C10,(Berekening!C45-(INDEX(T1_Rente,8)+0.000005)*Berekening!C46)/(360*((INDEX(T1_Rente,8)+0.000005)-Berekening!C10)),1000000000000),IF((INDEX(T1_Rente,8)-0.005+0.000005)&gt;Berekening!C10,(Berekening!C45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!C46)/(360*((INDEX(T1_Rente,8)-0.005+0.000005)-Berekening!C10)),1000000000000))</f>
-        <v>-1657963.2744036</v>
+        <v>1000000000000</v>
       </c>
       <c r="D46" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,8)+0.000005)&lt;Berekening!D10,(Berekening!D45-(INDEX(T1_Rente,8)+0.000005)*Berekening!D46)/(360*((INDEX(T1_Rente,8)+0.000005)-Berekening!D10)),1000000000000),IF((INDEX(T1_Rente,8)-0.005+0.000005)&gt;Berekening!D10,(Berekening!D45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!D46)/(360*((INDEX(T1_Rente,8)-0.005+0.000005)-Berekening!D10)),1000000000000))</f>
-        <v>-1607163.07783217</v>
+        <v>1000000000000</v>
       </c>
       <c r="E46" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,8)+0.000005)&lt;Berekening!E10,(Berekening!E45-(INDEX(T1_Rente,8)+0.000005)*Berekening!E46)/(360*((INDEX(T1_Rente,8)+0.000005)-Berekening!E10)),1000000000000),IF((INDEX(T1_Rente,8)-0.005+0.000005)&gt;Berekening!E10,(Berekening!E45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!E46)/(360*((INDEX(T1_Rente,8)-0.005+0.000005)-Berekening!E10)),1000000000000))</f>
-        <v>571703.459862137</v>
+        <v>1000000000000</v>
       </c>
       <c r="F46" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,8)+0.000005)&lt;Berekening!F10,(Berekening!F45-(INDEX(T1_Rente,8)+0.000005)*Berekening!F46)/(360*((INDEX(T1_Rente,8)+0.000005)-Berekening!F10)),1000000000000),IF((INDEX(T1_Rente,8)-0.005+0.000005)&gt;Berekening!F10,(Berekening!F45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!F46)/(360*((INDEX(T1_Rente,8)-0.005+0.000005)-Berekening!F10)),1000000000000))</f>
@@ -13497,31 +13497,31 @@
       </c>
       <c r="G46" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,8)+0.000005)&lt;Berekening!G10,(Berekening!G45-(INDEX(T1_Rente,8)+0.000005)*Berekening!G46)/(360*((INDEX(T1_Rente,8)+0.000005)-Berekening!G10)),1000000000000),IF((INDEX(T1_Rente,8)-0.005+0.000005)&gt;Berekening!G10,(Berekening!G45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!G46)/(360*((INDEX(T1_Rente,8)-0.005+0.000005)-Berekening!G10)),1000000000000))</f>
-        <v>0</v>
+        <v>1000000000000</v>
       </c>
       <c r="H46" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,8)+0.000005)&lt;Berekening!H10,(Berekening!H45-(INDEX(T1_Rente,8)+0.000005)*Berekening!H46)/(360*((INDEX(T1_Rente,8)+0.000005)-Berekening!H10)),1000000000000),IF((INDEX(T1_Rente,8)-0.005+0.000005)&gt;Berekening!H10,(Berekening!H45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!H46)/(360*((INDEX(T1_Rente,8)-0.005+0.000005)-Berekening!H10)),1000000000000))</f>
-        <v>0</v>
+        <v>1000000000000</v>
       </c>
       <c r="I46" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,8)+0.000005)&lt;Berekening!I10,(Berekening!I45-(INDEX(T1_Rente,8)+0.000005)*Berekening!I46)/(360*((INDEX(T1_Rente,8)+0.000005)-Berekening!I10)),1000000000000),IF((INDEX(T1_Rente,8)-0.005+0.000005)&gt;Berekening!I10,(Berekening!I45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!I46)/(360*((INDEX(T1_Rente,8)-0.005+0.000005)-Berekening!I10)),1000000000000))</f>
-        <v>0</v>
+        <v>1000000000000</v>
       </c>
       <c r="J46" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,8)+0.000005)&lt;Berekening!J10,(Berekening!J45-(INDEX(T1_Rente,8)+0.000005)*Berekening!J46)/(360*((INDEX(T1_Rente,8)+0.000005)-Berekening!J10)),1000000000000),IF((INDEX(T1_Rente,8)-0.005+0.000005)&gt;Berekening!J10,(Berekening!J45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!J46)/(360*((INDEX(T1_Rente,8)-0.005+0.000005)-Berekening!J10)),1000000000000))</f>
-        <v>-1657963.2744036</v>
+        <v>1000000000000</v>
       </c>
       <c r="K46" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,8)+0.000005)&lt;Berekening!K10,(Berekening!K45-(INDEX(T1_Rente,8)+0.000005)*Berekening!K46)/(360*((INDEX(T1_Rente,8)+0.000005)-Berekening!K10)),1000000000000),IF((INDEX(T1_Rente,8)-0.005+0.000005)&gt;Berekening!K10,(Berekening!K45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!K46)/(360*((INDEX(T1_Rente,8)-0.005+0.000005)-Berekening!K10)),1000000000000))</f>
-        <v>473496.503496503</v>
+        <v>1000000000000</v>
       </c>
       <c r="L46" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,8)+0.000005)&lt;Berekening!L10,(Berekening!L45-(INDEX(T1_Rente,8)+0.000005)*Berekening!L46)/(360*((INDEX(T1_Rente,8)+0.000005)-Berekening!L10)),1000000000000),IF((INDEX(T1_Rente,8)-0.005+0.000005)&gt;Berekening!L10,(Berekening!L45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!L46)/(360*((INDEX(T1_Rente,8)-0.005+0.000005)-Berekening!L10)),1000000000000))</f>
-        <v>-1657963.2744036</v>
+        <v>1000000000000</v>
       </c>
       <c r="M46" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,8)+0.000005)&lt;Berekening!M10,(Berekening!M45-(INDEX(T1_Rente,8)+0.000005)*Berekening!M46)/(360*((INDEX(T1_Rente,8)+0.000005)-Berekening!M10)),1000000000000),IF((INDEX(T1_Rente,8)-0.005+0.000005)&gt;Berekening!M10,(Berekening!M45-(INDEX(T1_Rente,8)-0.005+0.000005)*Berekening!M46)/(360*((INDEX(T1_Rente,8)-0.005+0.000005)-Berekening!M10)),1000000000000))</f>
-        <v>-1657963.2744036</v>
+        <v>1000000000000</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="E47" s="29" t="n">
         <f aca="false">IF(E45&gt;E46,-1,IF(E44&lt;E45-0.000000001,-1,IF(E44&gt;E46,MAX(E45,E46-1),E44)))</f>
-        <v>385561.679249296</v>
+        <v>270854.422938313</v>
       </c>
       <c r="F47" s="29" t="n">
         <f aca="false">IF(F45&gt;F46,-1,IF(F44&lt;F45-0.000000001,-1,IF(F44&gt;F46,MAX(F45,F46-1),F44)))</f>
@@ -13549,15 +13549,15 @@
       </c>
       <c r="G47" s="29" t="n">
         <f aca="false">IF(G45&gt;G46,-1,IF(G44&lt;G45-0.000000001,-1,IF(G44&gt;G46,MAX(G45,G46-1),G44)))</f>
-        <v>0</v>
+        <v>259434.811732502</v>
       </c>
       <c r="H47" s="29" t="n">
         <f aca="false">IF(H45&gt;H46,-1,IF(H44&lt;H45-0.000000001,-1,IF(H44&gt;H46,MAX(H45,H46-1),H44)))</f>
-        <v>0</v>
+        <v>684469.294466147</v>
       </c>
       <c r="I47" s="29" t="n">
         <f aca="false">IF(I45&gt;I46,-1,IF(I44&lt;I45-0.000000001,-1,IF(I44&gt;I46,MAX(I45,I46-1),I44)))</f>
-        <v>0</v>
+        <v>946273.873050534</v>
       </c>
       <c r="J47" s="29" t="n">
         <f aca="false">IF(J45&gt;J46,-1,IF(J44&lt;J45-0.000000001,-1,IF(J44&gt;J46,MAX(J45,J46-1),J44)))</f>
@@ -13565,7 +13565,7 @@
       </c>
       <c r="K47" s="29" t="n">
         <f aca="false">IF(K45&gt;K46,-1,IF(K44&lt;K45-0.000000001,-1,IF(K44&gt;K46,MAX(K45,K46-1),K44)))</f>
-        <v>289222.677894566</v>
+        <v>183119.501315332</v>
       </c>
       <c r="L47" s="29" t="n">
         <f aca="false">IF(L45&gt;L46,-1,IF(L44&lt;L45-0.000000001,-1,IF(L44&gt;L46,MAX(L45,L46-1),L44)))</f>
@@ -13637,39 +13637,39 @@
       </c>
       <c r="C49" s="29" t="n">
         <f aca="false">MAX(0,(C48*C6/12-Berekening!C18-Berekening!C44)*Berekening!C11-Berekening!C75+C7)</f>
-        <v>550678.487229771</v>
+        <v>422457.431122275</v>
       </c>
       <c r="D49" s="29" t="n">
         <f aca="false">MAX(0,(D48*D6/12-Berekening!D18-Berekening!D44)*Berekening!D11-Berekening!D75+D7)</f>
-        <v>582201.936128875</v>
+        <v>451508.983076084</v>
       </c>
       <c r="E49" s="29" t="n">
         <f aca="false">MAX(0,(E48*E6/12-Berekening!E18-Berekening!E44)*Berekening!E11-Berekening!E75+E7)</f>
-        <v>418097.991933181</v>
+        <v>299809.88778374</v>
       </c>
       <c r="F49" s="29" t="n">
         <f aca="false">MAX(0,(F48*F6/12-Berekening!F18-Berekening!F44)*Berekening!F11-Berekening!F75+F7)</f>
-        <v>489522.747776489</v>
+        <v>408024.540318831</v>
       </c>
       <c r="G49" s="29" t="n">
         <f aca="false">MAX(0,(G48*G6/12-Berekening!G18-Berekening!G44)*Berekening!G11-Berekening!G75+G7)</f>
-        <v>289063.081579099</v>
+        <v>268121.45118613</v>
       </c>
       <c r="H49" s="29" t="n">
         <f aca="false">MAX(0,(H48*H6/12-Berekening!H18-Berekening!H44)*Berekening!H11-Berekening!H75+H7)</f>
-        <v>764060.465635102</v>
+        <v>703772.937696431</v>
       </c>
       <c r="I49" s="29" t="n">
         <f aca="false">MAX(0,(I48*I6/12-Berekening!I18-Berekening!I44)*Berekening!I11-Berekening!I75+I7)</f>
-        <v>1152473.74201952</v>
+        <v>975229.337895961</v>
       </c>
       <c r="J49" s="29" t="n">
         <f aca="false">MAX(0,(J48*J6/12-Berekening!J18-Berekening!J44)*Berekening!J11-Berekening!J75+J7)</f>
-        <v>591137.10067532</v>
+        <v>459743.500747919</v>
       </c>
       <c r="K49" s="29" t="n">
         <f aca="false">MAX(0,(K48*K6/12-Berekening!K18-Berekening!K44)*Berekening!K11-Berekening!K75+K7)</f>
-        <v>321758.990578451</v>
+        <v>212074.966160759</v>
       </c>
       <c r="L49" s="29" t="n">
         <f aca="false">MAX(0,(L48*L6/12-Berekening!L18-Berekening!L44)*Berekening!L11-Berekening!L75+L7)</f>
@@ -13677,7 +13677,7 @@
       </c>
       <c r="M49" s="29" t="n">
         <f aca="false">MAX(0,(M48*M6/12-Berekening!M18-Berekening!M44)*Berekening!M11-Berekening!M75+M7)</f>
-        <v>550678.487229771</v>
+        <v>422457.431122275</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13741,15 +13741,15 @@
       </c>
       <c r="C51" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,9)+0.000005)&lt;Berekening!C10,(Berekening!C45-(INDEX(T1_Rente,9)+0.000005)*Berekening!C46)/(360*((INDEX(T1_Rente,9)+0.000005)-Berekening!C10)),1000000000000),IF((INDEX(T1_Rente,9)-0.005+0.000005)&gt;Berekening!C10,(Berekening!C45-(INDEX(T1_Rente,9)-0.005+0.000005)*Berekening!C46)/(360*((INDEX(T1_Rente,9)-0.005+0.000005)-Berekening!C10)),1000000000000))</f>
-        <v>-1115676.78611261</v>
+        <v>-3594958.53302952</v>
       </c>
       <c r="D51" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,9)+0.000005)&lt;Berekening!D10,(Berekening!D45-(INDEX(T1_Rente,9)+0.000005)*Berekening!D46)/(360*((INDEX(T1_Rente,9)+0.000005)-Berekening!D10)),1000000000000),IF((INDEX(T1_Rente,9)-0.005+0.000005)&gt;Berekening!D10,(Berekening!D45-(INDEX(T1_Rente,9)-0.005+0.000005)*Berekening!D46)/(360*((INDEX(T1_Rente,9)-0.005+0.000005)-Berekening!D10)),1000000000000))</f>
-        <v>-1115702.22434283</v>
+        <v>-3595040.50066022</v>
       </c>
       <c r="E51" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,9)+0.000005)&lt;Berekening!E10,(Berekening!E45-(INDEX(T1_Rente,9)+0.000005)*Berekening!E46)/(360*((INDEX(T1_Rente,9)+0.000005)-Berekening!E10)),1000000000000),IF((INDEX(T1_Rente,9)-0.005+0.000005)&gt;Berekening!E10,(Berekening!E45-(INDEX(T1_Rente,9)-0.005+0.000005)*Berekening!E46)/(360*((INDEX(T1_Rente,9)-0.005+0.000005)-Berekening!E10)),1000000000000))</f>
-        <v>-286.280865234338</v>
+        <v>-922.460565755087</v>
       </c>
       <c r="F51" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,9)+0.000005)&lt;Berekening!F10,(Berekening!F45-(INDEX(T1_Rente,9)+0.000005)*Berekening!F46)/(360*((INDEX(T1_Rente,9)+0.000005)-Berekening!F10)),1000000000000),IF((INDEX(T1_Rente,9)-0.005+0.000005)&gt;Berekening!F10,(Berekening!F45-(INDEX(T1_Rente,9)-0.005+0.000005)*Berekening!F46)/(360*((INDEX(T1_Rente,9)-0.005+0.000005)-Berekening!F10)),1000000000000))</f>
@@ -13769,19 +13769,19 @@
       </c>
       <c r="J51" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,9)+0.000005)&lt;Berekening!J10,(Berekening!J45-(INDEX(T1_Rente,9)+0.000005)*Berekening!J46)/(360*((INDEX(T1_Rente,9)+0.000005)-Berekening!J10)),1000000000000),IF((INDEX(T1_Rente,9)-0.005+0.000005)&gt;Berekening!J10,(Berekening!J45-(INDEX(T1_Rente,9)-0.005+0.000005)*Berekening!J46)/(360*((INDEX(T1_Rente,9)-0.005+0.000005)-Berekening!J10)),1000000000000))</f>
-        <v>-1115676.78611261</v>
+        <v>-3594958.53302952</v>
       </c>
       <c r="K51" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,9)+0.000005)&lt;Berekening!K10,(Berekening!K45-(INDEX(T1_Rente,9)+0.000005)*Berekening!K46)/(360*((INDEX(T1_Rente,9)+0.000005)-Berekening!K10)),1000000000000),IF((INDEX(T1_Rente,9)-0.005+0.000005)&gt;Berekening!K10,(Berekening!K45-(INDEX(T1_Rente,9)-0.005+0.000005)*Berekening!K46)/(360*((INDEX(T1_Rente,9)-0.005+0.000005)-Berekening!K10)),1000000000000))</f>
-        <v>-237.103670387029</v>
+        <v>-764.000715691536</v>
       </c>
       <c r="L51" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,9)+0.000005)&lt;Berekening!L10,(Berekening!L45-(INDEX(T1_Rente,9)+0.000005)*Berekening!L46)/(360*((INDEX(T1_Rente,9)+0.000005)-Berekening!L10)),1000000000000),IF((INDEX(T1_Rente,9)-0.005+0.000005)&gt;Berekening!L10,(Berekening!L45-(INDEX(T1_Rente,9)-0.005+0.000005)*Berekening!L46)/(360*((INDEX(T1_Rente,9)-0.005+0.000005)-Berekening!L10)),1000000000000))</f>
-        <v>-1115676.78611261</v>
+        <v>-3594958.53302952</v>
       </c>
       <c r="M51" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,9)+0.000005)&lt;Berekening!M10,(Berekening!M45-(INDEX(T1_Rente,9)+0.000005)*Berekening!M46)/(360*((INDEX(T1_Rente,9)+0.000005)-Berekening!M10)),1000000000000),IF((INDEX(T1_Rente,9)-0.005+0.000005)&gt;Berekening!M10,(Berekening!M45-(INDEX(T1_Rente,9)-0.005+0.000005)*Berekening!M46)/(360*((INDEX(T1_Rente,9)-0.005+0.000005)-Berekening!M10)),1000000000000))</f>
-        <v>-1115676.78611261</v>
+        <v>-3594958.53302952</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13897,39 +13897,39 @@
       </c>
       <c r="C54" s="29" t="n">
         <f aca="false">MAX(0,(C53*C6/12-Berekening!C18-Berekening!C44)*Berekening!C11-Berekening!C75+C7)</f>
-        <v>583214.799913655</v>
+        <v>451412.895967702</v>
       </c>
       <c r="D54" s="29" t="n">
         <f aca="false">MAX(0,(D53*D6/12-Berekening!D18-Berekening!D44)*Berekening!D11-Berekening!D75+D7)</f>
-        <v>614738.24881276</v>
+        <v>480464.447921511</v>
       </c>
       <c r="E54" s="29" t="n">
         <f aca="false">MAX(0,(E53*E6/12-Berekening!E18-Berekening!E44)*Berekening!E11-Berekening!E75+E7)</f>
-        <v>450634.304617066</v>
+        <v>328765.352629168</v>
       </c>
       <c r="F54" s="29" t="n">
         <f aca="false">MAX(0,(F53*F6/12-Berekening!F18-Berekening!F44)*Berekening!F11-Berekening!F75+F7)</f>
-        <v>518458.492290979</v>
+        <v>435966.782875742</v>
       </c>
       <c r="G54" s="29" t="n">
         <f aca="false">MAX(0,(G53*G6/12-Berekening!G18-Berekening!G44)*Berekening!G11-Berekening!G75+G7)</f>
-        <v>298488.837399538</v>
+        <v>276808.090639758</v>
       </c>
       <c r="H54" s="29" t="n">
         <f aca="false">MAX(0,(H53*H6/12-Berekening!H18-Berekening!H44)*Berekening!H11-Berekening!H75+H7)</f>
-        <v>785006.589680522</v>
+        <v>723076.580926716</v>
       </c>
       <c r="I54" s="29" t="n">
         <f aca="false">MAX(0,(I53*I6/12-Berekening!I18-Berekening!I44)*Berekening!I11-Berekening!I75+I7)</f>
-        <v>1185010.0547034</v>
+        <v>1004184.80274139</v>
       </c>
       <c r="J54" s="29" t="n">
         <f aca="false">MAX(0,(J53*J6/12-Berekening!J18-Berekening!J44)*Berekening!J11-Berekening!J75+J7)</f>
-        <v>623673.413359205</v>
+        <v>488698.965593346</v>
       </c>
       <c r="K54" s="29" t="n">
         <f aca="false">MAX(0,(K53*K6/12-Berekening!K18-Berekening!K44)*Berekening!K11-Berekening!K75+K7)</f>
-        <v>354295.303262336</v>
+        <v>241030.431006186</v>
       </c>
       <c r="L54" s="29" t="n">
         <f aca="false">MAX(0,(L53*L6/12-Berekening!L18-Berekening!L44)*Berekening!L11-Berekening!L75+L7)</f>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="M54" s="29" t="n">
         <f aca="false">MAX(0,(M53*M6/12-Berekening!M18-Berekening!M44)*Berekening!M11-Berekening!M75+M7)</f>
-        <v>583214.799913655</v>
+        <v>451412.895967702</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14001,15 +14001,15 @@
       </c>
       <c r="C56" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,10)-0.005+0.000005)&gt;Berekening!C10,(Berekening!C45-(INDEX(T1_Rente,10)-0.005+0.000005)*Berekening!C46)/(360*((INDEX(T1_Rente,10)-0.005+0.000005)-Berekening!C10)),1000000000000))</f>
-        <v>-934794.155396424</v>
+        <v>-1730609.04401275</v>
       </c>
       <c r="D56" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,10)-0.005+0.000005)&gt;Berekening!D10,(Berekening!D45-(INDEX(T1_Rente,10)-0.005+0.000005)*Berekening!D46)/(360*((INDEX(T1_Rente,10)-0.005+0.000005)-Berekening!D10)),1000000000000))</f>
-        <v>-951772.762715762</v>
+        <v>-1762041.98698951</v>
       </c>
       <c r="E56" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,10)-0.005+0.000005)&gt;Berekening!E10,(Berekening!E45-(INDEX(T1_Rente,10)-0.005+0.000005)*Berekening!E46)/(360*((INDEX(T1_Rente,10)-0.005+0.000005)-Berekening!E10)),1000000000000))</f>
-        <v>-191076.594250139</v>
+        <v>-353745.132229899</v>
       </c>
       <c r="F56" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,10)-0.005+0.000005)&gt;Berekening!F10,(Berekening!F45-(INDEX(T1_Rente,10)-0.005+0.000005)*Berekening!F46)/(360*((INDEX(T1_Rente,10)-0.005+0.000005)-Berekening!F10)),1000000000000))</f>
@@ -14029,19 +14029,19 @@
       </c>
       <c r="J56" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,10)-0.005+0.000005)&gt;Berekening!J10,(Berekening!J45-(INDEX(T1_Rente,10)-0.005+0.000005)*Berekening!J46)/(360*((INDEX(T1_Rente,10)-0.005+0.000005)-Berekening!J10)),1000000000000))</f>
-        <v>-934794.155396424</v>
+        <v>-1730609.04401275</v>
       </c>
       <c r="K56" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,10)-0.005+0.000005)&gt;Berekening!K10,(Berekening!K45-(INDEX(T1_Rente,10)-0.005+0.000005)*Berekening!K46)/(360*((INDEX(T1_Rente,10)-0.005+0.000005)-Berekening!K10)),1000000000000))</f>
-        <v>-158253.545114591</v>
+        <v>-292978.956748235</v>
       </c>
       <c r="L56" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,10)-0.005+0.000005)&gt;Berekening!L10,(Berekening!L45-(INDEX(T1_Rente,10)-0.005+0.000005)*Berekening!L46)/(360*((INDEX(T1_Rente,10)-0.005+0.000005)-Berekening!L10)),1000000000000))</f>
-        <v>-934794.155396424</v>
+        <v>-1730609.04401275</v>
       </c>
       <c r="M56" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T1_Rente,10)-0.005+0.000005)&gt;Berekening!M10,(Berekening!M45-(INDEX(T1_Rente,10)-0.005+0.000005)*Berekening!M46)/(360*((INDEX(T1_Rente,10)-0.005+0.000005)-Berekening!M10)),1000000000000))</f>
-        <v>-934794.155396424</v>
+        <v>-1730609.04401275</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14105,39 +14105,39 @@
       </c>
       <c r="C58" s="35" t="n">
         <f aca="false">MAX(0,C12,C17,C22,C27,C32,C37,C42,C47,C52,C57)</f>
-        <v>406298.599695031</v>
+        <v>328352.170374638</v>
       </c>
       <c r="D58" s="35" t="n">
         <f aca="false">MAX(0,D12,D17,D22,D27,D32,D37,D42,D47,D52,D57)</f>
-        <v>476458.919906249</v>
+        <v>357403.722328447</v>
       </c>
       <c r="E58" s="35" t="n">
         <f aca="false">MAX(0,E12,E17,E22,E27,E32,E37,E42,E47,E52,E57)</f>
-        <v>385561.679249296</v>
+        <v>270854.422938313</v>
       </c>
       <c r="F58" s="35" t="n">
         <f aca="false">MAX(0,F12,F17,F22,F27,F32,F37,F42,F47,F52,F57)</f>
-        <v>395481.578104395</v>
+        <v>317212.252008869</v>
       </c>
       <c r="G58" s="35" t="n">
         <f aca="false">MAX(0,G12,G17,G22,G27,G32,G37,G42,G47,G52,G57)</f>
-        <v>258691.20171324</v>
+        <v>259434.811732502</v>
       </c>
       <c r="H58" s="35" t="n">
         <f aca="false">MAX(0,H12,H17,H22,H27,H32,H37,H42,H47,H52,H57)</f>
-        <v>695985.562487489</v>
+        <v>684469.294466147</v>
       </c>
       <c r="I58" s="35" t="n">
         <f aca="false">MAX(0,I12,I17,I22,I27,I32,I37,I42,I47,I52,I57)</f>
-        <v>1046730.72579689</v>
+        <v>946273.873050534</v>
       </c>
       <c r="J58" s="35" t="n">
         <f aca="false">MAX(0,J12,J17,J22,J27,J32,J37,J42,J47,J52,J57)</f>
-        <v>446757.21314058</v>
+        <v>365638.240000281</v>
       </c>
       <c r="K58" s="35" t="n">
         <f aca="false">MAX(0,K12,K17,K22,K27,K32,K37,K42,K47,K52,K57)</f>
-        <v>289222.677894566</v>
+        <v>183119.501315332</v>
       </c>
       <c r="L58" s="35" t="n">
         <f aca="false">MAX(0,L12,L17,L22,L27,L32,L37,L42,L47,L52,L57)</f>
@@ -14145,7 +14145,7 @@
       </c>
       <c r="M58" s="35" t="n">
         <f aca="false">MAX(0,M12,M17,M22,M27,M32,M37,M42,M47,M52,M57)</f>
-        <v>406298.599695031</v>
+        <v>328352.170374638</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14174,19 +14174,19 @@
       </c>
       <c r="C60" s="29" t="n">
         <f aca="false">Berekening!C93</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="D60" s="29" t="n">
         <f aca="false">Berekening!D93</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="E60" s="29" t="n">
         <f aca="false">Berekening!E93</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="F60" s="29" t="n">
         <f aca="false">Berekening!F93</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="G60" s="29" t="n">
         <f aca="false">Berekening!G93</f>
@@ -14198,23 +14198,23 @@
       </c>
       <c r="I60" s="29" t="n">
         <f aca="false">Berekening!I93</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="J60" s="29" t="n">
         <f aca="false">Berekening!J93</f>
-        <v>155000</v>
+        <v>147000</v>
       </c>
       <c r="K60" s="29" t="n">
         <f aca="false">Berekening!K93</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="L60" s="29" t="n">
         <f aca="false">Berekening!L93</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="M60" s="29" t="n">
         <f aca="false">Berekening!M93</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14330,39 +14330,39 @@
       </c>
       <c r="C63" s="29" t="n">
         <f aca="false">MAX(0,(C62*C60/12-Berekening!C18-Berekening!C44)*Berekening!C11-Berekening!C75+C61)</f>
-        <v>485605.861862001</v>
+        <v>364546.501431421</v>
       </c>
       <c r="D63" s="29" t="n">
         <f aca="false">MAX(0,(D62*D60/12-Berekening!D18-Berekening!D44)*Berekening!D11-Berekening!D75+D61)</f>
-        <v>517129.310761105</v>
+        <v>393598.05338523</v>
       </c>
       <c r="E63" s="29" t="n">
         <f aca="false">MAX(0,(E62*E60/12-Berekening!E18-Berekening!E44)*Berekening!E11-Berekening!E75+E61)</f>
-        <v>353025.366565411</v>
+        <v>241898.958092886</v>
       </c>
       <c r="F63" s="29" t="n">
         <f aca="false">MAX(0,(F62*F60/12-Berekening!F18-Berekening!F44)*Berekening!F11-Berekening!F75+F61)</f>
-        <v>431651.258747508</v>
+        <v>352140.055205008</v>
       </c>
       <c r="G63" s="29" t="n">
         <f aca="false">MAX(0,(G62*G60/12-Berekening!G18-Berekening!G44)*Berekening!G11-Berekening!G75+G61)</f>
-        <v>289063.081579099</v>
+        <v>268121.45118613</v>
       </c>
       <c r="H63" s="29" t="n">
         <f aca="false">MAX(0,(H62*H60/12-Berekening!H18-Berekening!H44)*Berekening!H11-Berekening!H75+H61)</f>
-        <v>722168.217544263</v>
+        <v>665165.651235862</v>
       </c>
       <c r="I63" s="29" t="n">
         <f aca="false">MAX(0,(I62*I60/12-Berekening!I18-Berekening!I44)*Berekening!I11-Berekening!I75+I61)</f>
-        <v>1087401.11665175</v>
+        <v>917318.408205107</v>
       </c>
       <c r="J63" s="29" t="n">
         <f aca="false">MAX(0,(J62*J60/12-Berekening!J18-Berekening!J44)*Berekening!J11-Berekening!J75+J61)</f>
-        <v>139399.025429105</v>
+        <v>45487.3170260096</v>
       </c>
       <c r="K63" s="29" t="n">
         <f aca="false">MAX(0,(K62*K60/12-Berekening!K18-Berekening!K44)*Berekening!K11-Berekening!K75+K61)</f>
-        <v>256686.365210681</v>
+        <v>154164.036469905</v>
       </c>
       <c r="L63" s="29" t="n">
         <f aca="false">MAX(0,(L62*L60/12-Berekening!L18-Berekening!L44)*Berekening!L11-Berekening!L75+L61)</f>
@@ -14370,7 +14370,7 @@
       </c>
       <c r="M63" s="29" t="n">
         <f aca="false">MAX(0,(M62*M60/12-Berekening!M18-Berekening!M44)*Berekening!M11-Berekening!M75+M61)</f>
-        <v>485605.861862001</v>
+        <v>364546.501431421</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14434,15 +14434,15 @@
       </c>
       <c r="C65" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,1)+0.000005)&lt;Berekening!C10,(Berekening!C45-(INDEX(T2_Rente,1)+0.000005)*Berekening!C46)/(360*((INDEX(T2_Rente,1)+0.000005)-Berekening!C10)),1000000000000))</f>
-        <v>-355564.478960192</v>
+        <v>-278643.491193291</v>
       </c>
       <c r="D65" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,1)+0.000005)&lt;Berekening!D10,(Berekening!D45-(INDEX(T2_Rente,1)+0.000005)*Berekening!D46)/(360*((INDEX(T2_Rente,1)+0.000005)-Berekening!D10)),1000000000000))</f>
-        <v>-426831.210060012</v>
+        <v>-334492.744801693</v>
       </c>
       <c r="E65" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,1)+0.000005)&lt;Berekening!E10,(Berekening!E45-(INDEX(T2_Rente,1)+0.000005)*Berekening!E46)/(360*((INDEX(T2_Rente,1)+0.000005)-Berekening!E10)),1000000000000))</f>
-        <v>-802033.052874975</v>
+        <v>-628525.353710926</v>
       </c>
       <c r="F65" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,1)+0.000005)&lt;Berekening!F10,(Berekening!F45-(INDEX(T2_Rente,1)+0.000005)*Berekening!F46)/(360*((INDEX(T2_Rente,1)+0.000005)-Berekening!F10)),1000000000000))</f>
@@ -14462,19 +14462,19 @@
       </c>
       <c r="J65" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,1)+0.000005)&lt;Berekening!J10,(Berekening!J45-(INDEX(T2_Rente,1)+0.000005)*Berekening!J46)/(360*((INDEX(T2_Rente,1)+0.000005)-Berekening!J10)),1000000000000))</f>
-        <v>-355564.478960192</v>
+        <v>-278643.491193291</v>
       </c>
       <c r="K65" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,1)+0.000005)&lt;Berekening!K10,(Berekening!K45-(INDEX(T2_Rente,1)+0.000005)*Berekening!K46)/(360*((INDEX(T2_Rente,1)+0.000005)-Berekening!K10)),1000000000000))</f>
-        <v>-664260.185370407</v>
+        <v>-520557.558656007</v>
       </c>
       <c r="L65" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,1)+0.000005)&lt;Berekening!L10,(Berekening!L45-(INDEX(T2_Rente,1)+0.000005)*Berekening!L46)/(360*((INDEX(T2_Rente,1)+0.000005)-Berekening!L10)),1000000000000))</f>
-        <v>-355564.478960192</v>
+        <v>-278643.491193291</v>
       </c>
       <c r="M65" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,1)+0.000005)&lt;Berekening!M10,(Berekening!M45-(INDEX(T2_Rente,1)+0.000005)*Berekening!M46)/(360*((INDEX(T2_Rente,1)+0.000005)-Berekening!M10)),1000000000000))</f>
-        <v>-355564.478960192</v>
+        <v>-278643.491193291</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14590,39 +14590,39 @@
       </c>
       <c r="C68" s="29" t="n">
         <f aca="false">MAX(0,(C67*C60/12-Berekening!C18-Berekening!C44)*Berekening!C11-Berekening!C75+C61)</f>
-        <v>541188.729363637</v>
+        <v>414012.087209026</v>
       </c>
       <c r="D68" s="29" t="n">
         <f aca="false">MAX(0,(D67*D60/12-Berekening!D18-Berekening!D44)*Berekening!D11-Berekening!D75+D61)</f>
-        <v>572712.178262742</v>
+        <v>443063.639162835</v>
       </c>
       <c r="E68" s="29" t="n">
         <f aca="false">MAX(0,(E67*E60/12-Berekening!E18-Berekening!E44)*Berekening!E11-Berekening!E75+E61)</f>
-        <v>408608.234067048</v>
+        <v>291364.543870491</v>
       </c>
       <c r="F68" s="29" t="n">
         <f aca="false">MAX(0,(F67*F60/12-Berekening!F18-Berekening!F44)*Berekening!F11-Berekening!F75+F61)</f>
-        <v>481083.155626429</v>
+        <v>399874.719573065</v>
       </c>
       <c r="G68" s="29" t="n">
         <f aca="false">MAX(0,(G67*G60/12-Berekening!G18-Berekening!G44)*Berekening!G11-Berekening!G75+G61)</f>
-        <v>304423.57254574</v>
+        <v>282277.456221672</v>
       </c>
       <c r="H68" s="29" t="n">
         <f aca="false">MAX(0,(H67*H60/12-Berekening!H18-Berekening!H44)*Berekening!H11-Berekening!H75+H61)</f>
-        <v>757951.179455188</v>
+        <v>698142.708420932</v>
       </c>
       <c r="I68" s="29" t="n">
         <f aca="false">MAX(0,(I67*I60/12-Berekening!I18-Berekening!I44)*Berekening!I11-Berekening!I75+I61)</f>
-        <v>1142983.98415338</v>
+        <v>966783.993982711</v>
       </c>
       <c r="J68" s="29" t="n">
         <f aca="false">MAX(0,(J67*J60/12-Berekening!J18-Berekening!J44)*Berekening!J11-Berekening!J75+J61)</f>
-        <v>176374.752737061</v>
+        <v>77804.8330673778</v>
       </c>
       <c r="K68" s="29" t="n">
         <f aca="false">MAX(0,(K67*K60/12-Berekening!K18-Berekening!K44)*Berekening!K11-Berekening!K75+K61)</f>
-        <v>312269.232712318</v>
+        <v>203629.62224751</v>
       </c>
       <c r="L68" s="29" t="n">
         <f aca="false">MAX(0,(L67*L60/12-Berekening!L18-Berekening!L44)*Berekening!L11-Berekening!L75+L61)</f>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="M68" s="29" t="n">
         <f aca="false">MAX(0,(M67*M60/12-Berekening!M18-Berekening!M44)*Berekening!M11-Berekening!M75+M61)</f>
-        <v>541188.729363637</v>
+        <v>414012.087209026</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14694,15 +14694,15 @@
       </c>
       <c r="C70" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,2)+0.000005)&lt;Berekening!C10,(Berekening!C45-(INDEX(T2_Rente,2)+0.000005)*Berekening!C46)/(360*((INDEX(T2_Rente,2)+0.000005)-Berekening!C10)),1000000000000),IF((INDEX(T2_Rente,2)-0.005+0.000005)&gt;Berekening!C10,(Berekening!C45-(INDEX(T2_Rente,2)-0.005+0.000005)*Berekening!C46)/(360*((INDEX(T2_Rente,2)-0.005+0.000005)-Berekening!C10)),1000000000000))</f>
-        <v>-301230.012250229</v>
+        <v>-223948.469787817</v>
       </c>
       <c r="D70" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,2)+0.000005)&lt;Berekening!D10,(Berekening!D45-(INDEX(T2_Rente,2)+0.000005)*Berekening!D46)/(360*((INDEX(T2_Rente,2)+0.000005)-Berekening!D10)),1000000000000),IF((INDEX(T2_Rente,2)-0.005+0.000005)&gt;Berekening!D10,(Berekening!D45-(INDEX(T2_Rente,2)-0.005+0.000005)*Berekening!D46)/(360*((INDEX(T2_Rente,2)-0.005+0.000005)-Berekening!D10)),1000000000000))</f>
-        <v>-377589.224578645</v>
+        <v>-280717.477057074</v>
       </c>
       <c r="E70" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,2)+0.000005)&lt;Berekening!E10,(Berekening!E45-(INDEX(T2_Rente,2)+0.000005)*Berekening!E46)/(360*((INDEX(T2_Rente,2)+0.000005)-Berekening!E10)),1000000000000),IF((INDEX(T2_Rente,2)-0.005+0.000005)&gt;Berekening!E10,(Berekening!E45-(INDEX(T2_Rente,2)-0.005+0.000005)*Berekening!E46)/(360*((INDEX(T2_Rente,2)-0.005+0.000005)-Berekening!E10)),1000000000000))</f>
-        <v>-859343.640907393</v>
+        <v>-638876.226062217</v>
       </c>
       <c r="F70" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,2)+0.000005)&lt;Berekening!F10,(Berekening!F45-(INDEX(T2_Rente,2)+0.000005)*Berekening!F46)/(360*((INDEX(T2_Rente,2)+0.000005)-Berekening!F10)),1000000000000),IF((INDEX(T2_Rente,2)-0.005+0.000005)&gt;Berekening!F10,(Berekening!F45-(INDEX(T2_Rente,2)-0.005+0.000005)*Berekening!F46)/(360*((INDEX(T2_Rente,2)-0.005+0.000005)-Berekening!F10)),1000000000000))</f>
@@ -14722,19 +14722,19 @@
       </c>
       <c r="J70" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,2)+0.000005)&lt;Berekening!J10,(Berekening!J45-(INDEX(T2_Rente,2)+0.000005)*Berekening!J46)/(360*((INDEX(T2_Rente,2)+0.000005)-Berekening!J10)),1000000000000),IF((INDEX(T2_Rente,2)-0.005+0.000005)&gt;Berekening!J10,(Berekening!J45-(INDEX(T2_Rente,2)-0.005+0.000005)*Berekening!J46)/(360*((INDEX(T2_Rente,2)-0.005+0.000005)-Berekening!J10)),1000000000000))</f>
-        <v>-301230.012250229</v>
+        <v>-223948.469787817</v>
       </c>
       <c r="K70" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,2)+0.000005)&lt;Berekening!K10,(Berekening!K45-(INDEX(T2_Rente,2)+0.000005)*Berekening!K46)/(360*((INDEX(T2_Rente,2)+0.000005)-Berekening!K10)),1000000000000),IF((INDEX(T2_Rente,2)-0.005+0.000005)&gt;Berekening!K10,(Berekening!K45-(INDEX(T2_Rente,2)-0.005+0.000005)*Berekening!K46)/(360*((INDEX(T2_Rente,2)-0.005+0.000005)-Berekening!K10)),1000000000000))</f>
-        <v>-711725.987052319</v>
+        <v>-529130.362934044</v>
       </c>
       <c r="L70" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,2)+0.000005)&lt;Berekening!L10,(Berekening!L45-(INDEX(T2_Rente,2)+0.000005)*Berekening!L46)/(360*((INDEX(T2_Rente,2)+0.000005)-Berekening!L10)),1000000000000),IF((INDEX(T2_Rente,2)-0.005+0.000005)&gt;Berekening!L10,(Berekening!L45-(INDEX(T2_Rente,2)-0.005+0.000005)*Berekening!L46)/(360*((INDEX(T2_Rente,2)-0.005+0.000005)-Berekening!L10)),1000000000000))</f>
-        <v>-301230.012250229</v>
+        <v>-223948.469787817</v>
       </c>
       <c r="M70" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,2)+0.000005)&lt;Berekening!M10,(Berekening!M45-(INDEX(T2_Rente,2)+0.000005)*Berekening!M46)/(360*((INDEX(T2_Rente,2)+0.000005)-Berekening!M10)),1000000000000),IF((INDEX(T2_Rente,2)-0.005+0.000005)&gt;Berekening!M10,(Berekening!M45-(INDEX(T2_Rente,2)-0.005+0.000005)*Berekening!M46)/(360*((INDEX(T2_Rente,2)-0.005+0.000005)-Berekening!M10)),1000000000000))</f>
-        <v>-301230.012250229</v>
+        <v>-223948.469787817</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14850,39 +14850,39 @@
       </c>
       <c r="C73" s="29" t="n">
         <f aca="false">MAX(0,(C72*C60/12-Berekening!C18-Berekening!C44)*Berekening!C11-Berekening!C75+C61)</f>
-        <v>596771.596865274</v>
+        <v>463477.67298663</v>
       </c>
       <c r="D73" s="29" t="n">
         <f aca="false">MAX(0,(D72*D60/12-Berekening!D18-Berekening!D44)*Berekening!D11-Berekening!D75+D61)</f>
-        <v>628295.045764379</v>
+        <v>492529.224940439</v>
       </c>
       <c r="E73" s="29" t="n">
         <f aca="false">MAX(0,(E72*E60/12-Berekening!E18-Berekening!E44)*Berekening!E11-Berekening!E75+E61)</f>
-        <v>464191.101568685</v>
+        <v>340830.129648095</v>
       </c>
       <c r="F73" s="29" t="n">
         <f aca="false">MAX(0,(F72*F60/12-Berekening!F18-Berekening!F44)*Berekening!F11-Berekening!F75+F61)</f>
-        <v>530515.05250535</v>
+        <v>447609.383941122</v>
       </c>
       <c r="G73" s="29" t="n">
         <f aca="false">MAX(0,(G72*G60/12-Berekening!G18-Berekening!G44)*Berekening!G11-Berekening!G75+G61)</f>
-        <v>319784.063512381</v>
+        <v>296433.461257214</v>
       </c>
       <c r="H73" s="29" t="n">
         <f aca="false">MAX(0,(H72*H60/12-Berekening!H18-Berekening!H44)*Berekening!H11-Berekening!H75+H61)</f>
-        <v>793734.141366113</v>
+        <v>731119.765606001</v>
       </c>
       <c r="I73" s="29" t="n">
         <f aca="false">MAX(0,(I72*I60/12-Berekening!I18-Berekening!I44)*Berekening!I11-Berekening!I75+I61)</f>
-        <v>1198566.85165502</v>
+        <v>1016249.57976032</v>
       </c>
       <c r="J73" s="29" t="n">
         <f aca="false">MAX(0,(J72*J60/12-Berekening!J18-Berekening!J44)*Berekening!J11-Berekening!J75+J61)</f>
-        <v>213350.480045017</v>
+        <v>110122.349108746</v>
       </c>
       <c r="K73" s="29" t="n">
         <f aca="false">MAX(0,(K72*K60/12-Berekening!K18-Berekening!K44)*Berekening!K11-Berekening!K75+K61)</f>
-        <v>367852.100213955</v>
+        <v>253095.208025114</v>
       </c>
       <c r="L73" s="29" t="n">
         <f aca="false">MAX(0,(L72*L60/12-Berekening!L18-Berekening!L44)*Berekening!L11-Berekening!L75+L61)</f>
@@ -14890,7 +14890,7 @@
       </c>
       <c r="M73" s="29" t="n">
         <f aca="false">MAX(0,(M72*M60/12-Berekening!M18-Berekening!M44)*Berekening!M11-Berekening!M75+M61)</f>
-        <v>596771.596865274</v>
+        <v>463477.67298663</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14954,15 +14954,15 @@
       </c>
       <c r="C75" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,3)+0.000005)&lt;Berekening!C10,(Berekening!C45-(INDEX(T2_Rente,3)+0.000005)*Berekening!C46)/(360*((INDEX(T2_Rente,3)+0.000005)-Berekening!C10)),1000000000000),IF((INDEX(T2_Rente,3)-0.005+0.000005)&gt;Berekening!C10,(Berekening!C45-(INDEX(T2_Rente,3)-0.005+0.000005)*Berekening!C46)/(360*((INDEX(T2_Rente,3)-0.005+0.000005)-Berekening!C10)),1000000000000))</f>
-        <v>-210660.489381572</v>
+        <v>-144272.849430311</v>
       </c>
       <c r="D75" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,3)+0.000005)&lt;Berekening!D10,(Berekening!D45-(INDEX(T2_Rente,3)+0.000005)*Berekening!D46)/(360*((INDEX(T2_Rente,3)+0.000005)-Berekening!D10)),1000000000000),IF((INDEX(T2_Rente,3)-0.005+0.000005)&gt;Berekening!D10,(Berekening!D45-(INDEX(T2_Rente,3)-0.005+0.000005)*Berekening!D46)/(360*((INDEX(T2_Rente,3)-0.005+0.000005)-Berekening!D10)),1000000000000))</f>
-        <v>-295508.302464155</v>
+        <v>-202381.685108472</v>
       </c>
       <c r="E75" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,3)+0.000005)&lt;Berekening!E10,(Berekening!E45-(INDEX(T2_Rente,3)+0.000005)*Berekening!E46)/(360*((INDEX(T2_Rente,3)+0.000005)-Berekening!E10)),1000000000000),IF((INDEX(T2_Rente,3)-0.005+0.000005)&gt;Berekening!E10,(Berekening!E45-(INDEX(T2_Rente,3)-0.005+0.000005)*Berekening!E46)/(360*((INDEX(T2_Rente,3)-0.005+0.000005)-Berekening!E10)),1000000000000))</f>
-        <v>-954874.027560965</v>
+        <v>-653954.603483748</v>
       </c>
       <c r="F75" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,3)+0.000005)&lt;Berekening!F10,(Berekening!F45-(INDEX(T2_Rente,3)+0.000005)*Berekening!F46)/(360*((INDEX(T2_Rente,3)+0.000005)-Berekening!F10)),1000000000000),IF((INDEX(T2_Rente,3)-0.005+0.000005)&gt;Berekening!F10,(Berekening!F45-(INDEX(T2_Rente,3)-0.005+0.000005)*Berekening!F46)/(360*((INDEX(T2_Rente,3)-0.005+0.000005)-Berekening!F10)),1000000000000))</f>
@@ -14982,19 +14982,19 @@
       </c>
       <c r="J75" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,3)+0.000005)&lt;Berekening!J10,(Berekening!J45-(INDEX(T2_Rente,3)+0.000005)*Berekening!J46)/(360*((INDEX(T2_Rente,3)+0.000005)-Berekening!J10)),1000000000000),IF((INDEX(T2_Rente,3)-0.005+0.000005)&gt;Berekening!J10,(Berekening!J45-(INDEX(T2_Rente,3)-0.005+0.000005)*Berekening!J46)/(360*((INDEX(T2_Rente,3)-0.005+0.000005)-Berekening!J10)),1000000000000))</f>
-        <v>-210660.489381572</v>
+        <v>-144272.849430311</v>
       </c>
       <c r="K75" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,3)+0.000005)&lt;Berekening!K10,(Berekening!K45-(INDEX(T2_Rente,3)+0.000005)*Berekening!K46)/(360*((INDEX(T2_Rente,3)+0.000005)-Berekening!K10)),1000000000000),IF((INDEX(T2_Rente,3)-0.005+0.000005)&gt;Berekening!K10,(Berekening!K45-(INDEX(T2_Rente,3)-0.005+0.000005)*Berekening!K46)/(360*((INDEX(T2_Rente,3)-0.005+0.000005)-Berekening!K10)),1000000000000))</f>
-        <v>-790846.207995258</v>
+        <v>-541618.58364416</v>
       </c>
       <c r="L75" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,3)+0.000005)&lt;Berekening!L10,(Berekening!L45-(INDEX(T2_Rente,3)+0.000005)*Berekening!L46)/(360*((INDEX(T2_Rente,3)+0.000005)-Berekening!L10)),1000000000000),IF((INDEX(T2_Rente,3)-0.005+0.000005)&gt;Berekening!L10,(Berekening!L45-(INDEX(T2_Rente,3)-0.005+0.000005)*Berekening!L46)/(360*((INDEX(T2_Rente,3)-0.005+0.000005)-Berekening!L10)),1000000000000))</f>
-        <v>-210660.489381572</v>
+        <v>-144272.849430311</v>
       </c>
       <c r="M75" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,3)+0.000005)&lt;Berekening!M10,(Berekening!M45-(INDEX(T2_Rente,3)+0.000005)*Berekening!M46)/(360*((INDEX(T2_Rente,3)+0.000005)-Berekening!M10)),1000000000000),IF((INDEX(T2_Rente,3)-0.005+0.000005)&gt;Berekening!M10,(Berekening!M45-(INDEX(T2_Rente,3)-0.005+0.000005)*Berekening!M46)/(360*((INDEX(T2_Rente,3)-0.005+0.000005)-Berekening!M10)),1000000000000))</f>
-        <v>-210660.489381572</v>
+        <v>-144272.849430311</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15110,39 +15110,39 @@
       </c>
       <c r="C78" s="29" t="n">
         <f aca="false">MAX(0,(C77*C60/12-Berekening!C18-Berekening!C44)*Berekening!C11-Berekening!C75+C61)</f>
-        <v>652354.464366911</v>
+        <v>512943.258764235</v>
       </c>
       <c r="D78" s="29" t="n">
         <f aca="false">MAX(0,(D77*D60/12-Berekening!D18-Berekening!D44)*Berekening!D11-Berekening!D75+D61)</f>
-        <v>683877.913266016</v>
+        <v>541994.810718044</v>
       </c>
       <c r="E78" s="29" t="n">
         <f aca="false">MAX(0,(E77*E60/12-Berekening!E18-Berekening!E44)*Berekening!E11-Berekening!E75+E61)</f>
-        <v>519773.969070322</v>
+        <v>390295.7154257</v>
       </c>
       <c r="F78" s="29" t="n">
         <f aca="false">MAX(0,(F77*F60/12-Berekening!F18-Berekening!F44)*Berekening!F11-Berekening!F75+F61)</f>
-        <v>579946.949384271</v>
+        <v>495344.048309178</v>
       </c>
       <c r="G78" s="29" t="n">
         <f aca="false">MAX(0,(G77*G60/12-Berekening!G18-Berekening!G44)*Berekening!G11-Berekening!G75+G61)</f>
-        <v>335144.554479022</v>
+        <v>310589.466292756</v>
       </c>
       <c r="H78" s="29" t="n">
         <f aca="false">MAX(0,(H77*H60/12-Berekening!H18-Berekening!H44)*Berekening!H11-Berekening!H75+H61)</f>
-        <v>829517.103277038</v>
+        <v>764096.822791071</v>
       </c>
       <c r="I78" s="29" t="n">
         <f aca="false">MAX(0,(I77*I60/12-Berekening!I18-Berekening!I44)*Berekening!I11-Berekening!I75+I61)</f>
-        <v>1254149.71915666</v>
+        <v>1065715.16553792</v>
       </c>
       <c r="J78" s="29" t="n">
         <f aca="false">MAX(0,(J77*J60/12-Berekening!J18-Berekening!J44)*Berekening!J11-Berekening!J75+J61)</f>
-        <v>250326.207352973</v>
+        <v>142439.865150114</v>
       </c>
       <c r="K78" s="29" t="n">
         <f aca="false">MAX(0,(K77*K60/12-Berekening!K18-Berekening!K44)*Berekening!K11-Berekening!K75+K61)</f>
-        <v>423434.967715592</v>
+        <v>302560.793802719</v>
       </c>
       <c r="L78" s="29" t="n">
         <f aca="false">MAX(0,(L77*L60/12-Berekening!L18-Berekening!L44)*Berekening!L11-Berekening!L75+L61)</f>
@@ -15150,7 +15150,7 @@
       </c>
       <c r="M78" s="29" t="n">
         <f aca="false">MAX(0,(M77*M60/12-Berekening!M18-Berekening!M44)*Berekening!M11-Berekening!M75+M61)</f>
-        <v>652354.464366911</v>
+        <v>512943.258764235</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15214,15 +15214,15 @@
       </c>
       <c r="C80" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,4)+0.000005)&lt;Berekening!C10,(Berekening!C45-(INDEX(T2_Rente,4)+0.000005)*Berekening!C46)/(360*((INDEX(T2_Rente,4)+0.000005)-Berekening!C10)),1000000000000),IF((INDEX(T2_Rente,4)-0.005+0.000005)&gt;Berekening!C10,(Berekening!C45-(INDEX(T2_Rente,4)-0.005+0.000005)*Berekening!C46)/(360*((INDEX(T2_Rente,4)-0.005+0.000005)-Berekening!C10)),1000000000000))</f>
-        <v>-29476.1362291147</v>
+        <v>-17437.9391305121</v>
       </c>
       <c r="D80" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,4)+0.000005)&lt;Berekening!D10,(Berekening!D45-(INDEX(T2_Rente,4)+0.000005)*Berekening!D46)/(360*((INDEX(T2_Rente,4)+0.000005)-Berekening!D10)),1000000000000),IF((INDEX(T2_Rente,4)-0.005+0.000005)&gt;Berekening!D10,(Berekening!D45-(INDEX(T2_Rente,4)-0.005+0.000005)*Berekening!D46)/(360*((INDEX(T2_Rente,4)-0.005+0.000005)-Berekening!D10)),1000000000000))</f>
-        <v>-131305.397243622</v>
+        <v>-77679.6357176679</v>
       </c>
       <c r="E80" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,4)+0.000005)&lt;Berekening!E10,(Berekening!E45-(INDEX(T2_Rente,4)+0.000005)*Berekening!E46)/(360*((INDEX(T2_Rente,4)+0.000005)-Berekening!E10)),1000000000000),IF((INDEX(T2_Rente,4)-0.005+0.000005)&gt;Berekening!E10,(Berekening!E45-(INDEX(T2_Rente,4)-0.005+0.000005)*Berekening!E46)/(360*((INDEX(T2_Rente,4)-0.005+0.000005)-Berekening!E10)),1000000000000))</f>
-        <v>-1145982.58995598</v>
+        <v>-677957.738183486</v>
       </c>
       <c r="F80" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,4)+0.000005)&lt;Berekening!F10,(Berekening!F45-(INDEX(T2_Rente,4)+0.000005)*Berekening!F46)/(360*((INDEX(T2_Rente,4)+0.000005)-Berekening!F10)),1000000000000),IF((INDEX(T2_Rente,4)-0.005+0.000005)&gt;Berekening!F10,(Berekening!F45-(INDEX(T2_Rente,4)-0.005+0.000005)*Berekening!F46)/(360*((INDEX(T2_Rente,4)-0.005+0.000005)-Berekening!F10)),1000000000000))</f>
@@ -15242,19 +15242,19 @@
       </c>
       <c r="J80" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,4)+0.000005)&lt;Berekening!J10,(Berekening!J45-(INDEX(T2_Rente,4)+0.000005)*Berekening!J46)/(360*((INDEX(T2_Rente,4)+0.000005)-Berekening!J10)),1000000000000),IF((INDEX(T2_Rente,4)-0.005+0.000005)&gt;Berekening!J10,(Berekening!J45-(INDEX(T2_Rente,4)-0.005+0.000005)*Berekening!J46)/(360*((INDEX(T2_Rente,4)-0.005+0.000005)-Berekening!J10)),1000000000000))</f>
-        <v>-29476.1362291147</v>
+        <v>-17437.9391305121</v>
       </c>
       <c r="K80" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,4)+0.000005)&lt;Berekening!K10,(Berekening!K45-(INDEX(T2_Rente,4)+0.000005)*Berekening!K46)/(360*((INDEX(T2_Rente,4)+0.000005)-Berekening!K10)),1000000000000),IF((INDEX(T2_Rente,4)-0.005+0.000005)&gt;Berekening!K10,(Berekening!K45-(INDEX(T2_Rente,4)-0.005+0.000005)*Berekening!K46)/(360*((INDEX(T2_Rente,4)-0.005+0.000005)-Berekening!K10)),1000000000000))</f>
-        <v>-949126.229781557</v>
+        <v>-561498.470948012</v>
       </c>
       <c r="L80" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,4)+0.000005)&lt;Berekening!L10,(Berekening!L45-(INDEX(T2_Rente,4)+0.000005)*Berekening!L46)/(360*((INDEX(T2_Rente,4)+0.000005)-Berekening!L10)),1000000000000),IF((INDEX(T2_Rente,4)-0.005+0.000005)&gt;Berekening!L10,(Berekening!L45-(INDEX(T2_Rente,4)-0.005+0.000005)*Berekening!L46)/(360*((INDEX(T2_Rente,4)-0.005+0.000005)-Berekening!L10)),1000000000000))</f>
-        <v>-29476.1362291147</v>
+        <v>-17437.9391305121</v>
       </c>
       <c r="M80" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,4)+0.000005)&lt;Berekening!M10,(Berekening!M45-(INDEX(T2_Rente,4)+0.000005)*Berekening!M46)/(360*((INDEX(T2_Rente,4)+0.000005)-Berekening!M10)),1000000000000),IF((INDEX(T2_Rente,4)-0.005+0.000005)&gt;Berekening!M10,(Berekening!M45-(INDEX(T2_Rente,4)-0.005+0.000005)*Berekening!M46)/(360*((INDEX(T2_Rente,4)-0.005+0.000005)-Berekening!M10)),1000000000000))</f>
-        <v>-29476.1362291147</v>
+        <v>-17437.9391305121</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15370,39 +15370,39 @@
       </c>
       <c r="C83" s="29" t="n">
         <f aca="false">MAX(0,(C82*C60/12-Berekening!C18-Berekening!C44)*Berekening!C11-Berekening!C75+C61)</f>
-        <v>705225.972478224</v>
+        <v>559995.889138054</v>
       </c>
       <c r="D83" s="29" t="n">
         <f aca="false">MAX(0,(D82*D60/12-Berekening!D18-Berekening!D44)*Berekening!D11-Berekening!D75+D61)</f>
-        <v>736749.421377329</v>
+        <v>589047.441091863</v>
       </c>
       <c r="E83" s="29" t="n">
         <f aca="false">MAX(0,(E82*E60/12-Berekening!E18-Berekening!E44)*Berekening!E11-Berekening!E75+E61)</f>
-        <v>572645.477181635</v>
+        <v>437348.345799519</v>
       </c>
       <c r="F83" s="29" t="n">
         <f aca="false">MAX(0,(F82*F60/12-Berekening!F18-Berekening!F44)*Berekening!F11-Berekening!F75+F61)</f>
-        <v>626967.534220318</v>
+        <v>540750.192464159</v>
       </c>
       <c r="G83" s="29" t="n">
         <f aca="false">MAX(0,(G82*G60/12-Berekening!G18-Berekening!G44)*Berekening!G11-Berekening!G75+G61)</f>
-        <v>346664.922704002</v>
+        <v>321206.470069413</v>
       </c>
       <c r="H83" s="29" t="n">
         <f aca="false">MAX(0,(H82*H60/12-Berekening!H18-Berekening!H44)*Berekening!H11-Berekening!H75+H61)</f>
-        <v>863554.554850845</v>
+        <v>795465.243040284</v>
       </c>
       <c r="I83" s="29" t="n">
         <f aca="false">MAX(0,(I82*I60/12-Berekening!I18-Berekening!I44)*Berekening!I11-Berekening!I75+I61)</f>
-        <v>1307021.22726797</v>
+        <v>1112767.79591174</v>
       </c>
       <c r="J83" s="29" t="n">
         <f aca="false">MAX(0,(J82*J60/12-Berekening!J18-Berekening!J44)*Berekening!J11-Berekening!J75+J61)</f>
-        <v>285498.240645907</v>
+        <v>173180.916994343</v>
       </c>
       <c r="K83" s="29" t="n">
         <f aca="false">MAX(0,(K82*K60/12-Berekening!K18-Berekening!K44)*Berekening!K11-Berekening!K75+K61)</f>
-        <v>476306.475826904</v>
+        <v>349613.424176538</v>
       </c>
       <c r="L83" s="29" t="n">
         <f aca="false">MAX(0,(L82*L60/12-Berekening!L18-Berekening!L44)*Berekening!L11-Berekening!L75+L61)</f>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="M83" s="29" t="n">
         <f aca="false">MAX(0,(M82*M60/12-Berekening!M18-Berekening!M44)*Berekening!M11-Berekening!M75+M61)</f>
-        <v>705225.972478224</v>
+        <v>559995.889138054</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15474,15 +15474,15 @@
       </c>
       <c r="C85" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,5)+0.000005)&lt;Berekening!C10,(Berekening!C45-(INDEX(T2_Rente,5)+0.000005)*Berekening!C46)/(360*((INDEX(T2_Rente,5)+0.000005)-Berekening!C10)),1000000000000),IF((INDEX(T2_Rente,5)-0.005+0.000005)&gt;Berekening!C10,(Berekening!C45-(INDEX(T2_Rente,5)-0.005+0.000005)*Berekening!C46)/(360*((INDEX(T2_Rente,5)-0.005+0.000005)-Berekening!C10)),1000000000000))</f>
-        <v>514439.654665999</v>
+        <v>216025.731404512</v>
       </c>
       <c r="D85" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,5)+0.000005)&lt;Berekening!D10,(Berekening!D45-(INDEX(T2_Rente,5)+0.000005)*Berekening!D46)/(360*((INDEX(T2_Rente,5)+0.000005)-Berekening!D10)),1000000000000),IF((INDEX(T2_Rente,5)-0.005+0.000005)&gt;Berekening!D10,(Berekening!D45-(INDEX(T2_Rente,5)-0.005+0.000005)*Berekening!D46)/(360*((INDEX(T2_Rente,5)-0.005+0.000005)-Berekening!D10)),1000000000000))</f>
-        <v>361632.052962963</v>
+        <v>151858.100424548</v>
       </c>
       <c r="E85" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,5)+0.000005)&lt;Berekening!E10,(Berekening!E45-(INDEX(T2_Rente,5)+0.000005)*Berekening!E46)/(360*((INDEX(T2_Rente,5)+0.000005)-Berekening!E10)),1000000000000),IF((INDEX(T2_Rente,5)-0.005+0.000005)&gt;Berekening!E10,(Berekening!E45-(INDEX(T2_Rente,5)-0.005+0.000005)*Berekening!E46)/(360*((INDEX(T2_Rente,5)-0.005+0.000005)-Berekening!E10)),1000000000000))</f>
-        <v>-1719690.87686553</v>
+        <v>-722140.052958666</v>
       </c>
       <c r="F85" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,5)+0.000005)&lt;Berekening!F10,(Berekening!F45-(INDEX(T2_Rente,5)+0.000005)*Berekening!F46)/(360*((INDEX(T2_Rente,5)+0.000005)-Berekening!F10)),1000000000000),IF((INDEX(T2_Rente,5)-0.005+0.000005)&gt;Berekening!F10,(Berekening!F45-(INDEX(T2_Rente,5)-0.005+0.000005)*Berekening!F46)/(360*((INDEX(T2_Rente,5)-0.005+0.000005)-Berekening!F10)),1000000000000))</f>
@@ -15502,19 +15502,19 @@
       </c>
       <c r="J85" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,5)+0.000005)&lt;Berekening!J10,(Berekening!J45-(INDEX(T2_Rente,5)+0.000005)*Berekening!J46)/(360*((INDEX(T2_Rente,5)+0.000005)-Berekening!J10)),1000000000000),IF((INDEX(T2_Rente,5)-0.005+0.000005)&gt;Berekening!J10,(Berekening!J45-(INDEX(T2_Rente,5)-0.005+0.000005)*Berekening!J46)/(360*((INDEX(T2_Rente,5)-0.005+0.000005)-Berekening!J10)),1000000000000))</f>
-        <v>514439.654665999</v>
+        <v>216025.731404512</v>
       </c>
       <c r="K85" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,5)+0.000005)&lt;Berekening!K10,(Berekening!K45-(INDEX(T2_Rente,5)+0.000005)*Berekening!K46)/(360*((INDEX(T2_Rente,5)+0.000005)-Berekening!K10)),1000000000000),IF((INDEX(T2_Rente,5)-0.005+0.000005)&gt;Berekening!K10,(Berekening!K45-(INDEX(T2_Rente,5)-0.005+0.000005)*Berekening!K46)/(360*((INDEX(T2_Rente,5)-0.005+0.000005)-Berekening!K10)),1000000000000))</f>
-        <v>-1424283.17206095</v>
+        <v>-598091.168091168</v>
       </c>
       <c r="L85" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,5)+0.000005)&lt;Berekening!L10,(Berekening!L45-(INDEX(T2_Rente,5)+0.000005)*Berekening!L46)/(360*((INDEX(T2_Rente,5)+0.000005)-Berekening!L10)),1000000000000),IF((INDEX(T2_Rente,5)-0.005+0.000005)&gt;Berekening!L10,(Berekening!L45-(INDEX(T2_Rente,5)-0.005+0.000005)*Berekening!L46)/(360*((INDEX(T2_Rente,5)-0.005+0.000005)-Berekening!L10)),1000000000000))</f>
-        <v>514439.654665999</v>
+        <v>216025.731404512</v>
       </c>
       <c r="M85" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,5)+0.000005)&lt;Berekening!M10,(Berekening!M45-(INDEX(T2_Rente,5)+0.000005)*Berekening!M46)/(360*((INDEX(T2_Rente,5)+0.000005)-Berekening!M10)),1000000000000),IF((INDEX(T2_Rente,5)-0.005+0.000005)&gt;Berekening!M10,(Berekening!M45-(INDEX(T2_Rente,5)-0.005+0.000005)*Berekening!M46)/(360*((INDEX(T2_Rente,5)-0.005+0.000005)-Berekening!M10)),1000000000000))</f>
-        <v>514439.654665999</v>
+        <v>216025.731404512</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15526,11 +15526,11 @@
       </c>
       <c r="C86" s="29" t="n">
         <f aca="false">IF(C84&gt;C85,-1,IF(C83&lt;C84-0.000000001,-1,IF(C83&gt;C85,MAX(C84,C85-1),C83)))</f>
-        <v>514438.654665999</v>
+        <v>216024.731404512</v>
       </c>
       <c r="D86" s="29" t="n">
         <f aca="false">IF(D84&gt;D85,-1,IF(D83&lt;D84-0.000000001,-1,IF(D83&gt;D85,MAX(D84,D85-1),D83)))</f>
-        <v>361631.052962963</v>
+        <v>151857.100424548</v>
       </c>
       <c r="E86" s="29" t="n">
         <f aca="false">IF(E84&gt;E85,-1,IF(E83&lt;E84-0.000000001,-1,IF(E83&gt;E85,MAX(E84,E85-1),E83)))</f>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="J86" s="29" t="n">
         <f aca="false">IF(J84&gt;J85,-1,IF(J83&lt;J84-0.000000001,-1,IF(J83&gt;J85,MAX(J84,J85-1),J83)))</f>
-        <v>285498.240645907</v>
+        <v>173180.916994343</v>
       </c>
       <c r="K86" s="29" t="n">
         <f aca="false">IF(K84&gt;K85,-1,IF(K83&lt;K84-0.000000001,-1,IF(K83&gt;K85,MAX(K84,K85-1),K83)))</f>
@@ -15566,7 +15566,7 @@
       </c>
       <c r="M86" s="29" t="n">
         <f aca="false">IF(M84&gt;M85,-1,IF(M83&lt;M84-0.000000001,-1,IF(M83&gt;M85,MAX(M84,M85-1),M83)))</f>
-        <v>514438.654665999</v>
+        <v>216024.731404512</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15630,39 +15630,39 @@
       </c>
       <c r="C88" s="29" t="n">
         <f aca="false">MAX(0,(C87*C60/12-Berekening!C18-Berekening!C44)*Berekening!C11-Berekening!C75+C61)</f>
-        <v>758097.480589537</v>
+        <v>607048.519511873</v>
       </c>
       <c r="D88" s="29" t="n">
         <f aca="false">MAX(0,(D87*D60/12-Berekening!D18-Berekening!D44)*Berekening!D11-Berekening!D75+D61)</f>
-        <v>789620.929488642</v>
+        <v>636100.071465681</v>
       </c>
       <c r="E88" s="29" t="n">
         <f aca="false">MAX(0,(E87*E60/12-Berekening!E18-Berekening!E44)*Berekening!E11-Berekening!E75+E61)</f>
-        <v>625516.985292948</v>
+        <v>484400.976173338</v>
       </c>
       <c r="F88" s="29" t="n">
         <f aca="false">MAX(0,(F87*F60/12-Berekening!F18-Berekening!F44)*Berekening!F11-Berekening!F75+F61)</f>
-        <v>673988.119056364</v>
+        <v>586156.33661914</v>
       </c>
       <c r="G88" s="29" t="n">
         <f aca="false">MAX(0,(G87*G60/12-Berekening!G18-Berekening!G44)*Berekening!G11-Berekening!G75+G61)</f>
-        <v>358185.290928983</v>
+        <v>331823.473846069</v>
       </c>
       <c r="H88" s="29" t="n">
         <f aca="false">MAX(0,(H87*H60/12-Berekening!H18-Berekening!H44)*Berekening!H11-Berekening!H75+H61)</f>
-        <v>897592.006424652</v>
+        <v>826833.663289496</v>
       </c>
       <c r="I88" s="29" t="n">
         <f aca="false">MAX(0,(I87*I60/12-Berekening!I18-Berekening!I44)*Berekening!I11-Berekening!I75+I61)</f>
-        <v>1359892.73537928</v>
+        <v>1159820.42628556</v>
       </c>
       <c r="J88" s="29" t="n">
         <f aca="false">MAX(0,(J87*J60/12-Berekening!J18-Berekening!J44)*Berekening!J11-Berekening!J75+J61)</f>
-        <v>320670.27393884</v>
+        <v>203921.968838571</v>
       </c>
       <c r="K88" s="29" t="n">
         <f aca="false">MAX(0,(K87*K60/12-Berekening!K18-Berekening!K44)*Berekening!K11-Berekening!K75+K61)</f>
-        <v>529177.983938217</v>
+        <v>396666.054550356</v>
       </c>
       <c r="L88" s="29" t="n">
         <f aca="false">MAX(0,(L87*L60/12-Berekening!L18-Berekening!L44)*Berekening!L11-Berekening!L75+L61)</f>
@@ -15670,7 +15670,7 @@
       </c>
       <c r="M88" s="29" t="n">
         <f aca="false">MAX(0,(M87*M60/12-Berekening!M18-Berekening!M44)*Berekening!M11-Berekening!M75+M61)</f>
-        <v>758097.480589537</v>
+        <v>607048.519511873</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15682,15 +15682,15 @@
       </c>
       <c r="C89" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,6)+0.000005)&gt;Berekening!C10,(Berekening!C45-(INDEX(T2_Rente,6)+0.000005)*Berekening!C46)/(360*((INDEX(T2_Rente,6)+0.000005)-Berekening!C10)),IF((INDEX(T2_Rente,6)+0.000005)=Berekening!C10,IF(Berekening!C45-(INDEX(T2_Rente,6)+0.000005)*Berekening!C46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,6)-0.005+0.000005)&lt;Berekening!C10,(Berekening!C45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!C46)/(360*((INDEX(T2_Rente,6)-0.005+0.000005)-Berekening!C10)),IF((INDEX(T2_Rente,6)-0.005+0.000005)=Berekening!C10,IF(Berekening!C45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!C46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>514439.654665999</v>
+        <v>216025.731404512</v>
       </c>
       <c r="D89" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,6)+0.000005)&gt;Berekening!D10,(Berekening!D45-(INDEX(T2_Rente,6)+0.000005)*Berekening!D46)/(360*((INDEX(T2_Rente,6)+0.000005)-Berekening!D10)),IF((INDEX(T2_Rente,6)+0.000005)=Berekening!D10,IF(Berekening!D45-(INDEX(T2_Rente,6)+0.000005)*Berekening!D46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,6)-0.005+0.000005)&lt;Berekening!D10,(Berekening!D45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!D46)/(360*((INDEX(T2_Rente,6)-0.005+0.000005)-Berekening!D10)),IF((INDEX(T2_Rente,6)-0.005+0.000005)=Berekening!D10,IF(Berekening!D45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!D46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>361632.052962963</v>
+        <v>151858.100424548</v>
       </c>
       <c r="E89" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,6)+0.000005)&gt;Berekening!E10,(Berekening!E45-(INDEX(T2_Rente,6)+0.000005)*Berekening!E46)/(360*((INDEX(T2_Rente,6)+0.000005)-Berekening!E10)),IF((INDEX(T2_Rente,6)+0.000005)=Berekening!E10,IF(Berekening!E45-(INDEX(T2_Rente,6)+0.000005)*Berekening!E46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,6)-0.005+0.000005)&lt;Berekening!E10,(Berekening!E45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!E46)/(360*((INDEX(T2_Rente,6)-0.005+0.000005)-Berekening!E10)),IF((INDEX(T2_Rente,6)-0.005+0.000005)=Berekening!E10,IF(Berekening!E45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!E46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>1145123174.65578</v>
+        <v>0</v>
       </c>
       <c r="F89" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,6)+0.000005)&gt;Berekening!F10,(Berekening!F45-(INDEX(T2_Rente,6)+0.000005)*Berekening!F46)/(360*((INDEX(T2_Rente,6)+0.000005)-Berekening!F10)),IF((INDEX(T2_Rente,6)+0.000005)=Berekening!F10,IF(Berekening!F45-(INDEX(T2_Rente,6)+0.000005)*Berekening!F46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,6)-0.005+0.000005)&lt;Berekening!F10,(Berekening!F45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!F46)/(360*((INDEX(T2_Rente,6)-0.005+0.000005)-Berekening!F10)),IF((INDEX(T2_Rente,6)-0.005+0.000005)=Berekening!F10,IF(Berekening!F45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!F46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
@@ -15710,19 +15710,19 @@
       </c>
       <c r="J89" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,6)+0.000005)&gt;Berekening!J10,(Berekening!J45-(INDEX(T2_Rente,6)+0.000005)*Berekening!J46)/(360*((INDEX(T2_Rente,6)+0.000005)-Berekening!J10)),IF((INDEX(T2_Rente,6)+0.000005)=Berekening!J10,IF(Berekening!J45-(INDEX(T2_Rente,6)+0.000005)*Berekening!J46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,6)-0.005+0.000005)&lt;Berekening!J10,(Berekening!J45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!J46)/(360*((INDEX(T2_Rente,6)-0.005+0.000005)-Berekening!J10)),IF((INDEX(T2_Rente,6)-0.005+0.000005)=Berekening!J10,IF(Berekening!J45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!J46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>514439.654665999</v>
+        <v>216025.731404512</v>
       </c>
       <c r="K89" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,6)+0.000005)&gt;Berekening!K10,(Berekening!K45-(INDEX(T2_Rente,6)+0.000005)*Berekening!K46)/(360*((INDEX(T2_Rente,6)+0.000005)-Berekening!K10)),IF((INDEX(T2_Rente,6)+0.000005)=Berekening!K10,IF(Berekening!K45-(INDEX(T2_Rente,6)+0.000005)*Berekening!K46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,6)-0.005+0.000005)&lt;Berekening!K10,(Berekening!K45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!K46)/(360*((INDEX(T2_Rente,6)-0.005+0.000005)-Berekening!K10)),IF((INDEX(T2_Rente,6)-0.005+0.000005)=Berekening!K10,IF(Berekening!K45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!K46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>948414444.444812</v>
+        <v>0</v>
       </c>
       <c r="L89" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,6)+0.000005)&gt;Berekening!L10,(Berekening!L45-(INDEX(T2_Rente,6)+0.000005)*Berekening!L46)/(360*((INDEX(T2_Rente,6)+0.000005)-Berekening!L10)),IF((INDEX(T2_Rente,6)+0.000005)=Berekening!L10,IF(Berekening!L45-(INDEX(T2_Rente,6)+0.000005)*Berekening!L46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,6)-0.005+0.000005)&lt;Berekening!L10,(Berekening!L45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!L46)/(360*((INDEX(T2_Rente,6)-0.005+0.000005)-Berekening!L10)),IF((INDEX(T2_Rente,6)-0.005+0.000005)=Berekening!L10,IF(Berekening!L45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!L46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>514439.654665999</v>
+        <v>216025.731404512</v>
       </c>
       <c r="M89" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,6)+0.000005)&gt;Berekening!M10,(Berekening!M45-(INDEX(T2_Rente,6)+0.000005)*Berekening!M46)/(360*((INDEX(T2_Rente,6)+0.000005)-Berekening!M10)),IF((INDEX(T2_Rente,6)+0.000005)=Berekening!M10,IF(Berekening!M45-(INDEX(T2_Rente,6)+0.000005)*Berekening!M46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,6)-0.005+0.000005)&lt;Berekening!M10,(Berekening!M45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!M46)/(360*((INDEX(T2_Rente,6)-0.005+0.000005)-Berekening!M10)),IF((INDEX(T2_Rente,6)-0.005+0.000005)=Berekening!M10,IF(Berekening!M45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!M46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>514439.654665999</v>
+        <v>216025.731404512</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15734,15 +15734,15 @@
       </c>
       <c r="C90" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,6)+0.000005)&lt;Berekening!C10,(Berekening!C45-(INDEX(T2_Rente,6)+0.000005)*Berekening!C46)/(360*((INDEX(T2_Rente,6)+0.000005)-Berekening!C10)),1000000000000),IF((INDEX(T2_Rente,6)-0.005+0.000005)&gt;Berekening!C10,(Berekening!C45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!C46)/(360*((INDEX(T2_Rente,6)-0.005+0.000005)-Berekening!C10)),1000000000000))</f>
-        <v>1000000000000</v>
+        <v>788087.908879381</v>
       </c>
       <c r="D90" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,6)+0.000005)&lt;Berekening!D10,(Berekening!D45-(INDEX(T2_Rente,6)+0.000005)*Berekening!D46)/(360*((INDEX(T2_Rente,6)+0.000005)-Berekening!D10)),1000000000000),IF((INDEX(T2_Rente,6)-0.005+0.000005)&gt;Berekening!D10,(Berekening!D45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!D46)/(360*((INDEX(T2_Rente,6)-0.005+0.000005)-Berekening!D10)),1000000000000))</f>
-        <v>1000000000000</v>
+        <v>714300.45751269</v>
       </c>
       <c r="E90" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,6)+0.000005)&lt;Berekening!E10,(Berekening!E45-(INDEX(T2_Rente,6)+0.000005)*Berekening!E46)/(360*((INDEX(T2_Rente,6)+0.000005)-Berekening!E10)),1000000000000),IF((INDEX(T2_Rente,6)-0.005+0.000005)&gt;Berekening!E10,(Berekening!E45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!E46)/(360*((INDEX(T2_Rente,6)-0.005+0.000005)-Berekening!E10)),1000000000000))</f>
-        <v>1000000000000</v>
+        <v>-830401.14188204</v>
       </c>
       <c r="F90" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,6)+0.000005)&lt;Berekening!F10,(Berekening!F45-(INDEX(T2_Rente,6)+0.000005)*Berekening!F46)/(360*((INDEX(T2_Rente,6)+0.000005)-Berekening!F10)),1000000000000),IF((INDEX(T2_Rente,6)-0.005+0.000005)&gt;Berekening!F10,(Berekening!F45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!F46)/(360*((INDEX(T2_Rente,6)-0.005+0.000005)-Berekening!F10)),1000000000000))</f>
@@ -15750,31 +15750,31 @@
       </c>
       <c r="G90" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,6)+0.000005)&lt;Berekening!G10,(Berekening!G45-(INDEX(T2_Rente,6)+0.000005)*Berekening!G46)/(360*((INDEX(T2_Rente,6)+0.000005)-Berekening!G10)),1000000000000),IF((INDEX(T2_Rente,6)-0.005+0.000005)&gt;Berekening!G10,(Berekening!G45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!G46)/(360*((INDEX(T2_Rente,6)-0.005+0.000005)-Berekening!G10)),1000000000000))</f>
-        <v>1000000000000</v>
+        <v>-0</v>
       </c>
       <c r="H90" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,6)+0.000005)&lt;Berekening!H10,(Berekening!H45-(INDEX(T2_Rente,6)+0.000005)*Berekening!H46)/(360*((INDEX(T2_Rente,6)+0.000005)-Berekening!H10)),1000000000000),IF((INDEX(T2_Rente,6)-0.005+0.000005)&gt;Berekening!H10,(Berekening!H45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!H46)/(360*((INDEX(T2_Rente,6)-0.005+0.000005)-Berekening!H10)),1000000000000))</f>
-        <v>1000000000000</v>
+        <v>-0</v>
       </c>
       <c r="I90" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,6)+0.000005)&lt;Berekening!I10,(Berekening!I45-(INDEX(T2_Rente,6)+0.000005)*Berekening!I46)/(360*((INDEX(T2_Rente,6)+0.000005)-Berekening!I10)),1000000000000),IF((INDEX(T2_Rente,6)-0.005+0.000005)&gt;Berekening!I10,(Berekening!I45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!I46)/(360*((INDEX(T2_Rente,6)-0.005+0.000005)-Berekening!I10)),1000000000000))</f>
-        <v>1000000000000</v>
+        <v>-0</v>
       </c>
       <c r="J90" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,6)+0.000005)&lt;Berekening!J10,(Berekening!J45-(INDEX(T2_Rente,6)+0.000005)*Berekening!J46)/(360*((INDEX(T2_Rente,6)+0.000005)-Berekening!J10)),1000000000000),IF((INDEX(T2_Rente,6)-0.005+0.000005)&gt;Berekening!J10,(Berekening!J45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!J46)/(360*((INDEX(T2_Rente,6)-0.005+0.000005)-Berekening!J10)),1000000000000))</f>
-        <v>1000000000000</v>
+        <v>788087.908879381</v>
       </c>
       <c r="K90" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,6)+0.000005)&lt;Berekening!K10,(Berekening!K45-(INDEX(T2_Rente,6)+0.000005)*Berekening!K46)/(360*((INDEX(T2_Rente,6)+0.000005)-Berekening!K10)),1000000000000),IF((INDEX(T2_Rente,6)-0.005+0.000005)&gt;Berekening!K10,(Berekening!K45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!K46)/(360*((INDEX(T2_Rente,6)-0.005+0.000005)-Berekening!K10)),1000000000000))</f>
-        <v>1000000000000</v>
+        <v>-687755.21714608</v>
       </c>
       <c r="L90" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,6)+0.000005)&lt;Berekening!L10,(Berekening!L45-(INDEX(T2_Rente,6)+0.000005)*Berekening!L46)/(360*((INDEX(T2_Rente,6)+0.000005)-Berekening!L10)),1000000000000),IF((INDEX(T2_Rente,6)-0.005+0.000005)&gt;Berekening!L10,(Berekening!L45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!L46)/(360*((INDEX(T2_Rente,6)-0.005+0.000005)-Berekening!L10)),1000000000000))</f>
-        <v>1000000000000</v>
+        <v>788087.908879381</v>
       </c>
       <c r="M90" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,6)+0.000005)&lt;Berekening!M10,(Berekening!M45-(INDEX(T2_Rente,6)+0.000005)*Berekening!M46)/(360*((INDEX(T2_Rente,6)+0.000005)-Berekening!M10)),1000000000000),IF((INDEX(T2_Rente,6)-0.005+0.000005)&gt;Berekening!M10,(Berekening!M45-(INDEX(T2_Rente,6)-0.005+0.000005)*Berekening!M46)/(360*((INDEX(T2_Rente,6)-0.005+0.000005)-Berekening!M10)),1000000000000))</f>
-        <v>1000000000000</v>
+        <v>788087.908879381</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15786,11 +15786,11 @@
       </c>
       <c r="C91" s="29" t="n">
         <f aca="false">IF(C89&gt;C90,-1,IF(C88&lt;C89-0.000000001,-1,IF(C88&gt;C90,MAX(C89,C90-1),C88)))</f>
-        <v>758097.480589537</v>
+        <v>607048.519511873</v>
       </c>
       <c r="D91" s="29" t="n">
         <f aca="false">IF(D89&gt;D90,-1,IF(D88&lt;D89-0.000000001,-1,IF(D88&gt;D90,MAX(D89,D90-1),D88)))</f>
-        <v>789620.929488642</v>
+        <v>636100.071465681</v>
       </c>
       <c r="E91" s="29" t="n">
         <f aca="false">IF(E89&gt;E90,-1,IF(E88&lt;E89-0.000000001,-1,IF(E88&gt;E90,MAX(E89,E90-1),E88)))</f>
@@ -15802,15 +15802,15 @@
       </c>
       <c r="G91" s="29" t="n">
         <f aca="false">IF(G89&gt;G90,-1,IF(G88&lt;G89-0.000000001,-1,IF(G88&gt;G90,MAX(G89,G90-1),G88)))</f>
-        <v>358185.290928983</v>
+        <v>-0</v>
       </c>
       <c r="H91" s="29" t="n">
         <f aca="false">IF(H89&gt;H90,-1,IF(H88&lt;H89-0.000000001,-1,IF(H88&gt;H90,MAX(H89,H90-1),H88)))</f>
-        <v>897592.006424652</v>
+        <v>-0</v>
       </c>
       <c r="I91" s="29" t="n">
         <f aca="false">IF(I89&gt;I90,-1,IF(I88&lt;I89-0.000000001,-1,IF(I88&gt;I90,MAX(I89,I90-1),I88)))</f>
-        <v>1359892.73537928</v>
+        <v>-0</v>
       </c>
       <c r="J91" s="29" t="n">
         <f aca="false">IF(J89&gt;J90,-1,IF(J88&lt;J89-0.000000001,-1,IF(J88&gt;J90,MAX(J89,J90-1),J88)))</f>
@@ -15826,7 +15826,7 @@
       </c>
       <c r="M91" s="29" t="n">
         <f aca="false">IF(M89&gt;M90,-1,IF(M88&lt;M89-0.000000001,-1,IF(M88&gt;M90,MAX(M89,M90-1),M88)))</f>
-        <v>758097.480589537</v>
+        <v>607048.519511873</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15890,39 +15890,39 @@
       </c>
       <c r="C93" s="29" t="n">
         <f aca="false">MAX(0,(C92*C60/12-Berekening!C18-Berekening!C44)*Berekening!C11-Berekening!C75+C61)</f>
-        <v>806901.949615365</v>
+        <v>650481.716780013</v>
       </c>
       <c r="D93" s="29" t="n">
         <f aca="false">MAX(0,(D92*D60/12-Berekening!D18-Berekening!D44)*Berekening!D11-Berekening!D75+D61)</f>
-        <v>838425.39851447</v>
+        <v>679533.268733822</v>
       </c>
       <c r="E93" s="29" t="n">
         <f aca="false">MAX(0,(E92*E60/12-Berekening!E18-Berekening!E44)*Berekening!E11-Berekening!E75+E61)</f>
-        <v>674321.454318775</v>
+        <v>527834.173441478</v>
       </c>
       <c r="F93" s="29" t="n">
         <f aca="false">MAX(0,(F92*F60/12-Berekening!F18-Berekening!F44)*Berekening!F11-Berekening!F75+F61)</f>
-        <v>717391.7358281</v>
+        <v>628069.700454507</v>
       </c>
       <c r="G93" s="29" t="n">
         <f aca="false">MAX(0,(G92*G60/12-Berekening!G18-Berekening!G44)*Berekening!G11-Berekening!G75+G61)</f>
-        <v>368658.352951693</v>
+        <v>341475.295461211</v>
       </c>
       <c r="H93" s="29" t="n">
         <f aca="false">MAX(0,(H92*H60/12-Berekening!H18-Berekening!H44)*Berekening!H11-Berekening!H75+H61)</f>
-        <v>929011.192492781</v>
+        <v>855789.128134923</v>
       </c>
       <c r="I93" s="29" t="n">
         <f aca="false">MAX(0,(I92*I60/12-Berekening!I18-Berekening!I44)*Berekening!I11-Berekening!I75+I61)</f>
-        <v>1408697.20440511</v>
+        <v>1203253.6235537</v>
       </c>
       <c r="J93" s="29" t="n">
         <f aca="false">MAX(0,(J92*J60/12-Berekening!J18-Berekening!J44)*Berekening!J11-Berekening!J75+J61)</f>
-        <v>353136.766209241</v>
+        <v>232298.32438709</v>
       </c>
       <c r="K93" s="29" t="n">
         <f aca="false">MAX(0,(K92*K60/12-Berekening!K18-Berekening!K44)*Berekening!K11-Berekening!K75+K61)</f>
-        <v>577982.452964045</v>
+        <v>440099.251818497</v>
       </c>
       <c r="L93" s="29" t="n">
         <f aca="false">MAX(0,(L92*L60/12-Berekening!L18-Berekening!L44)*Berekening!L11-Berekening!L75+L61)</f>
@@ -15930,7 +15930,7 @@
       </c>
       <c r="M93" s="29" t="n">
         <f aca="false">MAX(0,(M92*M60/12-Berekening!M18-Berekening!M44)*Berekening!M11-Berekening!M75+M61)</f>
-        <v>806901.949615365</v>
+        <v>650481.716780013</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15942,15 +15942,15 @@
       </c>
       <c r="C94" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,7)+0.000005)&gt;Berekening!C10,(Berekening!C45-(INDEX(T2_Rente,7)+0.000005)*Berekening!C46)/(360*((INDEX(T2_Rente,7)+0.000005)-Berekening!C10)),IF((INDEX(T2_Rente,7)+0.000005)=Berekening!C10,IF(Berekening!C45-(INDEX(T2_Rente,7)+0.000005)*Berekening!C46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,7)-0.005+0.000005)&lt;Berekening!C10,(Berekening!C45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!C46)/(360*((INDEX(T2_Rente,7)-0.005+0.000005)-Berekening!C10)),IF((INDEX(T2_Rente,7)-0.005+0.000005)=Berekening!C10,IF(Berekening!C45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!C46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>788087.908879381</v>
       </c>
       <c r="D94" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,7)+0.000005)&gt;Berekening!D10,(Berekening!D45-(INDEX(T2_Rente,7)+0.000005)*Berekening!D46)/(360*((INDEX(T2_Rente,7)+0.000005)-Berekening!D10)),IF((INDEX(T2_Rente,7)+0.000005)=Berekening!D10,IF(Berekening!D45-(INDEX(T2_Rente,7)+0.000005)*Berekening!D46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,7)-0.005+0.000005)&lt;Berekening!D10,(Berekening!D45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!D46)/(360*((INDEX(T2_Rente,7)-0.005+0.000005)-Berekening!D10)),IF((INDEX(T2_Rente,7)-0.005+0.000005)=Berekening!D10,IF(Berekening!D45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!D46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>714300.45751269</v>
       </c>
       <c r="E94" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,7)+0.000005)&gt;Berekening!E10,(Berekening!E45-(INDEX(T2_Rente,7)+0.000005)*Berekening!E46)/(360*((INDEX(T2_Rente,7)+0.000005)-Berekening!E10)),IF((INDEX(T2_Rente,7)+0.000005)=Berekening!E10,IF(Berekening!E45-(INDEX(T2_Rente,7)+0.000005)*Berekening!E46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,7)-0.005+0.000005)&lt;Berekening!E10,(Berekening!E45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!E46)/(360*((INDEX(T2_Rente,7)-0.005+0.000005)-Berekening!E10)),IF((INDEX(T2_Rente,7)-0.005+0.000005)=Berekening!E10,IF(Berekening!E45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!E46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>571703.459862139</v>
+        <v>0</v>
       </c>
       <c r="F94" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,7)+0.000005)&gt;Berekening!F10,(Berekening!F45-(INDEX(T2_Rente,7)+0.000005)*Berekening!F46)/(360*((INDEX(T2_Rente,7)+0.000005)-Berekening!F10)),IF((INDEX(T2_Rente,7)+0.000005)=Berekening!F10,IF(Berekening!F45-(INDEX(T2_Rente,7)+0.000005)*Berekening!F46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,7)-0.005+0.000005)&lt;Berekening!F10,(Berekening!F45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!F46)/(360*((INDEX(T2_Rente,7)-0.005+0.000005)-Berekening!F10)),IF((INDEX(T2_Rente,7)-0.005+0.000005)=Berekening!F10,IF(Berekening!F45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!F46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
@@ -15958,31 +15958,31 @@
       </c>
       <c r="G94" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,7)+0.000005)&gt;Berekening!G10,(Berekening!G45-(INDEX(T2_Rente,7)+0.000005)*Berekening!G46)/(360*((INDEX(T2_Rente,7)+0.000005)-Berekening!G10)),IF((INDEX(T2_Rente,7)+0.000005)=Berekening!G10,IF(Berekening!G45-(INDEX(T2_Rente,7)+0.000005)*Berekening!G46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,7)-0.005+0.000005)&lt;Berekening!G10,(Berekening!G45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!G46)/(360*((INDEX(T2_Rente,7)-0.005+0.000005)-Berekening!G10)),IF((INDEX(T2_Rente,7)-0.005+0.000005)=Berekening!G10,IF(Berekening!G45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!G46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H94" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,7)+0.000005)&gt;Berekening!H10,(Berekening!H45-(INDEX(T2_Rente,7)+0.000005)*Berekening!H46)/(360*((INDEX(T2_Rente,7)+0.000005)-Berekening!H10)),IF((INDEX(T2_Rente,7)+0.000005)=Berekening!H10,IF(Berekening!H45-(INDEX(T2_Rente,7)+0.000005)*Berekening!H46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,7)-0.005+0.000005)&lt;Berekening!H10,(Berekening!H45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!H46)/(360*((INDEX(T2_Rente,7)-0.005+0.000005)-Berekening!H10)),IF((INDEX(T2_Rente,7)-0.005+0.000005)=Berekening!H10,IF(Berekening!H45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!H46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I94" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,7)+0.000005)&gt;Berekening!I10,(Berekening!I45-(INDEX(T2_Rente,7)+0.000005)*Berekening!I46)/(360*((INDEX(T2_Rente,7)+0.000005)-Berekening!I10)),IF((INDEX(T2_Rente,7)+0.000005)=Berekening!I10,IF(Berekening!I45-(INDEX(T2_Rente,7)+0.000005)*Berekening!I46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,7)-0.005+0.000005)&lt;Berekening!I10,(Berekening!I45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!I46)/(360*((INDEX(T2_Rente,7)-0.005+0.000005)-Berekening!I10)),IF((INDEX(T2_Rente,7)-0.005+0.000005)=Berekening!I10,IF(Berekening!I45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!I46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J94" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,7)+0.000005)&gt;Berekening!J10,(Berekening!J45-(INDEX(T2_Rente,7)+0.000005)*Berekening!J46)/(360*((INDEX(T2_Rente,7)+0.000005)-Berekening!J10)),IF((INDEX(T2_Rente,7)+0.000005)=Berekening!J10,IF(Berekening!J45-(INDEX(T2_Rente,7)+0.000005)*Berekening!J46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,7)-0.005+0.000005)&lt;Berekening!J10,(Berekening!J45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!J46)/(360*((INDEX(T2_Rente,7)-0.005+0.000005)-Berekening!J10)),IF((INDEX(T2_Rente,7)-0.005+0.000005)=Berekening!J10,IF(Berekening!J45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!J46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>788087.908879381</v>
       </c>
       <c r="K94" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,7)+0.000005)&gt;Berekening!K10,(Berekening!K45-(INDEX(T2_Rente,7)+0.000005)*Berekening!K46)/(360*((INDEX(T2_Rente,7)+0.000005)-Berekening!K10)),IF((INDEX(T2_Rente,7)+0.000005)=Berekening!K10,IF(Berekening!K45-(INDEX(T2_Rente,7)+0.000005)*Berekening!K46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,7)-0.005+0.000005)&lt;Berekening!K10,(Berekening!K45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!K46)/(360*((INDEX(T2_Rente,7)-0.005+0.000005)-Berekening!K10)),IF((INDEX(T2_Rente,7)-0.005+0.000005)=Berekening!K10,IF(Berekening!K45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!K46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>473496.503496504</v>
+        <v>0</v>
       </c>
       <c r="L94" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,7)+0.000005)&gt;Berekening!L10,(Berekening!L45-(INDEX(T2_Rente,7)+0.000005)*Berekening!L46)/(360*((INDEX(T2_Rente,7)+0.000005)-Berekening!L10)),IF((INDEX(T2_Rente,7)+0.000005)=Berekening!L10,IF(Berekening!L45-(INDEX(T2_Rente,7)+0.000005)*Berekening!L46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,7)-0.005+0.000005)&lt;Berekening!L10,(Berekening!L45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!L46)/(360*((INDEX(T2_Rente,7)-0.005+0.000005)-Berekening!L10)),IF((INDEX(T2_Rente,7)-0.005+0.000005)=Berekening!L10,IF(Berekening!L45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!L46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>788087.908879381</v>
       </c>
       <c r="M94" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,7)+0.000005)&gt;Berekening!M10,(Berekening!M45-(INDEX(T2_Rente,7)+0.000005)*Berekening!M46)/(360*((INDEX(T2_Rente,7)+0.000005)-Berekening!M10)),IF((INDEX(T2_Rente,7)+0.000005)=Berekening!M10,IF(Berekening!M45-(INDEX(T2_Rente,7)+0.000005)*Berekening!M46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,7)-0.005+0.000005)&lt;Berekening!M10,(Berekening!M45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!M46)/(360*((INDEX(T2_Rente,7)-0.005+0.000005)-Berekening!M10)),IF((INDEX(T2_Rente,7)-0.005+0.000005)=Berekening!M10,IF(Berekening!M45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!M46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>788087.908879381</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15994,15 +15994,15 @@
       </c>
       <c r="C95" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,7)+0.000005)&lt;Berekening!C10,(Berekening!C45-(INDEX(T2_Rente,7)+0.000005)*Berekening!C46)/(360*((INDEX(T2_Rente,7)+0.000005)-Berekening!C10)),1000000000000),IF((INDEX(T2_Rente,7)-0.005+0.000005)&gt;Berekening!C10,(Berekening!C45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!C46)/(360*((INDEX(T2_Rente,7)-0.005+0.000005)-Berekening!C10)),1000000000000))</f>
-        <v>-1086773226.34509</v>
+        <v>4378947.85667018</v>
       </c>
       <c r="D95" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,7)+0.000005)&lt;Berekening!D10,(Berekening!D45-(INDEX(T2_Rente,7)+0.000005)*Berekening!D46)/(360*((INDEX(T2_Rente,7)+0.000005)-Berekening!D10)),1000000000000),IF((INDEX(T2_Rente,7)-0.005+0.000005)&gt;Berekening!D10,(Berekening!D45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!D46)/(360*((INDEX(T2_Rente,7)-0.005+0.000005)-Berekening!D10)),1000000000000))</f>
-        <v>-985020330.910382</v>
+        <v>4244776.3612401</v>
       </c>
       <c r="E95" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,7)+0.000005)&lt;Berekening!E10,(Berekening!E45-(INDEX(T2_Rente,7)+0.000005)*Berekening!E46)/(360*((INDEX(T2_Rente,7)+0.000005)-Berekening!E10)),1000000000000),IF((INDEX(T2_Rente,7)-0.005+0.000005)&gt;Berekening!E10,(Berekening!E45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!E46)/(360*((INDEX(T2_Rente,7)-0.005+0.000005)-Berekening!E10)),1000000000000))</f>
-        <v>1145123174.65578</v>
+        <v>-1509960.85309235</v>
       </c>
       <c r="F95" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,7)+0.000005)&lt;Berekening!F10,(Berekening!F45-(INDEX(T2_Rente,7)+0.000005)*Berekening!F46)/(360*((INDEX(T2_Rente,7)+0.000005)-Berekening!F10)),1000000000000),IF((INDEX(T2_Rente,7)-0.005+0.000005)&gt;Berekening!F10,(Berekening!F45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!F46)/(360*((INDEX(T2_Rente,7)-0.005+0.000005)-Berekening!F10)),1000000000000))</f>
@@ -16010,31 +16010,31 @@
       </c>
       <c r="G95" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,7)+0.000005)&lt;Berekening!G10,(Berekening!G45-(INDEX(T2_Rente,7)+0.000005)*Berekening!G46)/(360*((INDEX(T2_Rente,7)+0.000005)-Berekening!G10)),1000000000000),IF((INDEX(T2_Rente,7)-0.005+0.000005)&gt;Berekening!G10,(Berekening!G45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!G46)/(360*((INDEX(T2_Rente,7)-0.005+0.000005)-Berekening!G10)),1000000000000))</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H95" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,7)+0.000005)&lt;Berekening!H10,(Berekening!H45-(INDEX(T2_Rente,7)+0.000005)*Berekening!H46)/(360*((INDEX(T2_Rente,7)+0.000005)-Berekening!H10)),1000000000000),IF((INDEX(T2_Rente,7)-0.005+0.000005)&gt;Berekening!H10,(Berekening!H45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!H46)/(360*((INDEX(T2_Rente,7)-0.005+0.000005)-Berekening!H10)),1000000000000))</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I95" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,7)+0.000005)&lt;Berekening!I10,(Berekening!I45-(INDEX(T2_Rente,7)+0.000005)*Berekening!I46)/(360*((INDEX(T2_Rente,7)+0.000005)-Berekening!I10)),1000000000000),IF((INDEX(T2_Rente,7)-0.005+0.000005)&gt;Berekening!I10,(Berekening!I45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!I46)/(360*((INDEX(T2_Rente,7)-0.005+0.000005)-Berekening!I10)),1000000000000))</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J95" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,7)+0.000005)&lt;Berekening!J10,(Berekening!J45-(INDEX(T2_Rente,7)+0.000005)*Berekening!J46)/(360*((INDEX(T2_Rente,7)+0.000005)-Berekening!J10)),1000000000000),IF((INDEX(T2_Rente,7)-0.005+0.000005)&gt;Berekening!J10,(Berekening!J45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!J46)/(360*((INDEX(T2_Rente,7)-0.005+0.000005)-Berekening!J10)),1000000000000))</f>
-        <v>-1086773226.34509</v>
+        <v>4378947.85667018</v>
       </c>
       <c r="K95" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,7)+0.000005)&lt;Berekening!K10,(Berekening!K45-(INDEX(T2_Rente,7)+0.000005)*Berekening!K46)/(360*((INDEX(T2_Rente,7)+0.000005)-Berekening!K10)),1000000000000),IF((INDEX(T2_Rente,7)-0.005+0.000005)&gt;Berekening!K10,(Berekening!K45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!K46)/(360*((INDEX(T2_Rente,7)-0.005+0.000005)-Berekening!K10)),1000000000000))</f>
-        <v>948414444.444812</v>
+        <v>-1250580.47493404</v>
       </c>
       <c r="L95" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,7)+0.000005)&lt;Berekening!L10,(Berekening!L45-(INDEX(T2_Rente,7)+0.000005)*Berekening!L46)/(360*((INDEX(T2_Rente,7)+0.000005)-Berekening!L10)),1000000000000),IF((INDEX(T2_Rente,7)-0.005+0.000005)&gt;Berekening!L10,(Berekening!L45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!L46)/(360*((INDEX(T2_Rente,7)-0.005+0.000005)-Berekening!L10)),1000000000000))</f>
-        <v>-1086773226.34509</v>
+        <v>4378947.85667018</v>
       </c>
       <c r="M95" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,7)+0.000005)&lt;Berekening!M10,(Berekening!M45-(INDEX(T2_Rente,7)+0.000005)*Berekening!M46)/(360*((INDEX(T2_Rente,7)+0.000005)-Berekening!M10)),1000000000000),IF((INDEX(T2_Rente,7)-0.005+0.000005)&gt;Berekening!M10,(Berekening!M45-(INDEX(T2_Rente,7)-0.005+0.000005)*Berekening!M46)/(360*((INDEX(T2_Rente,7)-0.005+0.000005)-Berekening!M10)),1000000000000))</f>
-        <v>-1086773226.34509</v>
+        <v>4378947.85667018</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16054,23 +16054,23 @@
       </c>
       <c r="E96" s="29" t="n">
         <f aca="false">IF(E94&gt;E95,-1,IF(E93&lt;E94-0.000000001,-1,IF(E93&gt;E95,MAX(E94,E95-1),E93)))</f>
-        <v>674321.454318775</v>
+        <v>-1</v>
       </c>
       <c r="F96" s="29" t="n">
         <f aca="false">IF(F94&gt;F95,-1,IF(F93&lt;F94-0.000000001,-1,IF(F93&gt;F95,MAX(F94,F95-1),F93)))</f>
-        <v>717391.7358281</v>
+        <v>628069.700454507</v>
       </c>
       <c r="G96" s="29" t="n">
         <f aca="false">IF(G94&gt;G95,-1,IF(G93&lt;G94-0.000000001,-1,IF(G93&gt;G95,MAX(G94,G95-1),G93)))</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H96" s="29" t="n">
         <f aca="false">IF(H94&gt;H95,-1,IF(H93&lt;H94-0.000000001,-1,IF(H93&gt;H95,MAX(H94,H95-1),H93)))</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I96" s="29" t="n">
         <f aca="false">IF(I94&gt;I95,-1,IF(I93&lt;I94-0.000000001,-1,IF(I93&gt;I95,MAX(I94,I95-1),I93)))</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J96" s="29" t="n">
         <f aca="false">IF(J94&gt;J95,-1,IF(J93&lt;J94-0.000000001,-1,IF(J93&gt;J95,MAX(J94,J95-1),J93)))</f>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="K96" s="29" t="n">
         <f aca="false">IF(K94&gt;K95,-1,IF(K93&lt;K94-0.000000001,-1,IF(K93&gt;K95,MAX(K94,K95-1),K93)))</f>
-        <v>577982.452964045</v>
+        <v>-1</v>
       </c>
       <c r="L96" s="29" t="n">
         <f aca="false">IF(L94&gt;L95,-1,IF(L93&lt;L94-0.000000001,-1,IF(L93&gt;L95,MAX(L94,L95-1),L93)))</f>
@@ -16150,39 +16150,39 @@
       </c>
       <c r="C98" s="29" t="n">
         <f aca="false">MAX(0,(C97*C60/12-Berekening!C18-Berekening!C44)*Berekening!C11-Berekening!C75+C61)</f>
-        <v>855706.418641192</v>
+        <v>693914.914048154</v>
       </c>
       <c r="D98" s="29" t="n">
         <f aca="false">MAX(0,(D97*D60/12-Berekening!D18-Berekening!D44)*Berekening!D11-Berekening!D75+D61)</f>
-        <v>887229.867540297</v>
+        <v>722966.466001963</v>
       </c>
       <c r="E98" s="29" t="n">
         <f aca="false">MAX(0,(E97*E60/12-Berekening!E18-Berekening!E44)*Berekening!E11-Berekening!E75+E61)</f>
-        <v>723125.923344603</v>
+        <v>571267.370709619</v>
       </c>
       <c r="F98" s="29" t="n">
         <f aca="false">MAX(0,(F97*F60/12-Berekening!F18-Berekening!F44)*Berekening!F11-Berekening!F75+F61)</f>
-        <v>760795.352599836</v>
+        <v>669983.064289874</v>
       </c>
       <c r="G98" s="29" t="n">
         <f aca="false">MAX(0,(G97*G60/12-Berekening!G18-Berekening!G44)*Berekening!G11-Berekening!G75+G61)</f>
-        <v>379131.414974403</v>
+        <v>351127.117076354</v>
       </c>
       <c r="H98" s="29" t="n">
         <f aca="false">MAX(0,(H97*H60/12-Berekening!H18-Berekening!H44)*Berekening!H11-Berekening!H75+H61)</f>
-        <v>960430.37856091</v>
+        <v>884744.59298035</v>
       </c>
       <c r="I98" s="29" t="n">
         <f aca="false">MAX(0,(I97*I60/12-Berekening!I18-Berekening!I44)*Berekening!I11-Berekening!I75+I61)</f>
-        <v>1457501.67343094</v>
+        <v>1246686.82082184</v>
       </c>
       <c r="J98" s="29" t="n">
         <f aca="false">MAX(0,(J97*J60/12-Berekening!J18-Berekening!J44)*Berekening!J11-Berekening!J75+J61)</f>
-        <v>385603.258479641</v>
+        <v>260674.679935608</v>
       </c>
       <c r="K98" s="29" t="n">
         <f aca="false">MAX(0,(K97*K60/12-Berekening!K18-Berekening!K44)*Berekening!K11-Berekening!K75+K61)</f>
-        <v>626786.921989872</v>
+        <v>483532.449086637</v>
       </c>
       <c r="L98" s="29" t="n">
         <f aca="false">MAX(0,(L97*L60/12-Berekening!L18-Berekening!L44)*Berekening!L11-Berekening!L75+L61)</f>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="M98" s="29" t="n">
         <f aca="false">MAX(0,(M97*M60/12-Berekening!M18-Berekening!M44)*Berekening!M11-Berekening!M75+M61)</f>
-        <v>855706.418641192</v>
+        <v>693914.914048154</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16202,11 +16202,11 @@
       </c>
       <c r="C99" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,8)+0.000005)&gt;Berekening!C10,(Berekening!C45-(INDEX(T2_Rente,8)+0.000005)*Berekening!C46)/(360*((INDEX(T2_Rente,8)+0.000005)-Berekening!C10)),IF((INDEX(T2_Rente,8)+0.000005)=Berekening!C10,IF(Berekening!C45-(INDEX(T2_Rente,8)+0.000005)*Berekening!C46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,8)-0.005+0.000005)&lt;Berekening!C10,(Berekening!C45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!C46)/(360*((INDEX(T2_Rente,8)-0.005+0.000005)-Berekening!C10)),IF((INDEX(T2_Rente,8)-0.005+0.000005)=Berekening!C10,IF(Berekening!C45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!C46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>4378947.8566702</v>
       </c>
       <c r="D99" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,8)+0.000005)&gt;Berekening!D10,(Berekening!D45-(INDEX(T2_Rente,8)+0.000005)*Berekening!D46)/(360*((INDEX(T2_Rente,8)+0.000005)-Berekening!D10)),IF((INDEX(T2_Rente,8)+0.000005)=Berekening!D10,IF(Berekening!D45-(INDEX(T2_Rente,8)+0.000005)*Berekening!D46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,8)-0.005+0.000005)&lt;Berekening!D10,(Berekening!D45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!D46)/(360*((INDEX(T2_Rente,8)-0.005+0.000005)-Berekening!D10)),IF((INDEX(T2_Rente,8)-0.005+0.000005)=Berekening!D10,IF(Berekening!D45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!D46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>4244776.36124012</v>
       </c>
       <c r="E99" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,8)+0.000005)&gt;Berekening!E10,(Berekening!E45-(INDEX(T2_Rente,8)+0.000005)*Berekening!E46)/(360*((INDEX(T2_Rente,8)+0.000005)-Berekening!E10)),IF((INDEX(T2_Rente,8)+0.000005)=Berekening!E10,IF(Berekening!E45-(INDEX(T2_Rente,8)+0.000005)*Berekening!E46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,8)-0.005+0.000005)&lt;Berekening!E10,(Berekening!E45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!E46)/(360*((INDEX(T2_Rente,8)-0.005+0.000005)-Berekening!E10)),IF((INDEX(T2_Rente,8)-0.005+0.000005)=Berekening!E10,IF(Berekening!E45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!E46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
@@ -16218,19 +16218,19 @@
       </c>
       <c r="G99" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,8)+0.000005)&gt;Berekening!G10,(Berekening!G45-(INDEX(T2_Rente,8)+0.000005)*Berekening!G46)/(360*((INDEX(T2_Rente,8)+0.000005)-Berekening!G10)),IF((INDEX(T2_Rente,8)+0.000005)=Berekening!G10,IF(Berekening!G45-(INDEX(T2_Rente,8)+0.000005)*Berekening!G46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,8)-0.005+0.000005)&lt;Berekening!G10,(Berekening!G45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!G46)/(360*((INDEX(T2_Rente,8)-0.005+0.000005)-Berekening!G10)),IF((INDEX(T2_Rente,8)-0.005+0.000005)=Berekening!G10,IF(Berekening!G45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!G46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H99" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,8)+0.000005)&gt;Berekening!H10,(Berekening!H45-(INDEX(T2_Rente,8)+0.000005)*Berekening!H46)/(360*((INDEX(T2_Rente,8)+0.000005)-Berekening!H10)),IF((INDEX(T2_Rente,8)+0.000005)=Berekening!H10,IF(Berekening!H45-(INDEX(T2_Rente,8)+0.000005)*Berekening!H46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,8)-0.005+0.000005)&lt;Berekening!H10,(Berekening!H45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!H46)/(360*((INDEX(T2_Rente,8)-0.005+0.000005)-Berekening!H10)),IF((INDEX(T2_Rente,8)-0.005+0.000005)=Berekening!H10,IF(Berekening!H45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!H46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I99" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,8)+0.000005)&gt;Berekening!I10,(Berekening!I45-(INDEX(T2_Rente,8)+0.000005)*Berekening!I46)/(360*((INDEX(T2_Rente,8)+0.000005)-Berekening!I10)),IF((INDEX(T2_Rente,8)+0.000005)=Berekening!I10,IF(Berekening!I45-(INDEX(T2_Rente,8)+0.000005)*Berekening!I46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,8)-0.005+0.000005)&lt;Berekening!I10,(Berekening!I45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!I46)/(360*((INDEX(T2_Rente,8)-0.005+0.000005)-Berekening!I10)),IF((INDEX(T2_Rente,8)-0.005+0.000005)=Berekening!I10,IF(Berekening!I45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!I46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J99" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,8)+0.000005)&gt;Berekening!J10,(Berekening!J45-(INDEX(T2_Rente,8)+0.000005)*Berekening!J46)/(360*((INDEX(T2_Rente,8)+0.000005)-Berekening!J10)),IF((INDEX(T2_Rente,8)+0.000005)=Berekening!J10,IF(Berekening!J45-(INDEX(T2_Rente,8)+0.000005)*Berekening!J46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,8)-0.005+0.000005)&lt;Berekening!J10,(Berekening!J45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!J46)/(360*((INDEX(T2_Rente,8)-0.005+0.000005)-Berekening!J10)),IF((INDEX(T2_Rente,8)-0.005+0.000005)=Berekening!J10,IF(Berekening!J45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!J46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>4378947.8566702</v>
       </c>
       <c r="K99" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,8)+0.000005)&gt;Berekening!K10,(Berekening!K45-(INDEX(T2_Rente,8)+0.000005)*Berekening!K46)/(360*((INDEX(T2_Rente,8)+0.000005)-Berekening!K10)),IF((INDEX(T2_Rente,8)+0.000005)=Berekening!K10,IF(Berekening!K45-(INDEX(T2_Rente,8)+0.000005)*Berekening!K46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,8)-0.005+0.000005)&lt;Berekening!K10,(Berekening!K45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!K46)/(360*((INDEX(T2_Rente,8)-0.005+0.000005)-Berekening!K10)),IF((INDEX(T2_Rente,8)-0.005+0.000005)=Berekening!K10,IF(Berekening!K45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!K46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
@@ -16238,11 +16238,11 @@
       </c>
       <c r="L99" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,8)+0.000005)&gt;Berekening!L10,(Berekening!L45-(INDEX(T2_Rente,8)+0.000005)*Berekening!L46)/(360*((INDEX(T2_Rente,8)+0.000005)-Berekening!L10)),IF((INDEX(T2_Rente,8)+0.000005)=Berekening!L10,IF(Berekening!L45-(INDEX(T2_Rente,8)+0.000005)*Berekening!L46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,8)-0.005+0.000005)&lt;Berekening!L10,(Berekening!L45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!L46)/(360*((INDEX(T2_Rente,8)-0.005+0.000005)-Berekening!L10)),IF((INDEX(T2_Rente,8)-0.005+0.000005)=Berekening!L10,IF(Berekening!L45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!L46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>4378947.8566702</v>
       </c>
       <c r="M99" s="29" t="n">
         <f aca="false">MAX(0,IF((INDEX(T2_Rente,8)+0.000005)&gt;Berekening!M10,(Berekening!M45-(INDEX(T2_Rente,8)+0.000005)*Berekening!M46)/(360*((INDEX(T2_Rente,8)+0.000005)-Berekening!M10)),IF((INDEX(T2_Rente,8)+0.000005)=Berekening!M10,IF(Berekening!M45-(INDEX(T2_Rente,8)+0.000005)*Berekening!M46&lt;=0,-1000000000000,1000000000000),-1000000000000)),IF((INDEX(T2_Rente,8)-0.005+0.000005)&lt;Berekening!M10,(Berekening!M45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!M46)/(360*((INDEX(T2_Rente,8)-0.005+0.000005)-Berekening!M10)),IF((INDEX(T2_Rente,8)-0.005+0.000005)=Berekening!M10,IF(Berekening!M45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!M46&gt;0,-1000000000000,1000000000000),-1000000000000)))</f>
-        <v>0</v>
+        <v>4378947.8566702</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16254,15 +16254,15 @@
       </c>
       <c r="C100" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,8)+0.000005)&lt;Berekening!C10,(Berekening!C45-(INDEX(T2_Rente,8)+0.000005)*Berekening!C46)/(360*((INDEX(T2_Rente,8)+0.000005)-Berekening!C10)),1000000000000),IF((INDEX(T2_Rente,8)-0.005+0.000005)&gt;Berekening!C10,(Berekening!C45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!C46)/(360*((INDEX(T2_Rente,8)-0.005+0.000005)-Berekening!C10)),1000000000000))</f>
-        <v>-1657963.2744036</v>
+        <v>1000000000000</v>
       </c>
       <c r="D100" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,8)+0.000005)&lt;Berekening!D10,(Berekening!D45-(INDEX(T2_Rente,8)+0.000005)*Berekening!D46)/(360*((INDEX(T2_Rente,8)+0.000005)-Berekening!D10)),1000000000000),IF((INDEX(T2_Rente,8)-0.005+0.000005)&gt;Berekening!D10,(Berekening!D45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!D46)/(360*((INDEX(T2_Rente,8)-0.005+0.000005)-Berekening!D10)),1000000000000))</f>
-        <v>-1607163.07783217</v>
+        <v>1000000000000</v>
       </c>
       <c r="E100" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,8)+0.000005)&lt;Berekening!E10,(Berekening!E45-(INDEX(T2_Rente,8)+0.000005)*Berekening!E46)/(360*((INDEX(T2_Rente,8)+0.000005)-Berekening!E10)),1000000000000),IF((INDEX(T2_Rente,8)-0.005+0.000005)&gt;Berekening!E10,(Berekening!E45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!E46)/(360*((INDEX(T2_Rente,8)-0.005+0.000005)-Berekening!E10)),1000000000000))</f>
-        <v>571703.459862137</v>
+        <v>1000000000000</v>
       </c>
       <c r="F100" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,8)+0.000005)&lt;Berekening!F10,(Berekening!F45-(INDEX(T2_Rente,8)+0.000005)*Berekening!F46)/(360*((INDEX(T2_Rente,8)+0.000005)-Berekening!F10)),1000000000000),IF((INDEX(T2_Rente,8)-0.005+0.000005)&gt;Berekening!F10,(Berekening!F45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!F46)/(360*((INDEX(T2_Rente,8)-0.005+0.000005)-Berekening!F10)),1000000000000))</f>
@@ -16270,31 +16270,31 @@
       </c>
       <c r="G100" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,8)+0.000005)&lt;Berekening!G10,(Berekening!G45-(INDEX(T2_Rente,8)+0.000005)*Berekening!G46)/(360*((INDEX(T2_Rente,8)+0.000005)-Berekening!G10)),1000000000000),IF((INDEX(T2_Rente,8)-0.005+0.000005)&gt;Berekening!G10,(Berekening!G45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!G46)/(360*((INDEX(T2_Rente,8)-0.005+0.000005)-Berekening!G10)),1000000000000))</f>
-        <v>0</v>
+        <v>1000000000000</v>
       </c>
       <c r="H100" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,8)+0.000005)&lt;Berekening!H10,(Berekening!H45-(INDEX(T2_Rente,8)+0.000005)*Berekening!H46)/(360*((INDEX(T2_Rente,8)+0.000005)-Berekening!H10)),1000000000000),IF((INDEX(T2_Rente,8)-0.005+0.000005)&gt;Berekening!H10,(Berekening!H45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!H46)/(360*((INDEX(T2_Rente,8)-0.005+0.000005)-Berekening!H10)),1000000000000))</f>
-        <v>0</v>
+        <v>1000000000000</v>
       </c>
       <c r="I100" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,8)+0.000005)&lt;Berekening!I10,(Berekening!I45-(INDEX(T2_Rente,8)+0.000005)*Berekening!I46)/(360*((INDEX(T2_Rente,8)+0.000005)-Berekening!I10)),1000000000000),IF((INDEX(T2_Rente,8)-0.005+0.000005)&gt;Berekening!I10,(Berekening!I45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!I46)/(360*((INDEX(T2_Rente,8)-0.005+0.000005)-Berekening!I10)),1000000000000))</f>
-        <v>0</v>
+        <v>1000000000000</v>
       </c>
       <c r="J100" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,8)+0.000005)&lt;Berekening!J10,(Berekening!J45-(INDEX(T2_Rente,8)+0.000005)*Berekening!J46)/(360*((INDEX(T2_Rente,8)+0.000005)-Berekening!J10)),1000000000000),IF((INDEX(T2_Rente,8)-0.005+0.000005)&gt;Berekening!J10,(Berekening!J45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!J46)/(360*((INDEX(T2_Rente,8)-0.005+0.000005)-Berekening!J10)),1000000000000))</f>
-        <v>-1657963.2744036</v>
+        <v>1000000000000</v>
       </c>
       <c r="K100" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,8)+0.000005)&lt;Berekening!K10,(Berekening!K45-(INDEX(T2_Rente,8)+0.000005)*Berekening!K46)/(360*((INDEX(T2_Rente,8)+0.000005)-Berekening!K10)),1000000000000),IF((INDEX(T2_Rente,8)-0.005+0.000005)&gt;Berekening!K10,(Berekening!K45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!K46)/(360*((INDEX(T2_Rente,8)-0.005+0.000005)-Berekening!K10)),1000000000000))</f>
-        <v>473496.503496503</v>
+        <v>1000000000000</v>
       </c>
       <c r="L100" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,8)+0.000005)&lt;Berekening!L10,(Berekening!L45-(INDEX(T2_Rente,8)+0.000005)*Berekening!L46)/(360*((INDEX(T2_Rente,8)+0.000005)-Berekening!L10)),1000000000000),IF((INDEX(T2_Rente,8)-0.005+0.000005)&gt;Berekening!L10,(Berekening!L45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!L46)/(360*((INDEX(T2_Rente,8)-0.005+0.000005)-Berekening!L10)),1000000000000))</f>
-        <v>-1657963.2744036</v>
+        <v>1000000000000</v>
       </c>
       <c r="M100" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,8)+0.000005)&lt;Berekening!M10,(Berekening!M45-(INDEX(T2_Rente,8)+0.000005)*Berekening!M46)/(360*((INDEX(T2_Rente,8)+0.000005)-Berekening!M10)),1000000000000),IF((INDEX(T2_Rente,8)-0.005+0.000005)&gt;Berekening!M10,(Berekening!M45-(INDEX(T2_Rente,8)-0.005+0.000005)*Berekening!M46)/(360*((INDEX(T2_Rente,8)-0.005+0.000005)-Berekening!M10)),1000000000000))</f>
-        <v>-1657963.2744036</v>
+        <v>1000000000000</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16314,7 +16314,7 @@
       </c>
       <c r="E101" s="29" t="n">
         <f aca="false">IF(E99&gt;E100,-1,IF(E98&lt;E99-0.000000001,-1,IF(E98&gt;E100,MAX(E99,E100-1),E98)))</f>
-        <v>571702.459862137</v>
+        <v>571267.370709619</v>
       </c>
       <c r="F101" s="29" t="n">
         <f aca="false">IF(F99&gt;F100,-1,IF(F98&lt;F99-0.000000001,-1,IF(F98&gt;F100,MAX(F99,F100-1),F98)))</f>
@@ -16322,15 +16322,15 @@
       </c>
       <c r="G101" s="29" t="n">
         <f aca="false">IF(G99&gt;G100,-1,IF(G98&lt;G99-0.000000001,-1,IF(G98&gt;G100,MAX(G99,G100-1),G98)))</f>
-        <v>0</v>
+        <v>351127.117076354</v>
       </c>
       <c r="H101" s="29" t="n">
         <f aca="false">IF(H99&gt;H100,-1,IF(H98&lt;H99-0.000000001,-1,IF(H98&gt;H100,MAX(H99,H100-1),H98)))</f>
-        <v>0</v>
+        <v>884744.59298035</v>
       </c>
       <c r="I101" s="29" t="n">
         <f aca="false">IF(I99&gt;I100,-1,IF(I98&lt;I99-0.000000001,-1,IF(I98&gt;I100,MAX(I99,I100-1),I98)))</f>
-        <v>0</v>
+        <v>1246686.82082184</v>
       </c>
       <c r="J101" s="29" t="n">
         <f aca="false">IF(J99&gt;J100,-1,IF(J98&lt;J99-0.000000001,-1,IF(J98&gt;J100,MAX(J99,J100-1),J98)))</f>
@@ -16338,7 +16338,7 @@
       </c>
       <c r="K101" s="29" t="n">
         <f aca="false">IF(K99&gt;K100,-1,IF(K98&lt;K99-0.000000001,-1,IF(K98&gt;K100,MAX(K99,K100-1),K98)))</f>
-        <v>473495.503496503</v>
+        <v>483532.449086637</v>
       </c>
       <c r="L101" s="29" t="n">
         <f aca="false">IF(L99&gt;L100,-1,IF(L98&lt;L99-0.000000001,-1,IF(L98&gt;L100,MAX(L99,L100-1),L98)))</f>
@@ -16410,39 +16410,39 @@
       </c>
       <c r="C103" s="29" t="n">
         <f aca="false">MAX(0,(C102*C60/12-Berekening!C18-Berekening!C44)*Berekening!C11-Berekening!C75+C61)</f>
-        <v>898410.329038791</v>
+        <v>731918.961657777</v>
       </c>
       <c r="D103" s="29" t="n">
         <f aca="false">MAX(0,(D102*D60/12-Berekening!D18-Berekening!D44)*Berekening!D11-Berekening!D75+D61)</f>
-        <v>929933.777937896</v>
+        <v>760970.513611586</v>
       </c>
       <c r="E103" s="29" t="n">
         <f aca="false">MAX(0,(E102*E60/12-Berekening!E18-Berekening!E44)*Berekening!E11-Berekening!E75+E61)</f>
-        <v>765829.833742202</v>
+        <v>609271.418319242</v>
       </c>
       <c r="F103" s="29" t="n">
         <f aca="false">MAX(0,(F102*F60/12-Berekening!F18-Berekening!F44)*Berekening!F11-Berekening!F75+F61)</f>
-        <v>798773.517275104</v>
+        <v>706657.25764582</v>
       </c>
       <c r="G103" s="29" t="n">
         <f aca="false">MAX(0,(G102*G60/12-Berekening!G18-Berekening!G44)*Berekening!G11-Berekening!G75+G61)</f>
-        <v>387509.86459257</v>
+        <v>358848.574368468</v>
       </c>
       <c r="H103" s="29" t="n">
         <f aca="false">MAX(0,(H102*H60/12-Berekening!H18-Berekening!H44)*Berekening!H11-Berekening!H75+H61)</f>
-        <v>987922.166370523</v>
+        <v>910080.624720099</v>
       </c>
       <c r="I103" s="29" t="n">
         <f aca="false">MAX(0,(I102*I60/12-Berekening!I18-Berekening!I44)*Berekening!I11-Berekening!I75+I61)</f>
-        <v>1500205.58382854</v>
+        <v>1284690.86843146</v>
       </c>
       <c r="J103" s="29" t="n">
         <f aca="false">MAX(0,(J102*J60/12-Berekening!J18-Berekening!J44)*Berekening!J11-Berekening!J75+J61)</f>
-        <v>414011.439216241</v>
+        <v>285503.991040562</v>
       </c>
       <c r="K103" s="29" t="n">
         <f aca="false">MAX(0,(K102*K60/12-Berekening!K18-Berekening!K44)*Berekening!K11-Berekening!K75+K61)</f>
-        <v>669490.832387471</v>
+        <v>521536.49669626</v>
       </c>
       <c r="L103" s="29" t="n">
         <f aca="false">MAX(0,(L102*L60/12-Berekening!L18-Berekening!L44)*Berekening!L11-Berekening!L75+L61)</f>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="M103" s="29" t="n">
         <f aca="false">MAX(0,(M102*M60/12-Berekening!M18-Berekening!M44)*Berekening!M11-Berekening!M75+M61)</f>
-        <v>898410.329038791</v>
+        <v>731918.961657777</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16514,15 +16514,15 @@
       </c>
       <c r="C105" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,9)+0.000005)&lt;Berekening!C10,(Berekening!C45-(INDEX(T2_Rente,9)+0.000005)*Berekening!C46)/(360*((INDEX(T2_Rente,9)+0.000005)-Berekening!C10)),1000000000000),IF((INDEX(T2_Rente,9)-0.005+0.000005)&gt;Berekening!C10,(Berekening!C45-(INDEX(T2_Rente,9)-0.005+0.000005)*Berekening!C46)/(360*((INDEX(T2_Rente,9)-0.005+0.000005)-Berekening!C10)),1000000000000))</f>
-        <v>-1115676.78611261</v>
+        <v>-3594958.53302952</v>
       </c>
       <c r="D105" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,9)+0.000005)&lt;Berekening!D10,(Berekening!D45-(INDEX(T2_Rente,9)+0.000005)*Berekening!D46)/(360*((INDEX(T2_Rente,9)+0.000005)-Berekening!D10)),1000000000000),IF((INDEX(T2_Rente,9)-0.005+0.000005)&gt;Berekening!D10,(Berekening!D45-(INDEX(T2_Rente,9)-0.005+0.000005)*Berekening!D46)/(360*((INDEX(T2_Rente,9)-0.005+0.000005)-Berekening!D10)),1000000000000))</f>
-        <v>-1115702.22434283</v>
+        <v>-3595040.50066022</v>
       </c>
       <c r="E105" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,9)+0.000005)&lt;Berekening!E10,(Berekening!E45-(INDEX(T2_Rente,9)+0.000005)*Berekening!E46)/(360*((INDEX(T2_Rente,9)+0.000005)-Berekening!E10)),1000000000000),IF((INDEX(T2_Rente,9)-0.005+0.000005)&gt;Berekening!E10,(Berekening!E45-(INDEX(T2_Rente,9)-0.005+0.000005)*Berekening!E46)/(360*((INDEX(T2_Rente,9)-0.005+0.000005)-Berekening!E10)),1000000000000))</f>
-        <v>-286.280865234338</v>
+        <v>-922.460565755087</v>
       </c>
       <c r="F105" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,9)+0.000005)&lt;Berekening!F10,(Berekening!F45-(INDEX(T2_Rente,9)+0.000005)*Berekening!F46)/(360*((INDEX(T2_Rente,9)+0.000005)-Berekening!F10)),1000000000000),IF((INDEX(T2_Rente,9)-0.005+0.000005)&gt;Berekening!F10,(Berekening!F45-(INDEX(T2_Rente,9)-0.005+0.000005)*Berekening!F46)/(360*((INDEX(T2_Rente,9)-0.005+0.000005)-Berekening!F10)),1000000000000))</f>
@@ -16542,19 +16542,19 @@
       </c>
       <c r="J105" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,9)+0.000005)&lt;Berekening!J10,(Berekening!J45-(INDEX(T2_Rente,9)+0.000005)*Berekening!J46)/(360*((INDEX(T2_Rente,9)+0.000005)-Berekening!J10)),1000000000000),IF((INDEX(T2_Rente,9)-0.005+0.000005)&gt;Berekening!J10,(Berekening!J45-(INDEX(T2_Rente,9)-0.005+0.000005)*Berekening!J46)/(360*((INDEX(T2_Rente,9)-0.005+0.000005)-Berekening!J10)),1000000000000))</f>
-        <v>-1115676.78611261</v>
+        <v>-3594958.53302952</v>
       </c>
       <c r="K105" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,9)+0.000005)&lt;Berekening!K10,(Berekening!K45-(INDEX(T2_Rente,9)+0.000005)*Berekening!K46)/(360*((INDEX(T2_Rente,9)+0.000005)-Berekening!K10)),1000000000000),IF((INDEX(T2_Rente,9)-0.005+0.000005)&gt;Berekening!K10,(Berekening!K45-(INDEX(T2_Rente,9)-0.005+0.000005)*Berekening!K46)/(360*((INDEX(T2_Rente,9)-0.005+0.000005)-Berekening!K10)),1000000000000))</f>
-        <v>-237.103670387029</v>
+        <v>-764.000715691536</v>
       </c>
       <c r="L105" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,9)+0.000005)&lt;Berekening!L10,(Berekening!L45-(INDEX(T2_Rente,9)+0.000005)*Berekening!L46)/(360*((INDEX(T2_Rente,9)+0.000005)-Berekening!L10)),1000000000000),IF((INDEX(T2_Rente,9)-0.005+0.000005)&gt;Berekening!L10,(Berekening!L45-(INDEX(T2_Rente,9)-0.005+0.000005)*Berekening!L46)/(360*((INDEX(T2_Rente,9)-0.005+0.000005)-Berekening!L10)),1000000000000))</f>
-        <v>-1115676.78611261</v>
+        <v>-3594958.53302952</v>
       </c>
       <c r="M105" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,9)+0.000005)&lt;Berekening!M10,(Berekening!M45-(INDEX(T2_Rente,9)+0.000005)*Berekening!M46)/(360*((INDEX(T2_Rente,9)+0.000005)-Berekening!M10)),1000000000000),IF((INDEX(T2_Rente,9)-0.005+0.000005)&gt;Berekening!M10,(Berekening!M45-(INDEX(T2_Rente,9)-0.005+0.000005)*Berekening!M46)/(360*((INDEX(T2_Rente,9)-0.005+0.000005)-Berekening!M10)),1000000000000))</f>
-        <v>-1115676.78611261</v>
+        <v>-3594958.53302952</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16670,39 +16670,39 @@
       </c>
       <c r="C108" s="29" t="n">
         <f aca="false">MAX(0,(C107*C60/12-Berekening!C18-Berekening!C44)*Berekening!C11-Berekening!C75+C61)</f>
-        <v>941114.23943639</v>
+        <v>769923.0092674</v>
       </c>
       <c r="D108" s="29" t="n">
         <f aca="false">MAX(0,(D107*D60/12-Berekening!D18-Berekening!D44)*Berekening!D11-Berekening!D75+D61)</f>
-        <v>972637.688335495</v>
+        <v>798974.561221209</v>
       </c>
       <c r="E108" s="29" t="n">
         <f aca="false">MAX(0,(E107*E60/12-Berekening!E18-Berekening!E44)*Berekening!E11-Berekening!E75+E61)</f>
-        <v>808533.744139801</v>
+        <v>647275.465928865</v>
       </c>
       <c r="F108" s="29" t="n">
         <f aca="false">MAX(0,(F107*F60/12-Berekening!F18-Berekening!F44)*Berekening!F11-Berekening!F75+F61)</f>
-        <v>836751.681950373</v>
+        <v>743331.451001766</v>
       </c>
       <c r="G108" s="29" t="n">
         <f aca="false">MAX(0,(G107*G60/12-Berekening!G18-Berekening!G44)*Berekening!G11-Berekening!G75+G61)</f>
-        <v>395888.314210738</v>
+        <v>366570.031660582</v>
       </c>
       <c r="H108" s="29" t="n">
         <f aca="false">MAX(0,(H107*H60/12-Berekening!H18-Berekening!H44)*Berekening!H11-Berekening!H75+H61)</f>
-        <v>1015413.95418014</v>
+        <v>935416.656459848</v>
       </c>
       <c r="I108" s="29" t="n">
         <f aca="false">MAX(0,(I107*I60/12-Berekening!I18-Berekening!I44)*Berekening!I11-Berekening!I75+I61)</f>
-        <v>1542909.49422614</v>
+        <v>1322694.91604109</v>
       </c>
       <c r="J108" s="29" t="n">
         <f aca="false">MAX(0,(J107*J60/12-Berekening!J18-Berekening!J44)*Berekening!J11-Berekening!J75+J61)</f>
-        <v>442419.619952841</v>
+        <v>310333.302145515</v>
       </c>
       <c r="K108" s="29" t="n">
         <f aca="false">MAX(0,(K107*K60/12-Berekening!K18-Berekening!K44)*Berekening!K11-Berekening!K75+K61)</f>
-        <v>712194.74278507</v>
+        <v>559540.544305884</v>
       </c>
       <c r="L108" s="29" t="n">
         <f aca="false">MAX(0,(L107*L60/12-Berekening!L18-Berekening!L44)*Berekening!L11-Berekening!L75+L61)</f>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="M108" s="29" t="n">
         <f aca="false">MAX(0,(M107*M60/12-Berekening!M18-Berekening!M44)*Berekening!M11-Berekening!M75+M61)</f>
-        <v>941114.23943639</v>
+        <v>769923.0092674</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16774,15 +16774,15 @@
       </c>
       <c r="C110" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,10)-0.005+0.000005)&gt;Berekening!C10,(Berekening!C45-(INDEX(T2_Rente,10)-0.005+0.000005)*Berekening!C46)/(360*((INDEX(T2_Rente,10)-0.005+0.000005)-Berekening!C10)),1000000000000))</f>
-        <v>-934794.155396424</v>
+        <v>-1730609.04401275</v>
       </c>
       <c r="D110" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,10)-0.005+0.000005)&gt;Berekening!D10,(Berekening!D45-(INDEX(T2_Rente,10)-0.005+0.000005)*Berekening!D46)/(360*((INDEX(T2_Rente,10)-0.005+0.000005)-Berekening!D10)),1000000000000))</f>
-        <v>-951772.762715762</v>
+        <v>-1762041.98698951</v>
       </c>
       <c r="E110" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,10)-0.005+0.000005)&gt;Berekening!E10,(Berekening!E45-(INDEX(T2_Rente,10)-0.005+0.000005)*Berekening!E46)/(360*((INDEX(T2_Rente,10)-0.005+0.000005)-Berekening!E10)),1000000000000))</f>
-        <v>-191076.594250139</v>
+        <v>-353745.132229899</v>
       </c>
       <c r="F110" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,10)-0.005+0.000005)&gt;Berekening!F10,(Berekening!F45-(INDEX(T2_Rente,10)-0.005+0.000005)*Berekening!F46)/(360*((INDEX(T2_Rente,10)-0.005+0.000005)-Berekening!F10)),1000000000000))</f>
@@ -16802,19 +16802,19 @@
       </c>
       <c r="J110" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,10)-0.005+0.000005)&gt;Berekening!J10,(Berekening!J45-(INDEX(T2_Rente,10)-0.005+0.000005)*Berekening!J46)/(360*((INDEX(T2_Rente,10)-0.005+0.000005)-Berekening!J10)),1000000000000))</f>
-        <v>-934794.155396424</v>
+        <v>-1730609.04401275</v>
       </c>
       <c r="K110" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,10)-0.005+0.000005)&gt;Berekening!K10,(Berekening!K45-(INDEX(T2_Rente,10)-0.005+0.000005)*Berekening!K46)/(360*((INDEX(T2_Rente,10)-0.005+0.000005)-Berekening!K10)),1000000000000))</f>
-        <v>-158253.545114591</v>
+        <v>-292978.956748235</v>
       </c>
       <c r="L110" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,10)-0.005+0.000005)&gt;Berekening!L10,(Berekening!L45-(INDEX(T2_Rente,10)-0.005+0.000005)*Berekening!L46)/(360*((INDEX(T2_Rente,10)-0.005+0.000005)-Berekening!L10)),1000000000000))</f>
-        <v>-934794.155396424</v>
+        <v>-1730609.04401275</v>
       </c>
       <c r="M110" s="29" t="n">
         <f aca="false">MIN(1000000000000,IF((INDEX(T2_Rente,10)-0.005+0.000005)&gt;Berekening!M10,(Berekening!M45-(INDEX(T2_Rente,10)-0.005+0.000005)*Berekening!M46)/(360*((INDEX(T2_Rente,10)-0.005+0.000005)-Berekening!M10)),1000000000000))</f>
-        <v>-934794.155396424</v>
+        <v>-1730609.04401275</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16878,39 +16878,39 @@
       </c>
       <c r="C112" s="35" t="n">
         <f aca="false">MAX(0,C66,C71,C76,C81,C86,C91,C96,C101,C106,C111)</f>
-        <v>758097.480589537</v>
+        <v>607048.519511873</v>
       </c>
       <c r="D112" s="35" t="n">
         <f aca="false">MAX(0,D66,D71,D76,D81,D86,D91,D96,D101,D106,D111)</f>
-        <v>789620.929488642</v>
+        <v>636100.071465681</v>
       </c>
       <c r="E112" s="35" t="n">
         <f aca="false">MAX(0,E66,E71,E76,E81,E86,E91,E96,E101,E106,E111)</f>
-        <v>674321.454318775</v>
+        <v>571267.370709619</v>
       </c>
       <c r="F112" s="35" t="n">
         <f aca="false">MAX(0,F66,F71,F76,F81,F86,F91,F96,F101,F106,F111)</f>
-        <v>717391.7358281</v>
+        <v>628069.700454507</v>
       </c>
       <c r="G112" s="35" t="n">
         <f aca="false">MAX(0,G66,G71,G76,G81,G86,G91,G96,G101,G106,G111)</f>
-        <v>358185.290928983</v>
+        <v>351127.117076354</v>
       </c>
       <c r="H112" s="35" t="n">
         <f aca="false">MAX(0,H66,H71,H76,H81,H86,H91,H96,H101,H106,H111)</f>
-        <v>897592.006424652</v>
+        <v>884744.59298035</v>
       </c>
       <c r="I112" s="35" t="n">
         <f aca="false">MAX(0,I66,I71,I76,I81,I86,I91,I96,I101,I106,I111)</f>
-        <v>1359892.73537928</v>
+        <v>1246686.82082184</v>
       </c>
       <c r="J112" s="35" t="n">
         <f aca="false">MAX(0,J66,J71,J76,J81,J86,J91,J96,J101,J106,J111)</f>
-        <v>285498.240645907</v>
+        <v>173180.916994343</v>
       </c>
       <c r="K112" s="35" t="n">
         <f aca="false">MAX(0,K66,K71,K76,K81,K86,K91,K96,K101,K106,K111)</f>
-        <v>577982.452964045</v>
+        <v>483532.449086637</v>
       </c>
       <c r="L112" s="35" t="n">
         <f aca="false">MAX(0,L66,L71,L76,L81,L86,L91,L96,L101,L106,L111)</f>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="M112" s="35" t="n">
         <f aca="false">MAX(0,M66,M71,M76,M81,M86,M91,M96,M101,M106,M111)</f>
-        <v>758097.480589537</v>
+        <v>607048.519511873</v>
       </c>
     </row>
   </sheetData>
@@ -18768,19 +18768,19 @@
       </c>
       <c r="C9" s="57" t="n">
         <f aca="false">Berekening!C9</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="D9" s="57" t="n">
         <f aca="false">Berekening!D9</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="E9" s="57" t="n">
         <f aca="false">Berekening!E9</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="F9" s="57" t="n">
         <f aca="false">Berekening!F9</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="G9" s="57" t="n">
         <f aca="false">Berekening!G9</f>
@@ -18792,23 +18792,23 @@
       </c>
       <c r="I9" s="57" t="n">
         <f aca="false">Berekening!I9</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="J9" s="57" t="n">
         <f aca="false">Berekening!J9</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="K9" s="57" t="n">
         <f aca="false">Berekening!K9</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="L9" s="57" t="n">
         <f aca="false">Berekening!L9</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="M9" s="57" t="n">
         <f aca="false">Berekening!M9</f>
-        <v>233000</v>
+        <v>225000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18817,15 +18817,15 @@
       </c>
       <c r="C10" s="58" t="n">
         <f aca="false">Berekening!C10</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="D10" s="58" t="n">
         <f aca="false">Berekening!D10</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="E10" s="58" t="n">
         <f aca="false">Berekening!E10</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="F10" s="58" t="n">
         <f aca="false">Berekening!F10</f>
@@ -18833,31 +18833,31 @@
       </c>
       <c r="G10" s="58" t="n">
         <f aca="false">Berekening!G10</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="H10" s="58" t="n">
         <f aca="false">Berekening!H10</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="I10" s="58" t="n">
         <f aca="false">Berekening!I10</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="J10" s="58" t="n">
         <f aca="false">Berekening!J10</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="K10" s="58" t="n">
         <f aca="false">Berekening!K10</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="L10" s="58" t="n">
         <f aca="false">Berekening!L10</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="M10" s="58" t="n">
         <f aca="false">Berekening!M10</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18964,15 +18964,15 @@
       </c>
       <c r="C13" s="58" t="n">
         <f aca="false">Berekening!C70</f>
-        <v>0.0348065552716385</v>
+        <v>0.0371653095711625</v>
       </c>
       <c r="D13" s="58" t="n">
         <f aca="false">Berekening!D70</f>
-        <v>0.0348065552716385</v>
+        <v>0.0371653095711625</v>
       </c>
       <c r="E13" s="58" t="n">
         <f aca="false">Berekening!E70</f>
-        <v>0.0465815155079362</v>
+        <v>0.0489402698074602</v>
       </c>
       <c r="F13" s="58" t="n">
         <f aca="false">Berekening!F70</f>
@@ -18980,31 +18980,31 @@
       </c>
       <c r="G13" s="58" t="n">
         <f aca="false">Berekening!G70</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="H13" s="58" t="n">
         <f aca="false">Berekening!H70</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="I13" s="58" t="n">
         <f aca="false">Berekening!I70</f>
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="J13" s="58" t="n">
         <f aca="false">Berekening!J70</f>
-        <v>0.0348065552716385</v>
+        <v>0.0371653095711625</v>
       </c>
       <c r="K13" s="58" t="n">
         <f aca="false">Berekening!K70</f>
-        <v>0.0352689787001638</v>
+        <v>0.0369873839432004</v>
       </c>
       <c r="L13" s="58" t="n">
         <f aca="false">Berekening!L70</f>
-        <v>0.0348065552716385</v>
+        <v>0.0371653095711625</v>
       </c>
       <c r="M13" s="58" t="n">
         <f aca="false">Berekening!M70</f>
-        <v>0.0348065552716385</v>
+        <v>0.0371653095711625</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19013,11 +19013,11 @@
       </c>
       <c r="C14" s="60" t="n">
         <f aca="false">Berekening!C71</f>
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="D14" s="60" t="n">
         <f aca="false">Berekening!D71</f>
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="E14" s="60" t="n">
         <f aca="false">Berekening!E71</f>
@@ -19029,19 +19029,19 @@
       </c>
       <c r="G14" s="60" t="n">
         <f aca="false">Berekening!G71</f>
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="H14" s="60" t="n">
         <f aca="false">Berekening!H71</f>
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="I14" s="60" t="n">
         <f aca="false">Berekening!I71</f>
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="J14" s="60" t="n">
         <f aca="false">Berekening!J71</f>
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="K14" s="60" t="n">
         <f aca="false">Berekening!K71</f>
@@ -19049,11 +19049,11 @@
       </c>
       <c r="L14" s="60" t="n">
         <f aca="false">Berekening!L71</f>
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="M14" s="60" t="n">
         <f aca="false">Berekening!M71</f>
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19062,19 +19062,19 @@
       </c>
       <c r="C15" s="57" t="n">
         <f aca="false">Berekening!C75</f>
-        <v>35692.1953733948</v>
+        <v>80110.1194056814</v>
       </c>
       <c r="D15" s="57" t="n">
         <f aca="false">Berekening!D75</f>
-        <v>35692.1953733948</v>
+        <v>80110.1194056814</v>
       </c>
       <c r="E15" s="57" t="n">
         <f aca="false">Berekening!E75</f>
-        <v>38666.5449878444</v>
+        <v>83314.5241819087</v>
       </c>
       <c r="F15" s="57" t="n">
         <f aca="false">Berekening!F75</f>
-        <v>33064.9870256784</v>
+        <v>77306.8710741212</v>
       </c>
       <c r="G15" s="57" t="n">
         <f aca="false">Berekening!G75</f>
@@ -19082,27 +19082,27 @@
       </c>
       <c r="H15" s="57" t="n">
         <f aca="false">Berekening!H75</f>
-        <v>31419.1860681293</v>
+        <v>30113.6834392441</v>
       </c>
       <c r="I15" s="57" t="n">
         <f aca="false">Berekening!I75</f>
-        <v>37179.3701806196</v>
+        <v>83314.5241819087</v>
       </c>
       <c r="J15" s="57" t="n">
         <f aca="false">Berekening!J75</f>
-        <v>35692.1953733948</v>
+        <v>80110.1194056814</v>
       </c>
       <c r="K15" s="57" t="n">
         <f aca="false">Berekening!K75</f>
-        <v>37179.3701806196</v>
+        <v>80110.1194056814</v>
       </c>
       <c r="L15" s="57" t="n">
         <f aca="false">Berekening!L75</f>
-        <v>35692.1953733948</v>
+        <v>80110.1194056814</v>
       </c>
       <c r="M15" s="57" t="n">
         <f aca="false">Berekening!M75</f>
-        <v>35692.1953733948</v>
+        <v>80110.1194056814</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19111,39 +19111,39 @@
       </c>
       <c r="C16" s="57" t="n">
         <f aca="false">Berekening!C101</f>
-        <v>1048217.90060412</v>
+        <v>949478.277826761</v>
       </c>
       <c r="D16" s="57" t="n">
         <f aca="false">Berekening!D101</f>
-        <v>1048217.90060412</v>
+        <v>949478.277826761</v>
       </c>
       <c r="E16" s="57" t="n">
         <f aca="false">Berekening!E101</f>
-        <v>1045243.55098967</v>
+        <v>946273.873050534</v>
       </c>
       <c r="F16" s="57" t="n">
         <f aca="false">Berekening!F101</f>
-        <v>997108.348581655</v>
+        <v>916603.643081576</v>
       </c>
       <c r="G16" s="57" t="n">
         <f aca="false">Berekening!G101</f>
-        <v>258691.20171324</v>
+        <v>259434.811732502</v>
       </c>
       <c r="H16" s="57" t="n">
         <f aca="false">Berekening!H101</f>
-        <v>695985.562487489</v>
+        <v>684469.294466147</v>
       </c>
       <c r="I16" s="57" t="n">
         <f aca="false">Berekening!I101</f>
-        <v>1046730.72579689</v>
+        <v>946273.873050534</v>
       </c>
       <c r="J16" s="57" t="n">
         <f aca="false">Berekening!J101</f>
-        <v>923952.703535812</v>
+        <v>816650.991485521</v>
       </c>
       <c r="K16" s="57" t="n">
         <f aca="false">Berekening!K101</f>
-        <v>881245.662835284</v>
+        <v>796185.505543883</v>
       </c>
       <c r="L16" s="57" t="n">
         <f aca="false">Berekening!L101</f>
@@ -19151,7 +19151,7 @@
       </c>
       <c r="M16" s="57" t="n">
         <f aca="false">Berekening!M101</f>
-        <v>1048217.90060412</v>
+        <v>949478.277826761</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19209,39 +19209,39 @@
       </c>
       <c r="C18" s="57" t="n">
         <f aca="false">Berekening!C105</f>
-        <v>406298.599695031</v>
+        <v>328352.170374638</v>
       </c>
       <c r="D18" s="57" t="n">
         <f aca="false">Berekening!D105</f>
-        <v>476458.919906249</v>
+        <v>357403.722328447</v>
       </c>
       <c r="E18" s="57" t="n">
         <f aca="false">Berekening!E105</f>
-        <v>385561.679249296</v>
+        <v>270854.422938313</v>
       </c>
       <c r="F18" s="57" t="n">
         <f aca="false">Berekening!F105</f>
-        <v>395481.578104395</v>
+        <v>317212.252008869</v>
       </c>
       <c r="G18" s="57" t="n">
         <f aca="false">Berekening!G105</f>
-        <v>258691.20171324</v>
+        <v>259434.811732502</v>
       </c>
       <c r="H18" s="57" t="n">
         <f aca="false">Berekening!H105</f>
-        <v>695985.562487489</v>
+        <v>684469.294466147</v>
       </c>
       <c r="I18" s="57" t="n">
         <f aca="false">Berekening!I105</f>
-        <v>1046730.72579689</v>
+        <v>946273.873050534</v>
       </c>
       <c r="J18" s="57" t="n">
         <f aca="false">Berekening!J105</f>
-        <v>285498.240645907</v>
+        <v>173180.916994343</v>
       </c>
       <c r="K18" s="57" t="n">
         <f aca="false">Berekening!K105</f>
-        <v>289222.677894566</v>
+        <v>183119.501315332</v>
       </c>
       <c r="L18" s="57" t="n">
         <f aca="false">Berekening!L105</f>
@@ -19249,7 +19249,7 @@
       </c>
       <c r="M18" s="57" t="n">
         <f aca="false">Berekening!M105</f>
-        <v>406298.599695031</v>
+        <v>328352.170374638</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19356,39 +19356,39 @@
       </c>
       <c r="C21" s="57" t="n">
         <f aca="false">Berekening!C118</f>
-        <v>376250.09</v>
+        <v>328352.170374638</v>
       </c>
       <c r="D21" s="57" t="n">
         <f aca="false">Berekening!D118</f>
-        <v>476458.919906249</v>
+        <v>357403.722328447</v>
       </c>
       <c r="E21" s="57" t="n">
         <f aca="false">Berekening!E118</f>
-        <v>376250.09</v>
+        <v>270854.422938313</v>
       </c>
       <c r="F21" s="57" t="n">
         <f aca="false">Berekening!F118</f>
-        <v>376250.09</v>
+        <v>317212.252008869</v>
       </c>
       <c r="G21" s="57" t="n">
         <f aca="false">Berekening!G118</f>
-        <v>258691.20171324</v>
+        <v>259434.811732502</v>
       </c>
       <c r="H21" s="57" t="n">
         <f aca="false">Berekening!H118</f>
-        <v>695985.562487489</v>
+        <v>684469.294466147</v>
       </c>
       <c r="I21" s="57" t="n">
         <f aca="false">Berekening!I118</f>
-        <v>1000000</v>
+        <v>946273.873050534</v>
       </c>
       <c r="J21" s="57" t="n">
         <f aca="false">Berekening!J118</f>
-        <v>285498.240645907</v>
+        <v>173180.916994343</v>
       </c>
       <c r="K21" s="57" t="n">
         <f aca="false">Berekening!K118</f>
-        <v>289222.677894566</v>
+        <v>183119.501315332</v>
       </c>
       <c r="L21" s="57" t="n">
         <f aca="false">Berekening!L118</f>
@@ -19396,7 +19396,7 @@
       </c>
       <c r="M21" s="57" t="n">
         <f aca="false">Berekening!M118</f>
-        <v>376250.09</v>
+        <v>328352.170374638</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19405,39 +19405,39 @@
       </c>
       <c r="C22" s="57" t="n">
         <f aca="false">Berekening!C120</f>
-        <v>52270.09</v>
+        <v>4372.1703746377</v>
       </c>
       <c r="D22" s="57" t="n">
         <f aca="false">Berekening!D120</f>
-        <v>152478.919906249</v>
+        <v>33423.7223284466</v>
       </c>
       <c r="E22" s="57" t="n">
         <f aca="false">Berekening!E120</f>
-        <v>52270.09</v>
+        <v>-53125.5770616866</v>
       </c>
       <c r="F22" s="57" t="n">
         <f aca="false">Berekening!F120</f>
-        <v>52270.09</v>
+        <v>-6767.74799113092</v>
       </c>
       <c r="G22" s="57" t="n">
         <f aca="false">Berekening!G120</f>
-        <v>-114008.79828676</v>
+        <v>-113265.188267498</v>
       </c>
       <c r="H22" s="57" t="n">
         <f aca="false">Berekening!H120</f>
-        <v>101035.562487489</v>
+        <v>89519.2944661467</v>
       </c>
       <c r="I22" s="57" t="n">
         <f aca="false">Berekening!I120</f>
-        <v>52270.0899999999</v>
+        <v>-1456.03694946633</v>
       </c>
       <c r="J22" s="57" t="n">
         <f aca="false">Berekening!J120</f>
-        <v>-38481.7593540933</v>
+        <v>-150799.083005657</v>
       </c>
       <c r="K22" s="57" t="n">
         <f aca="false">Berekening!K120</f>
-        <v>106822.677894566</v>
+        <v>719.501315332163</v>
       </c>
       <c r="L22" s="57" t="n">
         <f aca="false">Berekening!L120</f>
@@ -19445,7 +19445,7 @@
       </c>
       <c r="M22" s="57" t="n">
         <f aca="false">Berekening!M120</f>
-        <v>52270.09</v>
+        <v>4372.1703746377</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19462,15 +19462,15 @@
       </c>
       <c r="E23" s="57" t="n">
         <f aca="false">Berekening!E121</f>
-        <v>0</v>
+        <v>53125.5770616866</v>
       </c>
       <c r="F23" s="57" t="n">
         <f aca="false">Berekening!F121</f>
-        <v>0</v>
+        <v>6767.74799113092</v>
       </c>
       <c r="G23" s="57" t="n">
         <f aca="false">Berekening!G121</f>
-        <v>114008.79828676</v>
+        <v>113265.188267498</v>
       </c>
       <c r="H23" s="57" t="n">
         <f aca="false">Berekening!H121</f>
@@ -19478,11 +19478,11 @@
       </c>
       <c r="I23" s="57" t="n">
         <f aca="false">Berekening!I121</f>
-        <v>0</v>
+        <v>1456.03694946633</v>
       </c>
       <c r="J23" s="57" t="n">
         <f aca="false">Berekening!J121</f>
-        <v>38481.7593540933</v>
+        <v>150799.083005657</v>
       </c>
       <c r="K23" s="57" t="n">
         <f aca="false">Berekening!K121</f>
@@ -19511,11 +19511,11 @@
       </c>
       <c r="E24" s="61" t="n">
         <f aca="false">Berekening!E122</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" s="61" t="n">
         <f aca="false">Berekening!F122</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="61" t="n">
         <f aca="false">Berekening!G122</f>
@@ -19527,7 +19527,7 @@
       </c>
       <c r="I24" s="61" t="n">
         <f aca="false">Berekening!I122</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="61" t="n">
         <f aca="false">Berekening!J122</f>
@@ -19552,39 +19552,39 @@
       </c>
       <c r="C25" s="57" t="n">
         <f aca="false">Berekening!C117</f>
-        <v>1000000</v>
+        <v>952102.080374638</v>
       </c>
       <c r="D25" s="57" t="n">
         <f aca="false">Berekening!D117</f>
-        <v>1100208.82990625</v>
+        <v>981153.632328447</v>
       </c>
       <c r="E25" s="57" t="n">
         <f aca="false">Berekening!E117</f>
-        <v>1000000</v>
+        <v>894604.332938314</v>
       </c>
       <c r="F25" s="57" t="n">
         <f aca="false">Berekening!F117</f>
-        <v>1000000</v>
+        <v>940962.162008869</v>
       </c>
       <c r="G25" s="57" t="n">
         <f aca="false">Berekening!G117</f>
-        <v>258691.20171324</v>
+        <v>259434.811732502</v>
       </c>
       <c r="H25" s="57" t="n">
         <f aca="false">Berekening!H117</f>
-        <v>695985.562487489</v>
+        <v>684469.294466147</v>
       </c>
       <c r="I25" s="57" t="n">
         <f aca="false">Berekening!I117</f>
-        <v>1000000</v>
+        <v>946273.873050534</v>
       </c>
       <c r="J25" s="57" t="n">
         <f aca="false">Berekening!J117</f>
-        <v>909248.150645907</v>
+        <v>796930.826994343</v>
       </c>
       <c r="K25" s="57" t="n">
         <f aca="false">Berekening!K117</f>
-        <v>839222.677894566</v>
+        <v>733119.501315332</v>
       </c>
       <c r="L25" s="57" t="n">
         <f aca="false">Berekening!L117</f>
@@ -19592,7 +19592,7 @@
       </c>
       <c r="M25" s="57" t="n">
         <f aca="false">Berekening!M117</f>
-        <v>1000000</v>
+        <v>952102.080374638</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19601,19 +19601,19 @@
       </c>
       <c r="C26" s="57" t="n">
         <f aca="false">Berekening!C123</f>
-        <v>52270.0899999999</v>
+        <v>4372.1703746377</v>
       </c>
       <c r="D26" s="57" t="n">
         <f aca="false">Berekening!D123</f>
-        <v>152478.919906249</v>
+        <v>33423.7223284466</v>
       </c>
       <c r="E26" s="57" t="n">
         <f aca="false">Berekening!E123</f>
-        <v>52270.0899999999</v>
+        <v>-53125.5770616867</v>
       </c>
       <c r="F26" s="57" t="n">
         <f aca="false">Berekening!F123</f>
-        <v>52270.0899999999</v>
+        <v>-6767.74799113092</v>
       </c>
       <c r="G26" s="57" t="str">
         <f aca="false">Berekening!G123</f>
@@ -19625,15 +19625,15 @@
       </c>
       <c r="I26" s="57" t="n">
         <f aca="false">Berekening!I123</f>
-        <v>52270.0899999999</v>
+        <v>-1456.03694946622</v>
       </c>
       <c r="J26" s="57" t="n">
         <f aca="false">Berekening!J123</f>
-        <v>-38481.7593540933</v>
+        <v>-150799.083005657</v>
       </c>
       <c r="K26" s="57" t="n">
         <f aca="false">Berekening!K123</f>
-        <v>106822.677894566</v>
+        <v>719.501315332251</v>
       </c>
       <c r="L26" s="57" t="n">
         <f aca="false">Berekening!L123</f>
@@ -19641,7 +19641,7 @@
       </c>
       <c r="M26" s="57" t="n">
         <f aca="false">Berekening!M123</f>
-        <v>52270.0899999999</v>
+        <v>4372.1703746377</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19666,16 +19666,16 @@
         <v>53</v>
       </c>
       <c r="C30" s="62" t="n">
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="D30" s="62" t="n">
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="E30" s="62" t="n">
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="F30" s="62" t="n">
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="G30" s="62" t="n">
         <v>60000</v>
@@ -19684,16 +19684,16 @@
         <v>150000</v>
       </c>
       <c r="I30" s="62" t="n">
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="J30" s="62" t="n">
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="K30" s="62" t="n">
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="L30" s="62" t="n">
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="M30" s="63"/>
     </row>
@@ -19702,34 +19702,34 @@
         <v>174</v>
       </c>
       <c r="C31" s="64" t="n">
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="D31" s="64" t="n">
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="E31" s="64" t="n">
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="F31" s="64" t="n">
         <v>0.05</v>
       </c>
       <c r="G31" s="64" t="n">
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="H31" s="64" t="n">
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="I31" s="64" t="n">
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="J31" s="64" t="n">
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="K31" s="64" t="n">
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="L31" s="64" t="n">
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="M31" s="65"/>
     </row>
@@ -19810,34 +19810,34 @@
         <v>403</v>
       </c>
       <c r="C34" s="64" t="n">
-        <v>0.0348065552716385</v>
+        <v>0.0371653095711625</v>
       </c>
       <c r="D34" s="64" t="n">
-        <v>0.0348065552716385</v>
+        <v>0.0371653095711625</v>
       </c>
       <c r="E34" s="64" t="n">
-        <v>0.0465815155079362</v>
+        <v>0.0489402698074602</v>
       </c>
       <c r="F34" s="64" t="n">
         <v>0.0382250397637023</v>
       </c>
       <c r="G34" s="64" t="n">
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="H34" s="64" t="n">
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="I34" s="64" t="n">
-        <v>0.04</v>
+        <v>0.0469</v>
       </c>
       <c r="J34" s="64" t="n">
-        <v>0.0348065552716385</v>
+        <v>0.0371653095711625</v>
       </c>
       <c r="K34" s="64" t="n">
-        <v>0.0352689787001639</v>
+        <v>0.0369873839432004</v>
       </c>
       <c r="L34" s="64" t="n">
-        <v>0.0348065552716385</v>
+        <v>0.0371653095711625</v>
       </c>
       <c r="M34" s="65"/>
     </row>
@@ -19846,10 +19846,10 @@
         <v>57</v>
       </c>
       <c r="C35" s="68" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="D35" s="68" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="E35" s="68" t="n">
         <v>1.3</v>
@@ -19858,22 +19858,22 @@
         <v>1.25</v>
       </c>
       <c r="G35" s="68" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H35" s="68" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I35" s="68" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J35" s="68" t="n">
         <v>1.25</v>
-      </c>
-      <c r="H35" s="68" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I35" s="68" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="J35" s="68" t="n">
-        <v>1.2</v>
       </c>
       <c r="K35" s="68" t="n">
         <v>1.25</v>
       </c>
       <c r="L35" s="68" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="M35" s="69"/>
     </row>
@@ -19882,34 +19882,34 @@
         <v>404</v>
       </c>
       <c r="C36" s="62" t="n">
-        <v>35692.1953733948</v>
+        <v>80110.1194056814</v>
       </c>
       <c r="D36" s="62" t="n">
-        <v>35692.1953733948</v>
+        <v>80110.1194056814</v>
       </c>
       <c r="E36" s="62" t="n">
-        <v>38666.5449878444</v>
+        <v>83314.5241819087</v>
       </c>
       <c r="F36" s="62" t="n">
-        <v>33064.9870256784</v>
+        <v>77306.8710741212</v>
       </c>
       <c r="G36" s="62" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="62" t="n">
-        <v>31419.1860681293</v>
+        <v>30113.6834392441</v>
       </c>
       <c r="I36" s="62" t="n">
-        <v>37179.3701806196</v>
+        <v>83314.5241819087</v>
       </c>
       <c r="J36" s="62" t="n">
-        <v>35692.1953733948</v>
+        <v>80110.1194056814</v>
       </c>
       <c r="K36" s="62" t="n">
-        <v>37179.3701806196</v>
+        <v>80110.1194056814</v>
       </c>
       <c r="L36" s="62" t="n">
-        <v>35692.1953733948</v>
+        <v>80110.1194056814</v>
       </c>
       <c r="M36" s="63"/>
     </row>
@@ -19918,31 +19918,31 @@
         <v>405</v>
       </c>
       <c r="C37" s="62" t="n">
-        <v>1048217.90060412</v>
+        <v>949478.277826761</v>
       </c>
       <c r="D37" s="62" t="n">
-        <v>1048217.90060412</v>
+        <v>949478.277826761</v>
       </c>
       <c r="E37" s="62" t="n">
-        <v>1045243.55098967</v>
+        <v>946273.873050534</v>
       </c>
       <c r="F37" s="62" t="n">
-        <v>997108.348581655</v>
+        <v>916603.643081576</v>
       </c>
       <c r="G37" s="62" t="n">
-        <v>258691.20171324</v>
+        <v>259434.811732502</v>
       </c>
       <c r="H37" s="62" t="n">
-        <v>695985.562487489</v>
+        <v>684469.294466147</v>
       </c>
       <c r="I37" s="62" t="n">
-        <v>1046730.72579689</v>
+        <v>946273.873050534</v>
       </c>
       <c r="J37" s="62" t="n">
-        <v>923952.703535812</v>
+        <v>816650.991485521</v>
       </c>
       <c r="K37" s="62" t="n">
-        <v>881245.662835284</v>
+        <v>796185.505543883</v>
       </c>
       <c r="L37" s="62" t="n">
         <v>10000</v>
@@ -19990,31 +19990,31 @@
         <v>43</v>
       </c>
       <c r="C39" s="62" t="n">
-        <v>406298.599695031</v>
+        <v>328352.170374637</v>
       </c>
       <c r="D39" s="62" t="n">
-        <v>476458.919906249</v>
+        <v>357403.722328446</v>
       </c>
       <c r="E39" s="62" t="n">
-        <v>385561.679249296</v>
+        <v>270854.422938314</v>
       </c>
       <c r="F39" s="62" t="n">
-        <v>395481.578104395</v>
+        <v>317212.252008869</v>
       </c>
       <c r="G39" s="62" t="n">
-        <v>258691.20171324</v>
+        <v>259434.811732502</v>
       </c>
       <c r="H39" s="62" t="n">
-        <v>695985.562487489</v>
+        <v>684469.294466147</v>
       </c>
       <c r="I39" s="62" t="n">
-        <v>1046730.72579689</v>
+        <v>946273.873050534</v>
       </c>
       <c r="J39" s="62" t="n">
-        <v>285498.240645907</v>
+        <v>173180.916994343</v>
       </c>
       <c r="K39" s="62" t="n">
-        <v>289222.677894566</v>
+        <v>183119.501315332</v>
       </c>
       <c r="L39" s="62" t="n">
         <v>0</v>
@@ -20098,31 +20098,31 @@
         <v>45</v>
       </c>
       <c r="C42" s="62" t="n">
-        <v>376250.09</v>
+        <v>328352.170374637</v>
       </c>
       <c r="D42" s="62" t="n">
-        <v>476458.919906249</v>
+        <v>357403.722328446</v>
       </c>
       <c r="E42" s="62" t="n">
-        <v>376250.09</v>
+        <v>270854.422938314</v>
       </c>
       <c r="F42" s="62" t="n">
-        <v>376250.09</v>
+        <v>317212.252008869</v>
       </c>
       <c r="G42" s="62" t="n">
-        <v>258691.20171324</v>
+        <v>259434.811732502</v>
       </c>
       <c r="H42" s="62" t="n">
-        <v>695985.562487489</v>
+        <v>684469.294466147</v>
       </c>
       <c r="I42" s="62" t="n">
-        <v>1000000</v>
+        <v>946273.873050534</v>
       </c>
       <c r="J42" s="62" t="n">
-        <v>285498.240645907</v>
+        <v>173180.916994343</v>
       </c>
       <c r="K42" s="62" t="n">
-        <v>289222.677894566</v>
+        <v>183119.501315332</v>
       </c>
       <c r="L42" s="62" t="n">
         <v>0</v>
@@ -20134,31 +20134,31 @@
         <v>50</v>
       </c>
       <c r="C43" s="62" t="n">
-        <v>52270.09</v>
+        <v>4372.17037463735</v>
       </c>
       <c r="D43" s="62" t="n">
-        <v>152478.919906249</v>
+        <v>33423.7223284462</v>
       </c>
       <c r="E43" s="62" t="n">
-        <v>52270.09</v>
+        <v>-53125.5770616866</v>
       </c>
       <c r="F43" s="62" t="n">
-        <v>52270.09</v>
+        <v>-6767.74799113127</v>
       </c>
       <c r="G43" s="62" t="n">
-        <v>-114008.79828676</v>
+        <v>-113265.188267498</v>
       </c>
       <c r="H43" s="62" t="n">
-        <v>101035.562487489</v>
+        <v>89519.2944661467</v>
       </c>
       <c r="I43" s="62" t="n">
-        <v>52270.0899999999</v>
+        <v>-1456.03694946633</v>
       </c>
       <c r="J43" s="62" t="n">
-        <v>-38481.7593540933</v>
+        <v>-150799.083005657</v>
       </c>
       <c r="K43" s="62" t="n">
-        <v>106822.677894566</v>
+        <v>719.501315332163</v>
       </c>
       <c r="L43" s="62" t="n">
         <v>-323980</v>
@@ -20176,22 +20176,22 @@
         <v>0</v>
       </c>
       <c r="E44" s="62" t="n">
-        <v>0</v>
+        <v>53125.5770616866</v>
       </c>
       <c r="F44" s="62" t="n">
-        <v>0</v>
+        <v>6767.74799113127</v>
       </c>
       <c r="G44" s="62" t="n">
-        <v>114008.79828676</v>
+        <v>113265.188267498</v>
       </c>
       <c r="H44" s="62" t="n">
         <v>0</v>
       </c>
       <c r="I44" s="62" t="n">
-        <v>0</v>
+        <v>1456.03694946633</v>
       </c>
       <c r="J44" s="62" t="n">
-        <v>38481.7593540933</v>
+        <v>150799.083005657</v>
       </c>
       <c r="K44" s="62" t="n">
         <v>0</v>
@@ -20212,10 +20212,10 @@
         <v>1</v>
       </c>
       <c r="E45" s="70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" s="70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" s="70" t="n">
         <v>0</v>
@@ -20224,7 +20224,7 @@
         <v>1</v>
       </c>
       <c r="I45" s="70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" s="70" t="n">
         <v>0</v>
@@ -20242,31 +20242,31 @@
         <v>47</v>
       </c>
       <c r="C46" s="62" t="n">
-        <v>1000000</v>
+        <v>952102.080374637</v>
       </c>
       <c r="D46" s="62" t="n">
-        <v>1100208.82990625</v>
+        <v>981153.632328446</v>
       </c>
       <c r="E46" s="62" t="n">
-        <v>1000000</v>
+        <v>894604.332938314</v>
       </c>
       <c r="F46" s="62" t="n">
-        <v>1000000</v>
+        <v>940962.162008869</v>
       </c>
       <c r="G46" s="62" t="n">
-        <v>258691.20171324</v>
+        <v>259434.811732502</v>
       </c>
       <c r="H46" s="62" t="n">
-        <v>695985.562487489</v>
+        <v>684469.294466147</v>
       </c>
       <c r="I46" s="62" t="n">
-        <v>1000000</v>
+        <v>946273.873050534</v>
       </c>
       <c r="J46" s="62" t="n">
-        <v>909248.150645907</v>
+        <v>796930.826994343</v>
       </c>
       <c r="K46" s="62" t="n">
-        <v>839222.677894566</v>
+        <v>733119.501315332</v>
       </c>
       <c r="L46" s="62" t="n">
         <v>623749.91</v>
@@ -20278,16 +20278,16 @@
         <v>59</v>
       </c>
       <c r="C47" s="62" t="n">
-        <v>52270.0899999999</v>
+        <v>4372.17037463747</v>
       </c>
       <c r="D47" s="62" t="n">
-        <v>152478.919906249</v>
+        <v>33423.7223284463</v>
       </c>
       <c r="E47" s="62" t="n">
-        <v>52270.0899999999</v>
+        <v>-53125.5770616867</v>
       </c>
       <c r="F47" s="62" t="n">
-        <v>52270.0899999999</v>
+        <v>-6767.74799113115</v>
       </c>
       <c r="G47" s="62" t="s">
         <v>411</v>
@@ -20296,13 +20296,13 @@
         <v>411</v>
       </c>
       <c r="I47" s="62" t="n">
-        <v>52270.0899999999</v>
+        <v>-1456.03694946622</v>
       </c>
       <c r="J47" s="62" t="n">
-        <v>-38481.7593540933</v>
+        <v>-150799.083005657</v>
       </c>
       <c r="K47" s="62" t="n">
-        <v>106822.677894566</v>
+        <v>719.501315332251</v>
       </c>
       <c r="L47" s="62" t="n">
         <v>-323980</v>
@@ -20969,11 +20969,11 @@
       </c>
       <c r="C64" s="72" t="n">
         <f aca="false">IF(ISBLANK(C43),"",IF(AND(ISNUMBER(C43),ISNUMBER(C22)),C22-C43,IF(AND(C43="n.v.t.",C22="n.v.t."),"n.v.t.","FOUT")))</f>
-        <v>0</v>
+        <v>3.49245965480804E-010</v>
       </c>
       <c r="D64" s="72" t="n">
         <f aca="false">IF(ISBLANK(D43),"",IF(AND(ISNUMBER(D43),ISNUMBER(D22)),D22-D43,IF(AND(D43="n.v.t.",D22="n.v.t."),"n.v.t.","FOUT")))</f>
-        <v>0</v>
+        <v>3.49245965480804E-010</v>
       </c>
       <c r="E64" s="72" t="n">
         <f aca="false">IF(ISBLANK(E43),"",IF(AND(ISNUMBER(E43),ISNUMBER(E22)),E22-E43,IF(AND(E43="n.v.t.",E22="n.v.t."),"n.v.t.","FOUT")))</f>
@@ -20981,7 +20981,7 @@
       </c>
       <c r="F64" s="72" t="n">
         <f aca="false">IF(ISBLANK(F43),"",IF(AND(ISNUMBER(F43),ISNUMBER(F22)),F22-F43,IF(AND(F43="n.v.t.",F22="n.v.t."),"n.v.t.","FOUT")))</f>
-        <v>0</v>
+        <v>3.49245965480804E-010</v>
       </c>
       <c r="G64" s="72" t="n">
         <f aca="false">IF(ISBLANK(G43),"",IF(AND(ISNUMBER(G43),ISNUMBER(G22)),G22-G43,IF(AND(G43="n.v.t.",G22="n.v.t."),"n.v.t.","FOUT")))</f>
@@ -21030,7 +21030,7 @@
       </c>
       <c r="F65" s="72" t="n">
         <f aca="false">IF(ISBLANK(F44),"",IF(AND(ISNUMBER(F44),ISNUMBER(F23)),F23-F44,IF(AND(F44="n.v.t.",F23="n.v.t."),"n.v.t.","FOUT")))</f>
-        <v>0</v>
+        <v>-3.49245965480804E-010</v>
       </c>
       <c r="G65" s="72" t="n">
         <f aca="false">IF(ISBLANK(G44),"",IF(AND(ISNUMBER(G44),ISNUMBER(G23)),G23-G44,IF(AND(G44="n.v.t.",G23="n.v.t."),"n.v.t.","FOUT")))</f>
@@ -21165,11 +21165,11 @@
       </c>
       <c r="C68" s="72" t="n">
         <f aca="false">IF(ISBLANK(C47),"",IF(AND(ISNUMBER(C47),ISNUMBER(C26)),C26-C47,IF(AND(C47="n.v.t.",C26="n.v.t."),"n.v.t.","FOUT")))</f>
-        <v>0</v>
+        <v>2.3283064365387E-010</v>
       </c>
       <c r="D68" s="72" t="n">
         <f aca="false">IF(ISBLANK(D47),"",IF(AND(ISNUMBER(D47),ISNUMBER(D26)),D26-D47,IF(AND(D47="n.v.t.",D26="n.v.t."),"n.v.t.","FOUT")))</f>
-        <v>0</v>
+        <v>2.3283064365387E-010</v>
       </c>
       <c r="E68" s="72" t="n">
         <f aca="false">IF(ISBLANK(E47),"",IF(AND(ISNUMBER(E47),ISNUMBER(E26)),E26-E47,IF(AND(E47="n.v.t.",E26="n.v.t."),"n.v.t.","FOUT")))</f>
@@ -21177,7 +21177,7 @@
       </c>
       <c r="F68" s="72" t="n">
         <f aca="false">IF(ISBLANK(F47),"",IF(AND(ISNUMBER(F47),ISNUMBER(F26)),F26-F47,IF(AND(F47="n.v.t.",F26="n.v.t."),"n.v.t.","FOUT")))</f>
-        <v>0</v>
+        <v>2.3283064365387E-010</v>
       </c>
       <c r="G68" s="72" t="str">
         <f aca="false">IF(ISBLANK(G47),"",IF(AND(ISNUMBER(G47),ISNUMBER(G26)),G26-G47,IF(AND(G47="n.v.t.",G26="n.v.t."),"n.v.t.","FOUT")))</f>
